--- a/docs/40_テスト/44_テスト結果表.xlsx
+++ b/docs/40_テスト/44_テスト結果表.xlsx
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P2" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q2" s="12" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="P3" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q3" s="12" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="P4" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q4" s="12" t="inlineStr"/>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr"/>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr"/>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr"/>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q26" s="12" t="inlineStr"/>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr"/>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ApplicationServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr"/>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr"/>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q37" s="12" t="inlineStr"/>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr"/>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr"/>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr"/>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr"/>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q42" s="12" t="inlineStr"/>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr"/>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr"/>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr"/>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr"/>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q48" s="12" t="inlineStr"/>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q49" s="12" t="inlineStr"/>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q50" s="12" t="inlineStr"/>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q51" s="12" t="inlineStr"/>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q52" s="12" t="inlineStr"/>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q53" s="12" t="inlineStr"/>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q54" s="12" t="inlineStr"/>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="P55" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q55" s="12" t="inlineStr"/>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="P56" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q56" s="12" t="inlineStr"/>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="P57" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q57" s="12" t="inlineStr"/>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="P58" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q58" s="12" t="inlineStr"/>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="P59" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q59" s="12" t="inlineStr"/>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="P60" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q60" s="12" t="inlineStr"/>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="P61" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q61" s="12" t="inlineStr"/>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="P62" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q62" s="12" t="inlineStr"/>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="P63" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q63" s="12" t="inlineStr"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="P64" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q64" s="12" t="inlineStr"/>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="P65" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q65" s="12" t="inlineStr"/>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="P66" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q66" s="12" t="inlineStr"/>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="P67" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q67" s="12" t="inlineStr"/>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P68" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q68" s="12" t="inlineStr"/>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="P69" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q69" s="12" t="inlineStr"/>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="P70" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q70" s="12" t="inlineStr"/>
@@ -6823,7 +6823,7 @@
       </c>
       <c r="P71" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q71" s="12" t="inlineStr"/>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P72" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q72" s="12" t="inlineStr"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="P73" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.EventCommentServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q73" s="12" t="inlineStr"/>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="P74" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.FavoriteServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q74" s="12" t="inlineStr"/>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P75" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.FavoriteServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q75" s="12" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="P76" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.FavoriteServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q76" s="12" t="inlineStr"/>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="P77" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.FavoriteServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q77" s="12" t="inlineStr"/>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="P78" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.FavoriteServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q78" s="12" t="inlineStr"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="P79" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.FavoriteServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q79" s="12" t="inlineStr"/>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="P80" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.FavoriteServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q80" s="12" t="inlineStr"/>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="P81" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q81" s="12" t="inlineStr"/>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="P82" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q82" s="12" t="inlineStr"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="P83" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q83" s="12" t="inlineStr"/>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="P84" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q84" s="12" t="inlineStr"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P85" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q85" s="12" t="inlineStr"/>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="P86" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q86" s="12" t="inlineStr"/>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="P87" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q87" s="12" t="inlineStr"/>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="P88" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q88" s="12" t="inlineStr"/>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="P89" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q89" s="12" t="inlineStr"/>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="P90" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q90" s="12" t="inlineStr"/>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="P91" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q91" s="12" t="inlineStr"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="P92" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q92" s="12" t="inlineStr"/>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="P93" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q93" s="12" t="inlineStr"/>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P94" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q94" s="12" t="inlineStr"/>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="P95" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q95" s="12" t="inlineStr"/>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="P96" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q96" s="12" t="inlineStr"/>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="P97" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q97" s="12" t="inlineStr"/>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="P98" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q98" s="12" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="P99" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q99" s="12" t="inlineStr"/>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="P100" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q100" s="12" t="inlineStr"/>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="P101" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q101" s="12" t="inlineStr"/>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="P102" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q102" s="12" t="inlineStr"/>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="P103" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.UserServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q103" s="12" t="inlineStr"/>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="P104" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ReportServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q104" s="12" t="inlineStr"/>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="P105" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ReportServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q105" s="12" t="inlineStr"/>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="P106" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ReportServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q106" s="12" t="inlineStr"/>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="P107" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ReportServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q107" s="12" t="inlineStr"/>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="P108" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ReportServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q108" s="12" t="inlineStr"/>
@@ -9977,7 +9977,7 @@
       </c>
       <c r="P109" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ReportServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q109" s="12" t="inlineStr"/>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="P110" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ReportServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q110" s="12" t="inlineStr"/>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="P111" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/backend_20261007/com.example.eventapp.service.ReportServiceTest.txt</t>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q111" s="12" t="inlineStr"/>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P112" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q112" s="12" t="inlineStr"/>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="P113" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q113" s="12" t="inlineStr"/>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="P114" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q114" s="12" t="inlineStr"/>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="P115" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q115" s="12" t="inlineStr"/>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="P116" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q116" s="12" t="inlineStr"/>
@@ -10641,7 +10641,7 @@
       </c>
       <c r="P117" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q117" s="12" t="inlineStr"/>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="P118" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q118" s="12" t="inlineStr"/>
@@ -10807,7 +10807,7 @@
       </c>
       <c r="P119" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q119" s="12" t="inlineStr"/>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="P120" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q120" s="12" t="inlineStr"/>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="P121" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q121" s="12" t="inlineStr"/>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="P122" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q122" s="12" t="inlineStr"/>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="P123" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q123" s="12" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="P124" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q124" s="12" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
       </c>
       <c r="P125" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q125" s="12" t="inlineStr"/>
@@ -11388,7 +11388,7 @@
       </c>
       <c r="P126" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q126" s="12" t="inlineStr"/>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="P127" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q127" s="12" t="inlineStr"/>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="P128" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q128" s="12" t="inlineStr"/>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="P129" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q129" s="12" t="inlineStr"/>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="P130" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q130" s="12" t="inlineStr"/>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="P131" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q131" s="12" t="inlineStr"/>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="P132" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q132" s="12" t="inlineStr"/>
@@ -11969,7 +11969,7 @@
       </c>
       <c r="P133" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q133" s="12" t="inlineStr"/>
@@ -12052,7 +12052,7 @@
       </c>
       <c r="P134" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q134" s="12" t="inlineStr"/>
@@ -12135,7 +12135,7 @@
       </c>
       <c r="P135" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q135" s="12" t="inlineStr"/>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="P136" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q136" s="12" t="inlineStr"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="P137" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q137" s="12" t="inlineStr"/>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="P138" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q138" s="12" t="inlineStr"/>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="P139" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q139" s="12" t="inlineStr"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P140" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q140" s="12" t="inlineStr"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P141" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q141" s="12" t="inlineStr"/>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="P142" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q142" s="12" t="inlineStr"/>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="P143" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q143" s="12" t="inlineStr"/>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="P144" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q144" s="12" t="inlineStr"/>
@@ -12965,7 +12965,7 @@
       </c>
       <c r="P145" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q145" s="12" t="inlineStr"/>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="P146" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q146" s="12" t="inlineStr"/>
@@ -13131,7 +13131,7 @@
       </c>
       <c r="P147" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q147" s="12" t="inlineStr"/>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="P148" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q148" s="12" t="inlineStr"/>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="P149" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q149" s="12" t="inlineStr"/>
@@ -13380,7 +13380,7 @@
       </c>
       <c r="P150" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q150" s="12" t="inlineStr"/>
@@ -13463,7 +13463,7 @@
       </c>
       <c r="P151" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q151" s="12" t="inlineStr"/>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="P152" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q152" s="12" t="inlineStr"/>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="P153" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q153" s="12" t="inlineStr"/>
@@ -13712,7 +13712,7 @@
       </c>
       <c r="P154" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q154" s="12" t="inlineStr"/>
@@ -13795,7 +13795,7 @@
       </c>
       <c r="P155" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q155" s="12" t="inlineStr"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P156" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q156" s="12" t="inlineStr"/>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="P157" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q157" s="12" t="inlineStr"/>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="P158" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q158" s="12" t="inlineStr"/>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="P159" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q159" s="12" t="inlineStr"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P160" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q160" s="12" t="inlineStr"/>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="P161" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q161" s="12" t="inlineStr"/>
@@ -14376,7 +14376,7 @@
       </c>
       <c r="P162" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q162" s="12" t="inlineStr"/>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="P163" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q163" s="12" t="inlineStr"/>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="P164" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q164" s="12" t="inlineStr"/>
@@ -14625,7 +14625,7 @@
       </c>
       <c r="P165" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q165" s="12" t="inlineStr"/>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="P166" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q166" s="12" t="inlineStr"/>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="P167" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q167" s="12" t="inlineStr"/>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="P168" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q168" s="12" t="inlineStr"/>
@@ -14957,7 +14957,7 @@
       </c>
       <c r="P169" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q169" s="12" t="inlineStr"/>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="P170" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q170" s="12" t="inlineStr"/>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="P171" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q171" s="12" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="P172" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q172" s="12" t="inlineStr"/>
@@ -15289,7 +15289,7 @@
       </c>
       <c r="P173" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q173" s="12" t="inlineStr"/>
@@ -15372,7 +15372,7 @@
       </c>
       <c r="P174" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q174" s="12" t="inlineStr"/>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="P175" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q175" s="12" t="inlineStr"/>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="P176" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/frontend_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q176" s="12" t="inlineStr"/>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -16660,7 +16660,7 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr"/>
@@ -16970,7 +16970,7 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -17175,7 +17175,7 @@
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr"/>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr"/>
@@ -17341,7 +17341,7 @@
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr"/>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
@@ -17956,7 +17956,7 @@
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr"/>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr"/>
@@ -18244,7 +18244,7 @@
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr"/>
@@ -18327,7 +18327,7 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr"/>
@@ -18410,7 +18410,7 @@
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr"/>
@@ -18493,7 +18493,7 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr"/>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr"/>
@@ -18781,7 +18781,7 @@
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr"/>
@@ -18864,7 +18864,7 @@
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr"/>
@@ -19008,7 +19008,7 @@
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q48" s="12" t="inlineStr"/>
@@ -19091,7 +19091,7 @@
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q49" s="12" t="inlineStr"/>
@@ -19174,7 +19174,7 @@
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q50" s="12" t="inlineStr"/>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q51" s="12" t="inlineStr"/>
@@ -19340,7 +19340,7 @@
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q52" s="12" t="inlineStr"/>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q54" s="12" t="inlineStr"/>
@@ -19567,7 +19567,7 @@
       </c>
       <c r="P55" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q55" s="12" t="inlineStr"/>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="P59" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q59" s="12" t="inlineStr"/>
@@ -20099,7 +20099,7 @@
       </c>
       <c r="P63" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q63" s="12" t="inlineStr"/>
@@ -20182,7 +20182,7 @@
       </c>
       <c r="P64" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q64" s="12" t="inlineStr"/>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="P79" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q79" s="12" t="inlineStr"/>
@@ -21324,7 +21324,7 @@
       </c>
       <c r="P82" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q82" s="12" t="inlineStr"/>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="P119" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q119" s="12" t="inlineStr"/>
@@ -23686,7 +23686,7 @@
       </c>
       <c r="P120" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q120" s="12" t="inlineStr"/>
@@ -23769,7 +23769,7 @@
       </c>
       <c r="P121" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q121" s="12" t="inlineStr"/>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="P124" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q124" s="12" t="inlineStr"/>
@@ -24057,7 +24057,7 @@
       </c>
       <c r="P125" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q125" s="12" t="inlineStr"/>
@@ -24323,7 +24323,7 @@
       </c>
       <c r="P129" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q129" s="12" t="inlineStr"/>
@@ -24772,7 +24772,7 @@
       </c>
       <c r="P136" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q136" s="12" t="inlineStr"/>
@@ -24855,7 +24855,7 @@
       </c>
       <c r="P137" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q137" s="12" t="inlineStr"/>
@@ -25182,7 +25182,7 @@
       </c>
       <c r="P142" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q142" s="12" t="inlineStr"/>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="P174" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q174" s="12" t="inlineStr"/>
@@ -27239,7 +27239,7 @@
       </c>
       <c r="P175" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q175" s="12" t="inlineStr"/>
@@ -27322,7 +27322,7 @@
       </c>
       <c r="P176" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q176" s="12" t="inlineStr"/>
@@ -27466,7 +27466,7 @@
       </c>
       <c r="P178" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q178" s="12" t="inlineStr"/>
@@ -27549,7 +27549,7 @@
       </c>
       <c r="P179" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q179" s="12" t="inlineStr"/>
@@ -27632,7 +27632,7 @@
       </c>
       <c r="P180" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q180" s="12" t="inlineStr"/>
@@ -27959,7 +27959,7 @@
       </c>
       <c r="P185" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q185" s="12" t="inlineStr"/>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="P186" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q186" s="12" t="inlineStr"/>
@@ -28125,7 +28125,7 @@
       </c>
       <c r="P187" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q187" s="12" t="inlineStr"/>
@@ -28208,7 +28208,7 @@
       </c>
       <c r="P188" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q188" s="12" t="inlineStr"/>
@@ -28413,7 +28413,7 @@
       </c>
       <c r="P191" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q191" s="12" t="inlineStr"/>
@@ -28618,7 +28618,7 @@
       </c>
       <c r="P194" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q194" s="12" t="inlineStr"/>
@@ -28823,7 +28823,7 @@
       </c>
       <c r="P197" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q197" s="12" t="inlineStr"/>
@@ -28906,7 +28906,7 @@
       </c>
       <c r="P198" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q198" s="12" t="inlineStr"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="P199" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q199" s="12" t="inlineStr"/>
@@ -29194,7 +29194,7 @@
       </c>
       <c r="P202" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q202" s="12" t="inlineStr"/>
@@ -29277,7 +29277,7 @@
       </c>
       <c r="P203" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q203" s="12" t="inlineStr"/>
@@ -29360,7 +29360,7 @@
       </c>
       <c r="P204" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q204" s="12" t="inlineStr"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="P205" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q205" s="12" t="inlineStr"/>
@@ -29526,7 +29526,7 @@
       </c>
       <c r="P206" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q206" s="12" t="inlineStr"/>
@@ -29609,7 +29609,7 @@
       </c>
       <c r="P207" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/IT/IT_API結合_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q207" s="12" t="inlineStr"/>
@@ -42540,7 +42540,7 @@
       </c>
       <c r="P74" s="12" t="inlineStr">
         <is>
-          <t>evidence/IT/backend_20261007/com.example.eventapp.ApiIntegrationTest.txt</t>
+          <t>evidence/ST/ST_非機能_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="Q74" s="12" t="inlineStr"/>
@@ -43924,225 +43924,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010012AB853B196F794D8522E079E5062DE1" ma:contentTypeVersion="10" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f5519c8ad0001dc1944c7d5117d6ef1e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8d6e06c-e60e-47a7-a324-5df51f361a1d" xmlns:ns3="0eb4123e-ff08-448a-a51c-d574d85865b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6b6fc7ab0c5db989cb71f9aed3612649" ns2:_="" ns3:_="">
-    <xsd:import namespace="e8d6e06c-e60e-47a7-a324-5df51f361a1d"/>
-    <xsd:import namespace="0eb4123e-ff08-448a-a51c-d574d85865b6"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e8d6e06c-e60e-47a7-a324-5df51f361a1d" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8ae29c59-cffc-49bc-b1b2-82d81727b3d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0eb4123e-ff08-448a-a51c-d574d85865b6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{617f6a86-eb1c-4018-be3f-ff946cbc1596}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="0eb4123e-ff08-448a-a51c-d574d85865b6">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0eb4123e-ff08-448a-a51c-d574d85865b6" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8d6e06c-e60e-47a7-a324-5df51f361a1d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A5265FB-99B5-4F54-868A-1F425D348376}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D892701-3BC0-4589-B65D-AC64884BE627}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C180AA9B-4863-49C7-9361-8E560181613B}"/>
 </file>
--- a/docs/40_テスト/44_テスト結果表.xlsx
+++ b/docs/40_テスト/44_テスト結果表.xlsx
@@ -20849,9 +20849,19 @@
         </is>
       </c>
       <c r="L47" s="12" t="n"/>
-      <c r="M47" s="12" t="n"/>
-      <c r="N47" s="12" t="n"/>
-      <c r="O47" s="12" t="n"/>
+      <c r="M47" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N47" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O47" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P47" s="12" t="n"/>
       <c r="Q47" s="15" t="inlineStr">
         <is>
@@ -21775,9 +21785,19 @@
         </is>
       </c>
       <c r="L58" s="12" t="n"/>
-      <c r="M58" s="12" t="n"/>
-      <c r="N58" s="12" t="n"/>
-      <c r="O58" s="12" t="n"/>
+      <c r="M58" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N58" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O58" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P58" s="12" t="n"/>
       <c r="Q58" s="15" t="inlineStr">
         <is>
@@ -27000,9 +27020,19 @@
         </is>
       </c>
       <c r="L122" s="12" t="n"/>
-      <c r="M122" s="12" t="n"/>
-      <c r="N122" s="12" t="n"/>
-      <c r="O122" s="12" t="n"/>
+      <c r="M122" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N122" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O122" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P122" s="12" t="n"/>
       <c r="Q122" s="15" t="inlineStr">
         <is>
@@ -27071,9 +27101,19 @@
         </is>
       </c>
       <c r="L123" s="12" t="n"/>
-      <c r="M123" s="12" t="n"/>
-      <c r="N123" s="12" t="n"/>
-      <c r="O123" s="12" t="n"/>
+      <c r="M123" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N123" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O123" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P123" s="12" t="n"/>
       <c r="Q123" s="15" t="inlineStr">
         <is>
@@ -27318,9 +27358,19 @@
         </is>
       </c>
       <c r="L126" s="12" t="n"/>
-      <c r="M126" s="12" t="n"/>
-      <c r="N126" s="12" t="n"/>
-      <c r="O126" s="12" t="n"/>
+      <c r="M126" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N126" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O126" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P126" s="12" t="n"/>
       <c r="Q126" s="15" t="inlineStr">
         <is>
@@ -27389,9 +27439,19 @@
         </is>
       </c>
       <c r="L127" s="12" t="n"/>
-      <c r="M127" s="12" t="n"/>
-      <c r="N127" s="12" t="n"/>
-      <c r="O127" s="12" t="n"/>
+      <c r="M127" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N127" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O127" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P127" s="12" t="n"/>
       <c r="Q127" s="15" t="inlineStr">
         <is>
@@ -27460,9 +27520,19 @@
         </is>
       </c>
       <c r="L128" s="12" t="n"/>
-      <c r="M128" s="12" t="n"/>
-      <c r="N128" s="12" t="n"/>
-      <c r="O128" s="12" t="n"/>
+      <c r="M128" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N128" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O128" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P128" s="12" t="n"/>
       <c r="Q128" s="15" t="inlineStr">
         <is>
@@ -27619,9 +27689,19 @@
         </is>
       </c>
       <c r="L130" s="12" t="n"/>
-      <c r="M130" s="12" t="n"/>
-      <c r="N130" s="12" t="n"/>
-      <c r="O130" s="12" t="n"/>
+      <c r="M130" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N130" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O130" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P130" s="12" t="n"/>
       <c r="Q130" s="15" t="inlineStr">
         <is>
@@ -27690,9 +27770,19 @@
         </is>
       </c>
       <c r="L131" s="12" t="n"/>
-      <c r="M131" s="12" t="n"/>
-      <c r="N131" s="12" t="n"/>
-      <c r="O131" s="12" t="n"/>
+      <c r="M131" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N131" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O131" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P131" s="12" t="n"/>
       <c r="Q131" s="15" t="inlineStr">
         <is>
@@ -27761,9 +27851,19 @@
         </is>
       </c>
       <c r="L132" s="12" t="n"/>
-      <c r="M132" s="12" t="n"/>
-      <c r="N132" s="12" t="n"/>
-      <c r="O132" s="12" t="n"/>
+      <c r="M132" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N132" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O132" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P132" s="12" t="n"/>
       <c r="Q132" s="15" t="inlineStr">
         <is>
@@ -27833,9 +27933,19 @@
         </is>
       </c>
       <c r="L133" s="12" t="n"/>
-      <c r="M133" s="12" t="n"/>
-      <c r="N133" s="12" t="n"/>
-      <c r="O133" s="12" t="n"/>
+      <c r="M133" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N133" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O133" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P133" s="12" t="n"/>
       <c r="Q133" s="15" t="inlineStr">
         <is>
@@ -27905,9 +28015,19 @@
         </is>
       </c>
       <c r="L134" s="12" t="n"/>
-      <c r="M134" s="12" t="n"/>
-      <c r="N134" s="12" t="n"/>
-      <c r="O134" s="12" t="n"/>
+      <c r="M134" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N134" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O134" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P134" s="12" t="n"/>
       <c r="Q134" s="15" t="inlineStr">
         <is>
@@ -27977,9 +28097,19 @@
         </is>
       </c>
       <c r="L135" s="12" t="n"/>
-      <c r="M135" s="12" t="n"/>
-      <c r="N135" s="12" t="n"/>
-      <c r="O135" s="12" t="n"/>
+      <c r="M135" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N135" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O135" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P135" s="12" t="n"/>
       <c r="Q135" s="15" t="inlineStr">
         <is>
@@ -28224,9 +28354,19 @@
         </is>
       </c>
       <c r="L138" s="12" t="n"/>
-      <c r="M138" s="12" t="n"/>
-      <c r="N138" s="12" t="n"/>
-      <c r="O138" s="12" t="n"/>
+      <c r="M138" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N138" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O138" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P138" s="12" t="n"/>
       <c r="Q138" s="15" t="inlineStr">
         <is>
@@ -28296,9 +28436,19 @@
         </is>
       </c>
       <c r="L139" s="12" t="n"/>
-      <c r="M139" s="12" t="n"/>
-      <c r="N139" s="12" t="n"/>
-      <c r="O139" s="12" t="n"/>
+      <c r="M139" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N139" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O139" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P139" s="12" t="n"/>
       <c r="Q139" s="15" t="inlineStr">
         <is>
@@ -28368,9 +28518,19 @@
         </is>
       </c>
       <c r="L140" s="12" t="n"/>
-      <c r="M140" s="12" t="n"/>
-      <c r="N140" s="12" t="n"/>
-      <c r="O140" s="12" t="n"/>
+      <c r="M140" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N140" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O140" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P140" s="12" t="n"/>
       <c r="Q140" s="15" t="inlineStr">
         <is>
@@ -28439,9 +28599,19 @@
         </is>
       </c>
       <c r="L141" s="12" t="n"/>
-      <c r="M141" s="12" t="n"/>
-      <c r="N141" s="12" t="n"/>
-      <c r="O141" s="12" t="n"/>
+      <c r="M141" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N141" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O141" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P141" s="12" t="n"/>
       <c r="Q141" s="15" t="inlineStr">
         <is>
@@ -28599,9 +28769,19 @@
         </is>
       </c>
       <c r="L143" s="12" t="n"/>
-      <c r="M143" s="12" t="n"/>
-      <c r="N143" s="12" t="n"/>
-      <c r="O143" s="12" t="n"/>
+      <c r="M143" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N143" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O143" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P143" s="12" t="n"/>
       <c r="Q143" s="15" t="inlineStr">
         <is>
@@ -28670,9 +28850,19 @@
         </is>
       </c>
       <c r="L144" s="12" t="n"/>
-      <c r="M144" s="12" t="n"/>
-      <c r="N144" s="12" t="n"/>
-      <c r="O144" s="12" t="n"/>
+      <c r="M144" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N144" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O144" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P144" s="12" t="n"/>
       <c r="Q144" s="15" t="inlineStr">
         <is>
@@ -28742,9 +28932,19 @@
         </is>
       </c>
       <c r="L145" s="12" t="n"/>
-      <c r="M145" s="12" t="n"/>
-      <c r="N145" s="12" t="n"/>
-      <c r="O145" s="12" t="n"/>
+      <c r="M145" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N145" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O145" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P145" s="12" t="n"/>
       <c r="Q145" s="15" t="inlineStr">
         <is>
@@ -28812,9 +29012,19 @@
         </is>
       </c>
       <c r="L146" s="12" t="n"/>
-      <c r="M146" s="12" t="n"/>
-      <c r="N146" s="12" t="n"/>
-      <c r="O146" s="12" t="n"/>
+      <c r="M146" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N146" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O146" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P146" s="12" t="n"/>
       <c r="Q146" s="15" t="inlineStr">
         <is>
@@ -28883,9 +29093,19 @@
         </is>
       </c>
       <c r="L147" s="12" t="n"/>
-      <c r="M147" s="12" t="n"/>
-      <c r="N147" s="12" t="n"/>
-      <c r="O147" s="12" t="n"/>
+      <c r="M147" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N147" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O147" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P147" s="12" t="n"/>
       <c r="Q147" s="15" t="inlineStr">
         <is>
@@ -28954,9 +29174,19 @@
         </is>
       </c>
       <c r="L148" s="12" t="n"/>
-      <c r="M148" s="12" t="n"/>
-      <c r="N148" s="12" t="n"/>
-      <c r="O148" s="12" t="n"/>
+      <c r="M148" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N148" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O148" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P148" s="12" t="n"/>
       <c r="Q148" s="15" t="inlineStr">
         <is>
@@ -29025,9 +29255,19 @@
         </is>
       </c>
       <c r="L149" s="12" t="n"/>
-      <c r="M149" s="12" t="n"/>
-      <c r="N149" s="12" t="n"/>
-      <c r="O149" s="12" t="n"/>
+      <c r="M149" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N149" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O149" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P149" s="12" t="n"/>
       <c r="Q149" s="15" t="inlineStr">
         <is>
@@ -29096,9 +29336,19 @@
         </is>
       </c>
       <c r="L150" s="12" t="n"/>
-      <c r="M150" s="12" t="n"/>
-      <c r="N150" s="12" t="n"/>
-      <c r="O150" s="12" t="n"/>
+      <c r="M150" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N150" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O150" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P150" s="12" t="n"/>
       <c r="Q150" s="15" t="inlineStr">
         <is>
@@ -29166,9 +29416,19 @@
         </is>
       </c>
       <c r="L151" s="12" t="n"/>
-      <c r="M151" s="12" t="n"/>
-      <c r="N151" s="12" t="n"/>
-      <c r="O151" s="12" t="n"/>
+      <c r="M151" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N151" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O151" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P151" s="12" t="n"/>
       <c r="Q151" s="15" t="inlineStr">
         <is>
@@ -29236,9 +29496,19 @@
         </is>
       </c>
       <c r="L152" s="12" t="n"/>
-      <c r="M152" s="12" t="n"/>
-      <c r="N152" s="12" t="n"/>
-      <c r="O152" s="12" t="n"/>
+      <c r="M152" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N152" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O152" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P152" s="12" t="n"/>
       <c r="Q152" s="15" t="inlineStr">
         <is>
@@ -29306,9 +29576,19 @@
         </is>
       </c>
       <c r="L153" s="12" t="n"/>
-      <c r="M153" s="12" t="n"/>
-      <c r="N153" s="12" t="n"/>
-      <c r="O153" s="12" t="n"/>
+      <c r="M153" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N153" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O153" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P153" s="12" t="n"/>
       <c r="Q153" s="15" t="inlineStr">
         <is>
@@ -29377,9 +29657,19 @@
         </is>
       </c>
       <c r="L154" s="12" t="n"/>
-      <c r="M154" s="12" t="n"/>
-      <c r="N154" s="12" t="n"/>
-      <c r="O154" s="12" t="n"/>
+      <c r="M154" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N154" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O154" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P154" s="12" t="n"/>
       <c r="Q154" s="15" t="inlineStr">
         <is>
@@ -29448,9 +29738,19 @@
         </is>
       </c>
       <c r="L155" s="12" t="n"/>
-      <c r="M155" s="12" t="n"/>
-      <c r="N155" s="12" t="n"/>
-      <c r="O155" s="12" t="n"/>
+      <c r="M155" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N155" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O155" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P155" s="12" t="n"/>
       <c r="Q155" s="15" t="inlineStr">
         <is>
@@ -29519,9 +29819,19 @@
         </is>
       </c>
       <c r="L156" s="12" t="n"/>
-      <c r="M156" s="12" t="n"/>
-      <c r="N156" s="12" t="n"/>
-      <c r="O156" s="12" t="n"/>
+      <c r="M156" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N156" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O156" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P156" s="12" t="n"/>
       <c r="Q156" s="15" t="inlineStr">
         <is>
@@ -29590,9 +29900,19 @@
         </is>
       </c>
       <c r="L157" s="12" t="n"/>
-      <c r="M157" s="12" t="n"/>
-      <c r="N157" s="12" t="n"/>
-      <c r="O157" s="12" t="n"/>
+      <c r="M157" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N157" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O157" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P157" s="12" t="n"/>
       <c r="Q157" s="15" t="inlineStr">
         <is>
@@ -29660,9 +29980,19 @@
         </is>
       </c>
       <c r="L158" s="12" t="n"/>
-      <c r="M158" s="12" t="n"/>
-      <c r="N158" s="12" t="n"/>
-      <c r="O158" s="12" t="n"/>
+      <c r="M158" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N158" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O158" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P158" s="12" t="n"/>
       <c r="Q158" s="15" t="inlineStr">
         <is>
@@ -29730,9 +30060,19 @@
         </is>
       </c>
       <c r="L159" s="12" t="n"/>
-      <c r="M159" s="12" t="n"/>
-      <c r="N159" s="12" t="n"/>
-      <c r="O159" s="12" t="n"/>
+      <c r="M159" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N159" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O159" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P159" s="12" t="n"/>
       <c r="Q159" s="15" t="inlineStr">
         <is>
@@ -29800,9 +30140,19 @@
         </is>
       </c>
       <c r="L160" s="12" t="n"/>
-      <c r="M160" s="12" t="n"/>
-      <c r="N160" s="12" t="n"/>
-      <c r="O160" s="12" t="n"/>
+      <c r="M160" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N160" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O160" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P160" s="12" t="n"/>
       <c r="Q160" s="15" t="inlineStr">
         <is>
@@ -29870,9 +30220,19 @@
         </is>
       </c>
       <c r="L161" s="12" t="n"/>
-      <c r="M161" s="12" t="n"/>
-      <c r="N161" s="12" t="n"/>
-      <c r="O161" s="12" t="n"/>
+      <c r="M161" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N161" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O161" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P161" s="12" t="n"/>
       <c r="Q161" s="15" t="inlineStr">
         <is>
@@ -29940,9 +30300,19 @@
         </is>
       </c>
       <c r="L162" s="12" t="n"/>
-      <c r="M162" s="12" t="n"/>
-      <c r="N162" s="12" t="n"/>
-      <c r="O162" s="12" t="n"/>
+      <c r="M162" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N162" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O162" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P162" s="12" t="n"/>
       <c r="Q162" s="15" t="inlineStr">
         <is>
@@ -30011,9 +30381,19 @@
         </is>
       </c>
       <c r="L163" s="12" t="n"/>
-      <c r="M163" s="12" t="n"/>
-      <c r="N163" s="12" t="n"/>
-      <c r="O163" s="12" t="n"/>
+      <c r="M163" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N163" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O163" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P163" s="12" t="n"/>
       <c r="Q163" s="15" t="inlineStr">
         <is>
@@ -30082,9 +30462,19 @@
         </is>
       </c>
       <c r="L164" s="12" t="n"/>
-      <c r="M164" s="12" t="n"/>
-      <c r="N164" s="12" t="n"/>
-      <c r="O164" s="12" t="n"/>
+      <c r="M164" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N164" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O164" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P164" s="12" t="n"/>
       <c r="Q164" s="15" t="inlineStr">
         <is>
@@ -30153,9 +30543,19 @@
         </is>
       </c>
       <c r="L165" s="12" t="n"/>
-      <c r="M165" s="12" t="n"/>
-      <c r="N165" s="12" t="n"/>
-      <c r="O165" s="12" t="n"/>
+      <c r="M165" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N165" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O165" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P165" s="12" t="n"/>
       <c r="Q165" s="15" t="inlineStr">
         <is>
@@ -30224,9 +30624,19 @@
         </is>
       </c>
       <c r="L166" s="12" t="n"/>
-      <c r="M166" s="12" t="n"/>
-      <c r="N166" s="12" t="n"/>
-      <c r="O166" s="12" t="n"/>
+      <c r="M166" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N166" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O166" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P166" s="12" t="n"/>
       <c r="Q166" s="15" t="inlineStr">
         <is>
@@ -30295,9 +30705,19 @@
         </is>
       </c>
       <c r="L167" s="12" t="n"/>
-      <c r="M167" s="12" t="n"/>
-      <c r="N167" s="12" t="n"/>
-      <c r="O167" s="12" t="n"/>
+      <c r="M167" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N167" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O167" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P167" s="12" t="n"/>
       <c r="Q167" s="15" t="inlineStr">
         <is>
@@ -30366,9 +30786,19 @@
         </is>
       </c>
       <c r="L168" s="12" t="n"/>
-      <c r="M168" s="12" t="n"/>
-      <c r="N168" s="12" t="n"/>
-      <c r="O168" s="12" t="n"/>
+      <c r="M168" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N168" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O168" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P168" s="12" t="n"/>
       <c r="Q168" s="15" t="inlineStr">
         <is>
@@ -30436,9 +30866,19 @@
         </is>
       </c>
       <c r="L169" s="12" t="n"/>
-      <c r="M169" s="12" t="n"/>
-      <c r="N169" s="12" t="n"/>
-      <c r="O169" s="12" t="n"/>
+      <c r="M169" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N169" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O169" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P169" s="12" t="n"/>
       <c r="Q169" s="15" t="inlineStr">
         <is>
@@ -30506,9 +30946,19 @@
         </is>
       </c>
       <c r="L170" s="12" t="n"/>
-      <c r="M170" s="12" t="n"/>
-      <c r="N170" s="12" t="n"/>
-      <c r="O170" s="12" t="n"/>
+      <c r="M170" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N170" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O170" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P170" s="12" t="n"/>
       <c r="Q170" s="15" t="inlineStr">
         <is>
@@ -30576,9 +31026,19 @@
         </is>
       </c>
       <c r="L171" s="12" t="n"/>
-      <c r="M171" s="12" t="n"/>
-      <c r="N171" s="12" t="n"/>
-      <c r="O171" s="12" t="n"/>
+      <c r="M171" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N171" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O171" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P171" s="12" t="n"/>
       <c r="Q171" s="15" t="inlineStr">
         <is>
@@ -30646,9 +31106,19 @@
         </is>
       </c>
       <c r="L172" s="12" t="n"/>
-      <c r="M172" s="12" t="n"/>
-      <c r="N172" s="12" t="n"/>
-      <c r="O172" s="12" t="n"/>
+      <c r="M172" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N172" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O172" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P172" s="12" t="n"/>
       <c r="Q172" s="15" t="inlineStr">
         <is>
@@ -30716,9 +31186,19 @@
         </is>
       </c>
       <c r="L173" s="12" t="n"/>
-      <c r="M173" s="12" t="n"/>
-      <c r="N173" s="12" t="n"/>
-      <c r="O173" s="12" t="n"/>
+      <c r="M173" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N173" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O173" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P173" s="12" t="n"/>
       <c r="Q173" s="15" t="inlineStr">
         <is>
@@ -31050,9 +31530,19 @@
         </is>
       </c>
       <c r="L177" s="12" t="n"/>
-      <c r="M177" s="12" t="n"/>
-      <c r="N177" s="12" t="n"/>
-      <c r="O177" s="12" t="n"/>
+      <c r="M177" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N177" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O177" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P177" s="12" t="n"/>
       <c r="Q177" s="15" t="inlineStr">
         <is>
@@ -31384,9 +31874,19 @@
         </is>
       </c>
       <c r="L181" s="12" t="n"/>
-      <c r="M181" s="12" t="n"/>
-      <c r="N181" s="12" t="n"/>
-      <c r="O181" s="12" t="n"/>
+      <c r="M181" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N181" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O181" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P181" s="12" t="n"/>
       <c r="Q181" s="15" t="inlineStr">
         <is>
@@ -31454,9 +31954,19 @@
         </is>
       </c>
       <c r="L182" s="12" t="n"/>
-      <c r="M182" s="12" t="n"/>
-      <c r="N182" s="12" t="n"/>
-      <c r="O182" s="12" t="n"/>
+      <c r="M182" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N182" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O182" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P182" s="12" t="n"/>
       <c r="Q182" s="15" t="inlineStr">
         <is>
@@ -31524,9 +32034,19 @@
         </is>
       </c>
       <c r="L183" s="12" t="n"/>
-      <c r="M183" s="12" t="n"/>
-      <c r="N183" s="12" t="n"/>
-      <c r="O183" s="12" t="n"/>
+      <c r="M183" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N183" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O183" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P183" s="12" t="n"/>
       <c r="Q183" s="15" t="inlineStr">
         <is>
@@ -31594,9 +32114,19 @@
         </is>
       </c>
       <c r="L184" s="12" t="n"/>
-      <c r="M184" s="12" t="n"/>
-      <c r="N184" s="12" t="n"/>
-      <c r="O184" s="12" t="n"/>
+      <c r="M184" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N184" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O184" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P184" s="12" t="n"/>
       <c r="Q184" s="15" t="inlineStr">
         <is>
@@ -32016,9 +32546,19 @@
         </is>
       </c>
       <c r="L189" s="12" t="n"/>
-      <c r="M189" s="12" t="n"/>
-      <c r="N189" s="12" t="n"/>
-      <c r="O189" s="12" t="n"/>
+      <c r="M189" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N189" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O189" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P189" s="12" t="n"/>
       <c r="Q189" s="15" t="inlineStr">
         <is>
@@ -32086,9 +32626,19 @@
         </is>
       </c>
       <c r="L190" s="12" t="n"/>
-      <c r="M190" s="12" t="n"/>
-      <c r="N190" s="12" t="n"/>
-      <c r="O190" s="12" t="n"/>
+      <c r="M190" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N190" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O190" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P190" s="12" t="n"/>
       <c r="Q190" s="15" t="inlineStr">
         <is>
@@ -32244,9 +32794,19 @@
         </is>
       </c>
       <c r="L192" s="12" t="n"/>
-      <c r="M192" s="12" t="n"/>
-      <c r="N192" s="12" t="n"/>
-      <c r="O192" s="12" t="n"/>
+      <c r="M192" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N192" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O192" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P192" s="12" t="n"/>
       <c r="Q192" s="15" t="inlineStr">
         <is>
@@ -32314,9 +32874,19 @@
         </is>
       </c>
       <c r="L193" s="12" t="n"/>
-      <c r="M193" s="12" t="n"/>
-      <c r="N193" s="12" t="n"/>
-      <c r="O193" s="12" t="n"/>
+      <c r="M193" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N193" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O193" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P193" s="12" t="n"/>
       <c r="Q193" s="15" t="inlineStr">
         <is>
@@ -32472,9 +33042,19 @@
         </is>
       </c>
       <c r="L195" s="12" t="n"/>
-      <c r="M195" s="12" t="n"/>
-      <c r="N195" s="12" t="n"/>
-      <c r="O195" s="12" t="n"/>
+      <c r="M195" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N195" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O195" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P195" s="12" t="n"/>
       <c r="Q195" s="15" t="inlineStr">
         <is>
@@ -32542,9 +33122,19 @@
         </is>
       </c>
       <c r="L196" s="12" t="n"/>
-      <c r="M196" s="12" t="n"/>
-      <c r="N196" s="12" t="n"/>
-      <c r="O196" s="12" t="n"/>
+      <c r="M196" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N196" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O196" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P196" s="12" t="n"/>
       <c r="Q196" s="15" t="inlineStr">
         <is>
@@ -32877,9 +33467,19 @@
         </is>
       </c>
       <c r="L200" s="12" t="n"/>
-      <c r="M200" s="12" t="n"/>
-      <c r="N200" s="12" t="n"/>
-      <c r="O200" s="12" t="n"/>
+      <c r="M200" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N200" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O200" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P200" s="12" t="n"/>
       <c r="Q200" s="15" t="inlineStr">
         <is>
@@ -32948,9 +33548,19 @@
         </is>
       </c>
       <c r="L201" s="12" t="n"/>
-      <c r="M201" s="12" t="n"/>
-      <c r="N201" s="12" t="n"/>
-      <c r="O201" s="12" t="n"/>
+      <c r="M201" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N201" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O201" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P201" s="12" t="n"/>
       <c r="Q201" s="15" t="inlineStr">
         <is>
@@ -33546,9 +34156,19 @@
         </is>
       </c>
       <c r="L208" s="12" t="n"/>
-      <c r="M208" s="12" t="n"/>
-      <c r="N208" s="12" t="n"/>
-      <c r="O208" s="12" t="n"/>
+      <c r="M208" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N208" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O208" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P208" s="12" t="n"/>
       <c r="Q208" s="15" t="inlineStr">
         <is>
@@ -33616,9 +34236,19 @@
         </is>
       </c>
       <c r="L209" s="12" t="n"/>
-      <c r="M209" s="12" t="n"/>
-      <c r="N209" s="12" t="n"/>
-      <c r="O209" s="12" t="n"/>
+      <c r="M209" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N209" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O209" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P209" s="12" t="n"/>
       <c r="Q209" s="15" t="inlineStr">
         <is>
@@ -50711,13 +51341,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72DEE6A3-3E60-4415-B6F4-30A0401FE053}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CACC906C-3CA8-4650-A916-8D9184304EC2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0468774-0084-4D05-981B-0469B1D2AED0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ED1CC38-A086-4E46-898B-85B55345BB54}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E27FB40-061B-4063-8D78-7202FB007052}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B990BC16-3347-4678-9D17-F2BC795B3E14}"/>
 </file>
--- a/docs/40_テスト/44_テスト結果表.xlsx
+++ b/docs/40_テスト/44_テスト結果表.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="不具合一覧" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'UT'!$A$1:$T$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'UT'!$A$1:$T$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IT_API結合'!$A$1:$T$209</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'IT_画面結合'!$A$1:$T$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ST'!$A$1:$T$95</definedName>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,11 +181,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="36">
     <dxf>
       <font>
         <i val="1"/>
@@ -551,6 +554,52 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFD9D9D9"/>
           <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00595959"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9D9D9"/>
+          <bgColor rgb="00D9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FF5050"/>
+          <bgColor rgb="00FF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC000"/>
+          <bgColor rgb="00FFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <i val="1"/>
+        <color rgb="00A6A6A6"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F2F2F2"/>
+          <bgColor rgb="00F2F2F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1055,22 +1104,22 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D11" s="6">
-        <f>COUNTIF(UT!M2:M176,"OK")</f>
+        <f>COUNTIF(UT!M2:M177,"OK")</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>COUNTIF(UT!M2:M176,"NG")</f>
+        <f>COUNTIF(UT!M2:M177,"NG")</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>COUNTIF(UT!M2:M176,"保留")</f>
+        <f>COUNTIF(UT!M2:M177,"保留")</f>
         <v/>
       </c>
       <c r="G11" s="6">
-        <f>COUNTIF(UT!M2:M176,"対象外")</f>
+        <f>COUNTIF(UT!M2:M177,"対象外")</f>
         <v/>
       </c>
       <c r="H11" s="6">
@@ -1316,7 +1365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T176"/>
+  <dimension ref="A1:T177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16843,41 +16892,129 @@
       <c r="S176" s="12" t="n"/>
       <c r="T176" s="12" t="n"/>
     </row>
+    <row r="177" ht="40.5" customHeight="1">
+      <c r="A177" s="12" t="inlineStr">
+        <is>
+          <t>UT-APP-E15</t>
+        </is>
+      </c>
+      <c r="B177" s="12" t="inlineStr">
+        <is>
+          <t>ApplicationService（申込・キャンセル・当日受付）</t>
+        </is>
+      </c>
+      <c r="C177" s="12" t="inlineStr">
+        <is>
+          <t>異常系</t>
+        </is>
+      </c>
+      <c r="D177" s="12" t="inlineStr">
+        <is>
+          <t>区分の無いイベントに区分を指定すると指定された区分が見つかりませんで拒否される</t>
+        </is>
+      </c>
+      <c r="E177" s="12" t="inlineStr">
+        <is>
+          <t>区分なしイベントでticketTypeIdを指定</t>
+        </is>
+      </c>
+      <c r="F177" s="12" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="G177" s="12" t="inlineStr">
+        <is>
+          <t>NotFoundException「指定された区分が見つかりません」（E-B-005）</t>
+        </is>
+      </c>
+      <c r="H177" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="12" t="inlineStr">
+        <is>
+          <t>32_処理詳細設計書 4章 AP-030 No.7</t>
+        </is>
+      </c>
+      <c r="K177" s="12" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="L177" s="12" t="inlineStr">
+        <is>
+          <t>apply_異常系_区分の無いイベントに区分を指定すると指定された区分が見つかりませんで拒否される</t>
+        </is>
+      </c>
+      <c r="M177" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N177" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O177" s="12" t="inlineStr">
+        <is>
+          <t>佐々木（Claude Code）</t>
+        </is>
+      </c>
+      <c r="P177" s="12" t="inlineStr">
+        <is>
+          <t>自動テスト成功（Issue #18 の修正で追加）</t>
+        </is>
+      </c>
+      <c r="Q177" s="12" t="inlineStr">
+        <is>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261009.txt</t>
+        </is>
+      </c>
+      <c r="R177" s="12" t="n"/>
+      <c r="S177" s="12" t="n"/>
+      <c r="T177" s="12" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T176"/>
-  <conditionalFormatting sqref="M2:M176">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
+  <autoFilter ref="A1:T177"/>
+  <conditionalFormatting sqref="M2:M177">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="32">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="33">
       <formula>"NG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="34">
       <formula>"保留"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="35">
       <formula>"対象外"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S176">
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
+  <conditionalFormatting sqref="S2:S177">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="32">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="33">
       <formula>"NG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="34">
       <formula>"保留"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="35">
       <formula>"対象外"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M176" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,保留,対象外"</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S176" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="S2:S177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23195,7 +23332,8 @@
       </c>
       <c r="P75" s="12" t="inlineStr">
         <is>
-          <t>201が返り、申込が登録された（ticketTypeIdはnull、statusCode=1）。applicationsにID=2（event_id=53、user_id=1）の行が追加された</t>
+          <t>201が返り、申込が登録された（ticketTypeIdはnull、statusCode=1）。applicationsにID=2（event_id=53、user_id=1）の行が追加された
+【再テスト 2026/10/09】修正後、404「指定された区分が見つかりません」が返り、applicationsは変更されなかった（利用者はID=5で実施。ID=1が退会済みのため）</t>
         </is>
       </c>
       <c r="Q75" s="15" t="inlineStr">
@@ -23208,8 +23346,14 @@
           <t>#18</t>
         </is>
       </c>
-      <c r="S75" s="12" t="n"/>
-      <c r="T75" s="12" t="n"/>
+      <c r="S75" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T75" s="21" t="n">
+        <v>46304</v>
+      </c>
     </row>
     <row r="76" ht="27" customHeight="1">
       <c r="A76" s="12" t="inlineStr">
@@ -51115,12 +51259,18 @@
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>修正済み（再テストOK）</t>
         </is>
       </c>
       <c r="I3" s="16" t="n"/>
-      <c r="J3" s="16" t="n"/>
-      <c r="K3" s="16" t="n"/>
+      <c r="J3" s="23" t="n">
+        <v>46304</v>
+      </c>
+      <c r="K3" s="16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -51341,13 +51491,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CACC906C-3CA8-4650-A916-8D9184304EC2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C3B4A5B-5BD7-4FF5-BACD-086A5CF7B066}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ED1CC38-A086-4E46-898B-85B55345BB54}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49955E09-5CE1-4ED9-A6DC-4D42955CAF81}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B990BC16-3347-4678-9D17-F2BC795B3E14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58DBCBE2-5112-435B-BBC2-54F5EF9E6FDA}"/>
 </file>
--- a/docs/40_テスト/44_テスト結果表.xlsx
+++ b/docs/40_テスト/44_テスト結果表.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'UT'!$A$1:$T$177</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IT_API結合'!$A$1:$T$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IT_API結合'!$A$1:$T$212</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'IT_画面結合'!$A$1:$T$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ST'!$A$1:$T$95</definedName>
   </definedNames>
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D12" s="6">
-        <f>COUNTIF(IT_API結合!M2:M209,"OK")</f>
+        <f>COUNTIF(IT_API結合!M2:M212,"OK")</f>
         <v/>
       </c>
       <c r="E12" s="6">
-        <f>COUNTIF(IT_API結合!M2:M209,"NG")</f>
+        <f>COUNTIF(IT_API結合!M2:M212,"NG")</f>
         <v/>
       </c>
       <c r="F12" s="6">
-        <f>COUNTIF(IT_API結合!M2:M209,"保留")</f>
+        <f>COUNTIF(IT_API結合!M2:M212,"保留")</f>
         <v/>
       </c>
       <c r="G12" s="6">
-        <f>COUNTIF(IT_API結合!M2:M209,"対象外")</f>
+        <f>COUNTIF(IT_API結合!M2:M212,"対象外")</f>
         <v/>
       </c>
       <c r="H12" s="6">
@@ -17028,7 +17028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T209"/>
+  <dimension ref="A1:T212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -34403,41 +34403,305 @@
       <c r="S209" s="12" t="n"/>
       <c r="T209" s="12" t="n"/>
     </row>
+    <row r="210" ht="27" customHeight="1">
+      <c r="A210" s="12" t="inlineStr">
+        <is>
+          <t>IT-CMN-E08</t>
+        </is>
+      </c>
+      <c r="B210" s="12" t="inlineStr">
+        <is>
+          <t>認証・リクエスト形式</t>
+        </is>
+      </c>
+      <c r="C210" s="12" t="inlineStr">
+        <is>
+          <t>異常系</t>
+        </is>
+      </c>
+      <c r="D210" s="12" t="inlineStr">
+        <is>
+          <t>存在しないURLはリクエスト形式エラー（404）になる</t>
+        </is>
+      </c>
+      <c r="E210" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F210" s="12" t="inlineStr">
+        <is>
+          <t>一般ユーザー（ID=1）でGET /api/nothing</t>
+        </is>
+      </c>
+      <c r="G210" s="12" t="inlineStr">
+        <is>
+          <t>404「指定されたURLは存在しません」（E-V-028）。500にはならない</t>
+        </is>
+      </c>
+      <c r="H210" s="12" t="inlineStr">
+        <is>
+          <t>-（参照のみ）</t>
+        </is>
+      </c>
+      <c r="I210" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J210" s="12" t="inlineStr">
+        <is>
+          <t>33_共通詳細設計書 3.1</t>
+        </is>
+      </c>
+      <c r="K210" s="12" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="L210" s="12" t="inlineStr">
+        <is>
+          <t>cmn_存在しないURLは404になる</t>
+        </is>
+      </c>
+      <c r="M210" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N210" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O210" s="12" t="inlineStr">
+        <is>
+          <t>佐々木（Claude Code）</t>
+        </is>
+      </c>
+      <c r="P210" s="12" t="inlineStr">
+        <is>
+          <t>自動テスト成功（Issue #17 の修正で追加）</t>
+        </is>
+      </c>
+      <c r="Q210" s="12" t="inlineStr">
+        <is>
+          <t>evidence/IT/IT_API結合_結果一覧_20261009.txt</t>
+        </is>
+      </c>
+      <c r="R210" s="12" t="n"/>
+      <c r="S210" s="12" t="n"/>
+      <c r="T210" s="12" t="n"/>
+    </row>
+    <row r="211" ht="27" customHeight="1">
+      <c r="A211" s="12" t="inlineStr">
+        <is>
+          <t>IT-CMN-E09</t>
+        </is>
+      </c>
+      <c r="B211" s="12" t="inlineStr">
+        <is>
+          <t>認証・リクエスト形式</t>
+        </is>
+      </c>
+      <c r="C211" s="12" t="inlineStr">
+        <is>
+          <t>異常系</t>
+        </is>
+      </c>
+      <c r="D211" s="12" t="inlineStr">
+        <is>
+          <t>対応していないメソッドはリクエスト形式エラー（405）になる</t>
+        </is>
+      </c>
+      <c r="E211" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F211" s="12" t="inlineStr">
+        <is>
+          <t>POST /api/ping（稼働確認はGETだけに対応する）</t>
+        </is>
+      </c>
+      <c r="G211" s="12" t="inlineStr">
+        <is>
+          <t>405「この操作には対応していません」（E-V-029）。500にはならない</t>
+        </is>
+      </c>
+      <c r="H211" s="12" t="inlineStr">
+        <is>
+          <t>-（参照のみ）</t>
+        </is>
+      </c>
+      <c r="I211" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J211" s="12" t="inlineStr">
+        <is>
+          <t>33_共通詳細設計書 3.1</t>
+        </is>
+      </c>
+      <c r="K211" s="12" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="L211" s="12" t="inlineStr">
+        <is>
+          <t>cmn_対応していないメソッドは405になる</t>
+        </is>
+      </c>
+      <c r="M211" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N211" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O211" s="12" t="inlineStr">
+        <is>
+          <t>佐々木（Claude Code）</t>
+        </is>
+      </c>
+      <c r="P211" s="12" t="inlineStr">
+        <is>
+          <t>自動テスト成功（Issue #17 の修正で追加）</t>
+        </is>
+      </c>
+      <c r="Q211" s="12" t="inlineStr">
+        <is>
+          <t>evidence/IT/IT_API結合_結果一覧_20261009.txt</t>
+        </is>
+      </c>
+      <c r="R211" s="12" t="n"/>
+      <c r="S211" s="12" t="n"/>
+      <c r="T211" s="12" t="n"/>
+    </row>
+    <row r="212" ht="27" customHeight="1">
+      <c r="A212" s="12" t="inlineStr">
+        <is>
+          <t>IT-CMN-E10</t>
+        </is>
+      </c>
+      <c r="B212" s="12" t="inlineStr">
+        <is>
+          <t>認証・リクエスト形式</t>
+        </is>
+      </c>
+      <c r="C212" s="12" t="inlineStr">
+        <is>
+          <t>異常系</t>
+        </is>
+      </c>
+      <c r="D212" s="12" t="inlineStr">
+        <is>
+          <t>本文の形式がJSONでないとリクエスト形式エラー（415）になる</t>
+        </is>
+      </c>
+      <c r="E212" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F212" s="12" t="inlineStr">
+        <is>
+          <t>一般ユーザー（ID=1）でPOST /api/favoritesに、Content-Type: text/plainの本文を送る</t>
+        </is>
+      </c>
+      <c r="G212" s="12" t="inlineStr">
+        <is>
+          <t>415「リクエストの形式が不正です」（E-V-030）。500にはならない</t>
+        </is>
+      </c>
+      <c r="H212" s="12" t="inlineStr">
+        <is>
+          <t>favoritesは変更されない</t>
+        </is>
+      </c>
+      <c r="I212" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J212" s="12" t="inlineStr">
+        <is>
+          <t>33_共通詳細設計書 3.1</t>
+        </is>
+      </c>
+      <c r="K212" s="12" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="L212" s="12" t="inlineStr">
+        <is>
+          <t>cmn_JSON以外の形式の本文は415になる</t>
+        </is>
+      </c>
+      <c r="M212" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N212" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O212" s="12" t="inlineStr">
+        <is>
+          <t>佐々木（Claude Code）</t>
+        </is>
+      </c>
+      <c r="P212" s="12" t="inlineStr">
+        <is>
+          <t>自動テスト成功（Issue #17 の修正で追加）</t>
+        </is>
+      </c>
+      <c r="Q212" s="12" t="inlineStr">
+        <is>
+          <t>evidence/IT/IT_API結合_結果一覧_20261009.txt</t>
+        </is>
+      </c>
+      <c r="R212" s="12" t="n"/>
+      <c r="S212" s="12" t="n"/>
+      <c r="T212" s="12" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T209"/>
-  <conditionalFormatting sqref="M2:M209">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
+  <autoFilter ref="A1:T212"/>
+  <conditionalFormatting sqref="M2:M212">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="32">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="33">
       <formula>"NG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="34">
       <formula>"保留"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="35">
       <formula>"対象外"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S209">
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
+  <conditionalFormatting sqref="S2:S212">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="32">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="33">
       <formula>"NG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="34">
       <formula>"保留"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="35">
       <formula>"対象外"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M209" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,保留,対象外"</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S209" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="S2:S212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>
@@ -51216,12 +51480,18 @@
       </c>
       <c r="H2" s="16" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>修正済み（再確認OK）</t>
         </is>
       </c>
       <c r="I2" s="16" t="n"/>
-      <c r="J2" s="16" t="n"/>
-      <c r="K2" s="16" t="n"/>
+      <c r="J2" s="23" t="n">
+        <v>46304</v>
+      </c>
+      <c r="K2" s="16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="n">
@@ -51491,13 +51761,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C3B4A5B-5BD7-4FF5-BACD-086A5CF7B066}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DA9D84E-CC7C-4C1D-912F-87E8362FA891}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49955E09-5CE1-4ED9-A6DC-4D42955CAF81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{905F03B3-EAB7-4040-B1D9-390A08979C5B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58DBCBE2-5112-435B-BBC2-54F5EF9E6FDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07234612-BAB6-4BFD-808F-B16B179D7014}"/>
 </file>
--- a/docs/40_テスト/44_テスト結果表.xlsx
+++ b/docs/40_テスト/44_テスト結果表.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="サマリ" sheetId="1" state="visible" r:id="rId1"/>
@@ -82,7 +82,11 @@
       <u val="single"/>
     </font>
     <font>
-      <color rgb="000563C1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -131,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -170,15 +174,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -188,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="32">
     <dxf>
       <font>
         <i val="1"/>
@@ -554,52 +561,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFD9D9D9"/>
           <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="00595959"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9D9D9"/>
-          <bgColor rgb="00D9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="00FFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FF5050"/>
-          <bgColor rgb="00FF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="00000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFC000"/>
-          <bgColor rgb="00FFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <i val="1"/>
-        <color rgb="00A6A6A6"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F2F2F2"/>
-          <bgColor rgb="00F2F2F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -993,7 +954,7 @@
           <t>テスト開始日</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="20" t="n">
         <v>46302</v>
       </c>
     </row>
@@ -1126,7 +1087,7 @@
         <f>C11-SUM(D11:G11)</f>
         <v/>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="21">
         <f>IF(C11=0,0,(D11+E11+G11)/C11)</f>
         <v/>
       </c>
@@ -1165,7 +1126,7 @@
         <f>C12-SUM(D12:G12)</f>
         <v/>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="21">
         <f>IF(C12=0,0,(D12+E12+G12)/C12)</f>
         <v/>
       </c>
@@ -1204,7 +1165,7 @@
         <f>C13-SUM(D13:G13)</f>
         <v/>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="21">
         <f>IF(C13=0,0,(D13+E13+G13)/C13)</f>
         <v/>
       </c>
@@ -1243,7 +1204,7 @@
         <f>C14-SUM(D14:G14)</f>
         <v/>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="21">
         <f>IF(C14=0,0,(D14+E14+G14)/C14)</f>
         <v/>
       </c>
@@ -1279,7 +1240,7 @@
         <f>SUM(H11:H14)</f>
         <v/>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="22">
         <f>IF(C15=0,0,(D15+E15+G15)/C15)</f>
         <v/>
       </c>
@@ -1558,7 +1519,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N2" s="21" t="n">
+      <c r="N2" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O2" s="12" t="inlineStr">
@@ -1646,7 +1607,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N3" s="21" t="n">
+      <c r="N3" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O3" s="12" t="inlineStr">
@@ -1734,7 +1695,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N4" s="21" t="n">
+      <c r="N4" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O4" s="12" t="inlineStr">
@@ -1822,7 +1783,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N5" s="21" t="n">
+      <c r="N5" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O5" s="12" t="inlineStr">
@@ -1910,7 +1871,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N6" s="21" t="n">
+      <c r="N6" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O6" s="12" t="inlineStr">
@@ -1998,7 +1959,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N7" s="21" t="n">
+      <c r="N7" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O7" s="12" t="inlineStr">
@@ -2086,7 +2047,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N8" s="21" t="n">
+      <c r="N8" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O8" s="12" t="inlineStr">
@@ -2174,7 +2135,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N9" s="21" t="n">
+      <c r="N9" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O9" s="12" t="inlineStr">
@@ -2262,7 +2223,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N10" s="21" t="n">
+      <c r="N10" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O10" s="12" t="inlineStr">
@@ -2350,7 +2311,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N11" s="21" t="n">
+      <c r="N11" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O11" s="12" t="inlineStr">
@@ -2438,7 +2399,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N12" s="21" t="n">
+      <c r="N12" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O12" s="12" t="inlineStr">
@@ -2526,7 +2487,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N13" s="21" t="n">
+      <c r="N13" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O13" s="12" t="inlineStr">
@@ -2614,7 +2575,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N14" s="21" t="n">
+      <c r="N14" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O14" s="12" t="inlineStr">
@@ -2702,7 +2663,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N15" s="21" t="n">
+      <c r="N15" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O15" s="12" t="inlineStr">
@@ -2790,7 +2751,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N16" s="21" t="n">
+      <c r="N16" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O16" s="12" t="inlineStr">
@@ -2878,7 +2839,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N17" s="21" t="n">
+      <c r="N17" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O17" s="12" t="inlineStr">
@@ -2966,7 +2927,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N18" s="21" t="n">
+      <c r="N18" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O18" s="12" t="inlineStr">
@@ -3054,7 +3015,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N19" s="21" t="n">
+      <c r="N19" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O19" s="12" t="inlineStr">
@@ -3142,7 +3103,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N20" s="21" t="n">
+      <c r="N20" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O20" s="12" t="inlineStr">
@@ -3230,7 +3191,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N21" s="21" t="n">
+      <c r="N21" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O21" s="12" t="inlineStr">
@@ -3318,7 +3279,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N22" s="21" t="n">
+      <c r="N22" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O22" s="12" t="inlineStr">
@@ -3406,7 +3367,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N23" s="21" t="n">
+      <c r="N23" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O23" s="12" t="inlineStr">
@@ -3494,7 +3455,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N24" s="21" t="n">
+      <c r="N24" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O24" s="12" t="inlineStr">
@@ -3582,7 +3543,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N25" s="21" t="n">
+      <c r="N25" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O25" s="12" t="inlineStr">
@@ -3670,7 +3631,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N26" s="21" t="n">
+      <c r="N26" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O26" s="12" t="inlineStr">
@@ -3758,7 +3719,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N27" s="21" t="n">
+      <c r="N27" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O27" s="12" t="inlineStr">
@@ -3846,7 +3807,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N28" s="21" t="n">
+      <c r="N28" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O28" s="12" t="inlineStr">
@@ -3934,7 +3895,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N29" s="21" t="n">
+      <c r="N29" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O29" s="12" t="inlineStr">
@@ -4022,7 +3983,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N30" s="21" t="n">
+      <c r="N30" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O30" s="12" t="inlineStr">
@@ -4110,7 +4071,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N31" s="21" t="n">
+      <c r="N31" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O31" s="12" t="inlineStr">
@@ -4198,7 +4159,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N32" s="21" t="n">
+      <c r="N32" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O32" s="12" t="inlineStr">
@@ -4286,7 +4247,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N33" s="21" t="n">
+      <c r="N33" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O33" s="12" t="inlineStr">
@@ -4374,7 +4335,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N34" s="21" t="n">
+      <c r="N34" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O34" s="12" t="inlineStr">
@@ -4462,7 +4423,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N35" s="21" t="n">
+      <c r="N35" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O35" s="12" t="inlineStr">
@@ -4550,7 +4511,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N36" s="21" t="n">
+      <c r="N36" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O36" s="12" t="inlineStr">
@@ -4638,7 +4599,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N37" s="21" t="n">
+      <c r="N37" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O37" s="12" t="inlineStr">
@@ -4726,7 +4687,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N38" s="21" t="n">
+      <c r="N38" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O38" s="12" t="inlineStr">
@@ -4814,7 +4775,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N39" s="21" t="n">
+      <c r="N39" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O39" s="12" t="inlineStr">
@@ -4902,7 +4863,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N40" s="21" t="n">
+      <c r="N40" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O40" s="12" t="inlineStr">
@@ -4990,7 +4951,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N41" s="21" t="n">
+      <c r="N41" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O41" s="12" t="inlineStr">
@@ -5078,7 +5039,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N42" s="21" t="n">
+      <c r="N42" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O42" s="12" t="inlineStr">
@@ -5166,7 +5127,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N43" s="21" t="n">
+      <c r="N43" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O43" s="12" t="inlineStr">
@@ -5254,7 +5215,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N44" s="21" t="n">
+      <c r="N44" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O44" s="12" t="inlineStr">
@@ -5342,7 +5303,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N45" s="21" t="n">
+      <c r="N45" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O45" s="12" t="inlineStr">
@@ -5430,7 +5391,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N46" s="21" t="n">
+      <c r="N46" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O46" s="12" t="inlineStr">
@@ -5518,7 +5479,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N47" s="21" t="n">
+      <c r="N47" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O47" s="12" t="inlineStr">
@@ -5606,7 +5567,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N48" s="21" t="n">
+      <c r="N48" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O48" s="12" t="inlineStr">
@@ -5694,7 +5655,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N49" s="21" t="n">
+      <c r="N49" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O49" s="12" t="inlineStr">
@@ -5782,7 +5743,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N50" s="21" t="n">
+      <c r="N50" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O50" s="12" t="inlineStr">
@@ -5870,7 +5831,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N51" s="21" t="n">
+      <c r="N51" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O51" s="12" t="inlineStr">
@@ -5958,7 +5919,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N52" s="21" t="n">
+      <c r="N52" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O52" s="12" t="inlineStr">
@@ -6046,7 +6007,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N53" s="21" t="n">
+      <c r="N53" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O53" s="12" t="inlineStr">
@@ -6134,7 +6095,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N54" s="21" t="n">
+      <c r="N54" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O54" s="12" t="inlineStr">
@@ -6222,7 +6183,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N55" s="21" t="n">
+      <c r="N55" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O55" s="12" t="inlineStr">
@@ -6310,7 +6271,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N56" s="21" t="n">
+      <c r="N56" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O56" s="12" t="inlineStr">
@@ -6398,7 +6359,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N57" s="21" t="n">
+      <c r="N57" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O57" s="12" t="inlineStr">
@@ -6486,7 +6447,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N58" s="21" t="n">
+      <c r="N58" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O58" s="12" t="inlineStr">
@@ -6574,7 +6535,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N59" s="21" t="n">
+      <c r="N59" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O59" s="12" t="inlineStr">
@@ -6662,7 +6623,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N60" s="21" t="n">
+      <c r="N60" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O60" s="12" t="inlineStr">
@@ -6750,7 +6711,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N61" s="21" t="n">
+      <c r="N61" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O61" s="12" t="inlineStr">
@@ -6838,7 +6799,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N62" s="21" t="n">
+      <c r="N62" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O62" s="12" t="inlineStr">
@@ -6926,7 +6887,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N63" s="21" t="n">
+      <c r="N63" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O63" s="12" t="inlineStr">
@@ -7014,7 +6975,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N64" s="21" t="n">
+      <c r="N64" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O64" s="12" t="inlineStr">
@@ -7102,7 +7063,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N65" s="21" t="n">
+      <c r="N65" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O65" s="12" t="inlineStr">
@@ -7190,7 +7151,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N66" s="21" t="n">
+      <c r="N66" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O66" s="12" t="inlineStr">
@@ -7278,7 +7239,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N67" s="21" t="n">
+      <c r="N67" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O67" s="12" t="inlineStr">
@@ -7366,7 +7327,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N68" s="21" t="n">
+      <c r="N68" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O68" s="12" t="inlineStr">
@@ -7454,7 +7415,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N69" s="21" t="n">
+      <c r="N69" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O69" s="12" t="inlineStr">
@@ -7542,7 +7503,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N70" s="21" t="n">
+      <c r="N70" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O70" s="12" t="inlineStr">
@@ -7630,7 +7591,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N71" s="21" t="n">
+      <c r="N71" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O71" s="12" t="inlineStr">
@@ -7718,7 +7679,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N72" s="21" t="n">
+      <c r="N72" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O72" s="12" t="inlineStr">
@@ -7806,7 +7767,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N73" s="21" t="n">
+      <c r="N73" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O73" s="12" t="inlineStr">
@@ -7894,7 +7855,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N74" s="21" t="n">
+      <c r="N74" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O74" s="12" t="inlineStr">
@@ -7982,7 +7943,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N75" s="21" t="n">
+      <c r="N75" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O75" s="12" t="inlineStr">
@@ -8070,7 +8031,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N76" s="21" t="n">
+      <c r="N76" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O76" s="12" t="inlineStr">
@@ -8158,7 +8119,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N77" s="21" t="n">
+      <c r="N77" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O77" s="12" t="inlineStr">
@@ -8246,7 +8207,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N78" s="21" t="n">
+      <c r="N78" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O78" s="12" t="inlineStr">
@@ -8334,7 +8295,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N79" s="21" t="n">
+      <c r="N79" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O79" s="12" t="inlineStr">
@@ -8422,7 +8383,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N80" s="21" t="n">
+      <c r="N80" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O80" s="12" t="inlineStr">
@@ -8510,7 +8471,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N81" s="21" t="n">
+      <c r="N81" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O81" s="12" t="inlineStr">
@@ -8598,7 +8559,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N82" s="21" t="n">
+      <c r="N82" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O82" s="12" t="inlineStr">
@@ -8686,7 +8647,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N83" s="21" t="n">
+      <c r="N83" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O83" s="12" t="inlineStr">
@@ -8774,7 +8735,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N84" s="21" t="n">
+      <c r="N84" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O84" s="12" t="inlineStr">
@@ -8862,7 +8823,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N85" s="21" t="n">
+      <c r="N85" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O85" s="12" t="inlineStr">
@@ -8950,7 +8911,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N86" s="21" t="n">
+      <c r="N86" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O86" s="12" t="inlineStr">
@@ -9038,7 +8999,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N87" s="21" t="n">
+      <c r="N87" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O87" s="12" t="inlineStr">
@@ -9126,7 +9087,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N88" s="21" t="n">
+      <c r="N88" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O88" s="12" t="inlineStr">
@@ -9214,7 +9175,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N89" s="21" t="n">
+      <c r="N89" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O89" s="12" t="inlineStr">
@@ -9302,7 +9263,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N90" s="21" t="n">
+      <c r="N90" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O90" s="12" t="inlineStr">
@@ -9390,7 +9351,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N91" s="21" t="n">
+      <c r="N91" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O91" s="12" t="inlineStr">
@@ -9478,7 +9439,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N92" s="21" t="n">
+      <c r="N92" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O92" s="12" t="inlineStr">
@@ -9566,7 +9527,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N93" s="21" t="n">
+      <c r="N93" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O93" s="12" t="inlineStr">
@@ -9654,7 +9615,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N94" s="21" t="n">
+      <c r="N94" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O94" s="12" t="inlineStr">
@@ -9742,7 +9703,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N95" s="21" t="n">
+      <c r="N95" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O95" s="12" t="inlineStr">
@@ -9830,7 +9791,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N96" s="21" t="n">
+      <c r="N96" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O96" s="12" t="inlineStr">
@@ -9918,7 +9879,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N97" s="21" t="n">
+      <c r="N97" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O97" s="12" t="inlineStr">
@@ -10006,7 +9967,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N98" s="21" t="n">
+      <c r="N98" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O98" s="12" t="inlineStr">
@@ -10094,7 +10055,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N99" s="21" t="n">
+      <c r="N99" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O99" s="12" t="inlineStr">
@@ -10182,7 +10143,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N100" s="21" t="n">
+      <c r="N100" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O100" s="12" t="inlineStr">
@@ -10270,7 +10231,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N101" s="21" t="n">
+      <c r="N101" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O101" s="12" t="inlineStr">
@@ -10358,7 +10319,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N102" s="21" t="n">
+      <c r="N102" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O102" s="12" t="inlineStr">
@@ -10446,7 +10407,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N103" s="21" t="n">
+      <c r="N103" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O103" s="12" t="inlineStr">
@@ -10534,7 +10495,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N104" s="21" t="n">
+      <c r="N104" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O104" s="12" t="inlineStr">
@@ -10622,7 +10583,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N105" s="21" t="n">
+      <c r="N105" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O105" s="12" t="inlineStr">
@@ -10710,7 +10671,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N106" s="21" t="n">
+      <c r="N106" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O106" s="12" t="inlineStr">
@@ -10798,7 +10759,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N107" s="21" t="n">
+      <c r="N107" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O107" s="12" t="inlineStr">
@@ -10886,7 +10847,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N108" s="21" t="n">
+      <c r="N108" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O108" s="12" t="inlineStr">
@@ -10974,7 +10935,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N109" s="21" t="n">
+      <c r="N109" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O109" s="12" t="inlineStr">
@@ -11062,7 +11023,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N110" s="21" t="n">
+      <c r="N110" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O110" s="12" t="inlineStr">
@@ -11150,7 +11111,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N111" s="21" t="n">
+      <c r="N111" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O111" s="12" t="inlineStr">
@@ -11238,7 +11199,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N112" s="21" t="n">
+      <c r="N112" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O112" s="12" t="inlineStr">
@@ -11326,7 +11287,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N113" s="21" t="n">
+      <c r="N113" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O113" s="12" t="inlineStr">
@@ -11414,7 +11375,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N114" s="21" t="n">
+      <c r="N114" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O114" s="12" t="inlineStr">
@@ -11502,7 +11463,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N115" s="21" t="n">
+      <c r="N115" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O115" s="12" t="inlineStr">
@@ -11590,7 +11551,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N116" s="21" t="n">
+      <c r="N116" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O116" s="12" t="inlineStr">
@@ -11678,7 +11639,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N117" s="21" t="n">
+      <c r="N117" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O117" s="12" t="inlineStr">
@@ -11766,7 +11727,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N118" s="21" t="n">
+      <c r="N118" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O118" s="12" t="inlineStr">
@@ -11854,7 +11815,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N119" s="21" t="n">
+      <c r="N119" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O119" s="12" t="inlineStr">
@@ -11942,7 +11903,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N120" s="21" t="n">
+      <c r="N120" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O120" s="12" t="inlineStr">
@@ -12030,7 +11991,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N121" s="21" t="n">
+      <c r="N121" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O121" s="12" t="inlineStr">
@@ -12118,7 +12079,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N122" s="21" t="n">
+      <c r="N122" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O122" s="12" t="inlineStr">
@@ -12206,7 +12167,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N123" s="21" t="n">
+      <c r="N123" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O123" s="12" t="inlineStr">
@@ -12294,7 +12255,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N124" s="21" t="n">
+      <c r="N124" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O124" s="12" t="inlineStr">
@@ -12382,7 +12343,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N125" s="21" t="n">
+      <c r="N125" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O125" s="12" t="inlineStr">
@@ -12470,7 +12431,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N126" s="21" t="n">
+      <c r="N126" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O126" s="12" t="inlineStr">
@@ -12558,7 +12519,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N127" s="21" t="n">
+      <c r="N127" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O127" s="12" t="inlineStr">
@@ -12646,7 +12607,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N128" s="21" t="n">
+      <c r="N128" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O128" s="12" t="inlineStr">
@@ -12734,7 +12695,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N129" s="21" t="n">
+      <c r="N129" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O129" s="12" t="inlineStr">
@@ -12822,7 +12783,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N130" s="21" t="n">
+      <c r="N130" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O130" s="12" t="inlineStr">
@@ -12910,7 +12871,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N131" s="21" t="n">
+      <c r="N131" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O131" s="12" t="inlineStr">
@@ -12998,7 +12959,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N132" s="21" t="n">
+      <c r="N132" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O132" s="12" t="inlineStr">
@@ -13086,7 +13047,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N133" s="21" t="n">
+      <c r="N133" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O133" s="12" t="inlineStr">
@@ -13174,7 +13135,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N134" s="21" t="n">
+      <c r="N134" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O134" s="12" t="inlineStr">
@@ -13262,7 +13223,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N135" s="21" t="n">
+      <c r="N135" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O135" s="12" t="inlineStr">
@@ -13350,7 +13311,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N136" s="21" t="n">
+      <c r="N136" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O136" s="12" t="inlineStr">
@@ -13438,7 +13399,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N137" s="21" t="n">
+      <c r="N137" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O137" s="12" t="inlineStr">
@@ -13526,7 +13487,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N138" s="21" t="n">
+      <c r="N138" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O138" s="12" t="inlineStr">
@@ -13614,7 +13575,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N139" s="21" t="n">
+      <c r="N139" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O139" s="12" t="inlineStr">
@@ -13702,7 +13663,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N140" s="21" t="n">
+      <c r="N140" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O140" s="12" t="inlineStr">
@@ -13790,7 +13751,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N141" s="21" t="n">
+      <c r="N141" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O141" s="12" t="inlineStr">
@@ -13878,7 +13839,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N142" s="21" t="n">
+      <c r="N142" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O142" s="12" t="inlineStr">
@@ -13966,7 +13927,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N143" s="21" t="n">
+      <c r="N143" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O143" s="12" t="inlineStr">
@@ -14054,7 +14015,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N144" s="21" t="n">
+      <c r="N144" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O144" s="12" t="inlineStr">
@@ -14142,7 +14103,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N145" s="21" t="n">
+      <c r="N145" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O145" s="12" t="inlineStr">
@@ -14230,7 +14191,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N146" s="21" t="n">
+      <c r="N146" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O146" s="12" t="inlineStr">
@@ -14318,7 +14279,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N147" s="21" t="n">
+      <c r="N147" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O147" s="12" t="inlineStr">
@@ -14406,7 +14367,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N148" s="21" t="n">
+      <c r="N148" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O148" s="12" t="inlineStr">
@@ -14494,7 +14455,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N149" s="21" t="n">
+      <c r="N149" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O149" s="12" t="inlineStr">
@@ -14582,7 +14543,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N150" s="21" t="n">
+      <c r="N150" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O150" s="12" t="inlineStr">
@@ -14670,7 +14631,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N151" s="21" t="n">
+      <c r="N151" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O151" s="12" t="inlineStr">
@@ -14758,7 +14719,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N152" s="21" t="n">
+      <c r="N152" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O152" s="12" t="inlineStr">
@@ -14846,7 +14807,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N153" s="21" t="n">
+      <c r="N153" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O153" s="12" t="inlineStr">
@@ -14934,7 +14895,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N154" s="21" t="n">
+      <c r="N154" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O154" s="12" t="inlineStr">
@@ -15022,7 +14983,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N155" s="21" t="n">
+      <c r="N155" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O155" s="12" t="inlineStr">
@@ -15110,7 +15071,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N156" s="21" t="n">
+      <c r="N156" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O156" s="12" t="inlineStr">
@@ -15198,7 +15159,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N157" s="21" t="n">
+      <c r="N157" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O157" s="12" t="inlineStr">
@@ -15286,7 +15247,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N158" s="21" t="n">
+      <c r="N158" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O158" s="12" t="inlineStr">
@@ -15374,7 +15335,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N159" s="21" t="n">
+      <c r="N159" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O159" s="12" t="inlineStr">
@@ -15462,7 +15423,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N160" s="21" t="n">
+      <c r="N160" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O160" s="12" t="inlineStr">
@@ -15550,7 +15511,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N161" s="21" t="n">
+      <c r="N161" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O161" s="12" t="inlineStr">
@@ -15638,7 +15599,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N162" s="21" t="n">
+      <c r="N162" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O162" s="12" t="inlineStr">
@@ -15726,7 +15687,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N163" s="21" t="n">
+      <c r="N163" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O163" s="12" t="inlineStr">
@@ -15814,7 +15775,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N164" s="21" t="n">
+      <c r="N164" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O164" s="12" t="inlineStr">
@@ -15902,7 +15863,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N165" s="21" t="n">
+      <c r="N165" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O165" s="12" t="inlineStr">
@@ -15990,7 +15951,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N166" s="21" t="n">
+      <c r="N166" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O166" s="12" t="inlineStr">
@@ -16078,7 +16039,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N167" s="21" t="n">
+      <c r="N167" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O167" s="12" t="inlineStr">
@@ -16166,7 +16127,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N168" s="21" t="n">
+      <c r="N168" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O168" s="12" t="inlineStr">
@@ -16254,7 +16215,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N169" s="21" t="n">
+      <c r="N169" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O169" s="12" t="inlineStr">
@@ -16342,7 +16303,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N170" s="21" t="n">
+      <c r="N170" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O170" s="12" t="inlineStr">
@@ -16430,7 +16391,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N171" s="21" t="n">
+      <c r="N171" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O171" s="12" t="inlineStr">
@@ -16518,7 +16479,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N172" s="21" t="n">
+      <c r="N172" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O172" s="12" t="inlineStr">
@@ -16606,7 +16567,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N173" s="21" t="n">
+      <c r="N173" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O173" s="12" t="inlineStr">
@@ -16694,7 +16655,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N174" s="21" t="n">
+      <c r="N174" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O174" s="12" t="inlineStr">
@@ -16782,7 +16743,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N175" s="21" t="n">
+      <c r="N175" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O175" s="12" t="inlineStr">
@@ -16870,7 +16831,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N176" s="21" t="n">
+      <c r="N176" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O176" s="12" t="inlineStr">
@@ -16958,7 +16919,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N177" s="21" t="n">
+      <c r="N177" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O177" s="12" t="inlineStr">
@@ -16983,30 +16944,30 @@
   </sheetData>
   <autoFilter ref="A1:T177"/>
   <conditionalFormatting sqref="M2:M177">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="32">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="33">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
       <formula>"NG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="34">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
       <formula>"保留"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="35">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
       <formula>"対象外"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S177">
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="32">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="33">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
       <formula>"NG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="34">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
       <formula>"保留"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="35">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="0">
       <formula>"対象外"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17216,7 +17177,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N2" s="21" t="n">
+      <c r="N2" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O2" s="12" t="inlineStr">
@@ -17297,7 +17258,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N3" s="21" t="n">
+      <c r="N3" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O3" s="12" t="inlineStr">
@@ -17377,7 +17338,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N4" s="21" t="n">
+      <c r="N4" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O4" s="12" t="inlineStr">
@@ -17457,7 +17418,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N5" s="21" t="n">
+      <c r="N5" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O5" s="12" t="inlineStr">
@@ -17537,7 +17498,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N6" s="21" t="n">
+      <c r="N6" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O6" s="12" t="inlineStr">
@@ -17618,7 +17579,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N7" s="21" t="n">
+      <c r="N7" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O7" s="12" t="inlineStr">
@@ -17698,7 +17659,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N8" s="21" t="n">
+      <c r="N8" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O8" s="12" t="inlineStr">
@@ -17778,7 +17739,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N9" s="21" t="n">
+      <c r="N9" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O9" s="12" t="inlineStr">
@@ -17858,7 +17819,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N10" s="21" t="n">
+      <c r="N10" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O10" s="12" t="inlineStr">
@@ -17942,7 +17903,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N11" s="21" t="n">
+      <c r="N11" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O11" s="12" t="inlineStr">
@@ -18027,7 +17988,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N12" s="21" t="n">
+      <c r="N12" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O12" s="12" t="inlineStr">
@@ -18107,7 +18068,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N13" s="21" t="n">
+      <c r="N13" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O13" s="12" t="inlineStr">
@@ -18188,7 +18149,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N14" s="21" t="n">
+      <c r="N14" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O14" s="12" t="inlineStr">
@@ -18272,7 +18233,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N15" s="21" t="n">
+      <c r="N15" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O15" s="12" t="inlineStr">
@@ -18360,7 +18321,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N16" s="21" t="n">
+      <c r="N16" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O16" s="12" t="inlineStr">
@@ -18444,7 +18405,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N17" s="21" t="n">
+      <c r="N17" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O17" s="12" t="inlineStr">
@@ -18528,7 +18489,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N18" s="21" t="n">
+      <c r="N18" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O18" s="12" t="inlineStr">
@@ -18616,7 +18577,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N19" s="21" t="n">
+      <c r="N19" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O19" s="12" t="inlineStr">
@@ -18704,7 +18665,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N20" s="21" t="n">
+      <c r="N20" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O20" s="12" t="inlineStr">
@@ -18788,7 +18749,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N21" s="21" t="n">
+      <c r="N21" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O21" s="12" t="inlineStr">
@@ -18868,7 +18829,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N22" s="21" t="n">
+      <c r="N22" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O22" s="12" t="inlineStr">
@@ -18952,7 +18913,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N23" s="21" t="n">
+      <c r="N23" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O23" s="12" t="inlineStr">
@@ -19040,7 +19001,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N24" s="21" t="n">
+      <c r="N24" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O24" s="12" t="inlineStr">
@@ -19128,7 +19089,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N25" s="21" t="n">
+      <c r="N25" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O25" s="12" t="inlineStr">
@@ -19213,7 +19174,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N26" s="21" t="n">
+      <c r="N26" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O26" s="12" t="inlineStr">
@@ -19294,7 +19255,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N27" s="21" t="n">
+      <c r="N27" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O27" s="12" t="inlineStr">
@@ -19375,7 +19336,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N28" s="21" t="n">
+      <c r="N28" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O28" s="12" t="inlineStr">
@@ -19456,7 +19417,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N29" s="21" t="n">
+      <c r="N29" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O29" s="12" t="inlineStr">
@@ -19540,7 +19501,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N30" s="21" t="n">
+      <c r="N30" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O30" s="12" t="inlineStr">
@@ -19625,7 +19586,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N31" s="21" t="n">
+      <c r="N31" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O31" s="12" t="inlineStr">
@@ -19706,7 +19667,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N32" s="21" t="n">
+      <c r="N32" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O32" s="12" t="inlineStr">
@@ -19790,7 +19751,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N33" s="21" t="n">
+      <c r="N33" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O33" s="12" t="inlineStr">
@@ -19878,7 +19839,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N34" s="21" t="n">
+      <c r="N34" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O34" s="12" t="inlineStr">
@@ -19966,7 +19927,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N35" s="21" t="n">
+      <c r="N35" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O35" s="12" t="inlineStr">
@@ -20051,7 +20012,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N36" s="21" t="n">
+      <c r="N36" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O36" s="12" t="inlineStr">
@@ -20132,7 +20093,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N37" s="21" t="n">
+      <c r="N37" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O37" s="12" t="inlineStr">
@@ -20216,7 +20177,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N38" s="21" t="n">
+      <c r="N38" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O38" s="12" t="inlineStr">
@@ -20304,7 +20265,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N39" s="21" t="n">
+      <c r="N39" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O39" s="12" t="inlineStr">
@@ -20392,7 +20353,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N40" s="21" t="n">
+      <c r="N40" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O40" s="12" t="inlineStr">
@@ -20480,7 +20441,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N41" s="21" t="n">
+      <c r="N41" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O41" s="12" t="inlineStr">
@@ -20565,7 +20526,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N42" s="21" t="n">
+      <c r="N42" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O42" s="12" t="inlineStr">
@@ -20646,7 +20607,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N43" s="21" t="n">
+      <c r="N43" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O43" s="12" t="inlineStr">
@@ -20730,7 +20691,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N44" s="21" t="n">
+      <c r="N44" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O44" s="12" t="inlineStr">
@@ -20818,7 +20779,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N45" s="21" t="n">
+      <c r="N45" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O45" s="12" t="inlineStr">
@@ -20906,7 +20867,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N46" s="21" t="n">
+      <c r="N46" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O46" s="12" t="inlineStr">
@@ -20991,7 +20952,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N47" s="21" t="n">
+      <c r="N47" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O47" s="12" t="inlineStr">
@@ -21075,7 +21036,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N48" s="21" t="n">
+      <c r="N48" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O48" s="12" t="inlineStr">
@@ -21163,7 +21124,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N49" s="21" t="n">
+      <c r="N49" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O49" s="12" t="inlineStr">
@@ -21251,7 +21212,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N50" s="21" t="n">
+      <c r="N50" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O50" s="12" t="inlineStr">
@@ -21339,7 +21300,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N51" s="21" t="n">
+      <c r="N51" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O51" s="12" t="inlineStr">
@@ -21427,7 +21388,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N52" s="21" t="n">
+      <c r="N52" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O52" s="12" t="inlineStr">
@@ -21511,7 +21472,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N53" s="21" t="n">
+      <c r="N53" s="23" t="n">
         <v>46303</v>
       </c>
       <c r="O53" s="12" t="inlineStr">
@@ -21595,7 +21556,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N54" s="21" t="n">
+      <c r="N54" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O54" s="12" t="inlineStr">
@@ -21683,7 +21644,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N55" s="21" t="n">
+      <c r="N55" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O55" s="12" t="inlineStr">
@@ -21767,7 +21728,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N56" s="21" t="n">
+      <c r="N56" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O56" s="12" t="inlineStr">
@@ -21847,7 +21808,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N57" s="21" t="n">
+      <c r="N57" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O57" s="12" t="inlineStr">
@@ -21927,7 +21888,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N58" s="21" t="n">
+      <c r="N58" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O58" s="12" t="inlineStr">
@@ -22011,7 +21972,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N59" s="21" t="n">
+      <c r="N59" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O59" s="12" t="inlineStr">
@@ -22095,7 +22056,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N60" s="21" t="n">
+      <c r="N60" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O60" s="12" t="inlineStr">
@@ -22175,7 +22136,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N61" s="21" t="n">
+      <c r="N61" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O61" s="12" t="inlineStr">
@@ -22255,7 +22216,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N62" s="21" t="n">
+      <c r="N62" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O62" s="12" t="inlineStr">
@@ -22339,7 +22300,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N63" s="21" t="n">
+      <c r="N63" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O63" s="12" t="inlineStr">
@@ -22427,7 +22388,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N64" s="21" t="n">
+      <c r="N64" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O64" s="12" t="inlineStr">
@@ -22512,7 +22473,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N65" s="21" t="n">
+      <c r="N65" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O65" s="12" t="inlineStr">
@@ -22593,7 +22554,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N66" s="21" t="n">
+      <c r="N66" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O66" s="12" t="inlineStr">
@@ -22674,7 +22635,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N67" s="21" t="n">
+      <c r="N67" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O67" s="12" t="inlineStr">
@@ -22755,7 +22716,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N68" s="21" t="n">
+      <c r="N68" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O68" s="12" t="inlineStr">
@@ -22836,7 +22797,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N69" s="21" t="n">
+      <c r="N69" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O69" s="12" t="inlineStr">
@@ -22917,7 +22878,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N70" s="21" t="n">
+      <c r="N70" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O70" s="12" t="inlineStr">
@@ -22998,7 +22959,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N71" s="21" t="n">
+      <c r="N71" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O71" s="12" t="inlineStr">
@@ -23079,7 +23040,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N72" s="21" t="n">
+      <c r="N72" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O72" s="12" t="inlineStr">
@@ -23160,7 +23121,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N73" s="21" t="n">
+      <c r="N73" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O73" s="12" t="inlineStr">
@@ -23241,7 +23202,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N74" s="21" t="n">
+      <c r="N74" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O74" s="12" t="inlineStr">
@@ -23322,7 +23283,7 @@
           <t>NG</t>
         </is>
       </c>
-      <c r="N75" s="21" t="n">
+      <c r="N75" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O75" s="12" t="inlineStr">
@@ -23341,7 +23302,7 @@
           <t>45_テストエビデンス_API結合.xlsx／AP-030</t>
         </is>
       </c>
-      <c r="R75" s="22" t="inlineStr">
+      <c r="R75" s="18" t="inlineStr">
         <is>
           <t>#18</t>
         </is>
@@ -23351,7 +23312,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="T75" s="21" t="n">
+      <c r="T75" s="23" t="n">
         <v>46304</v>
       </c>
     </row>
@@ -23418,7 +23379,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N76" s="21" t="n">
+      <c r="N76" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O76" s="12" t="inlineStr">
@@ -23499,7 +23460,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N77" s="21" t="n">
+      <c r="N77" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O77" s="12" t="inlineStr">
@@ -23580,7 +23541,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N78" s="21" t="n">
+      <c r="N78" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O78" s="12" t="inlineStr">
@@ -23664,7 +23625,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N79" s="21" t="n">
+      <c r="N79" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O79" s="12" t="inlineStr">
@@ -23748,7 +23709,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N80" s="21" t="n">
+      <c r="N80" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O80" s="12" t="inlineStr">
@@ -23828,7 +23789,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N81" s="21" t="n">
+      <c r="N81" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O81" s="12" t="inlineStr">
@@ -23912,7 +23873,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N82" s="21" t="n">
+      <c r="N82" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O82" s="12" t="inlineStr">
@@ -23997,7 +23958,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N83" s="21" t="n">
+      <c r="N83" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O83" s="12" t="inlineStr">
@@ -24078,7 +24039,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N84" s="21" t="n">
+      <c r="N84" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O84" s="12" t="inlineStr">
@@ -24159,7 +24120,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N85" s="21" t="n">
+      <c r="N85" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O85" s="12" t="inlineStr">
@@ -24240,7 +24201,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N86" s="21" t="n">
+      <c r="N86" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O86" s="12" t="inlineStr">
@@ -24321,7 +24282,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N87" s="21" t="n">
+      <c r="N87" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O87" s="12" t="inlineStr">
@@ -24402,7 +24363,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N88" s="21" t="n">
+      <c r="N88" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O88" s="12" t="inlineStr">
@@ -24483,7 +24444,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N89" s="21" t="n">
+      <c r="N89" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O89" s="12" t="inlineStr">
@@ -24564,7 +24525,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N90" s="21" t="n">
+      <c r="N90" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O90" s="12" t="inlineStr">
@@ -24645,7 +24606,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N91" s="21" t="n">
+      <c r="N91" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O91" s="12" t="inlineStr">
@@ -24726,7 +24687,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N92" s="21" t="n">
+      <c r="N92" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O92" s="12" t="inlineStr">
@@ -24807,7 +24768,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N93" s="21" t="n">
+      <c r="N93" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O93" s="12" t="inlineStr">
@@ -24888,7 +24849,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N94" s="21" t="n">
+      <c r="N94" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O94" s="12" t="inlineStr">
@@ -24969,7 +24930,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N95" s="21" t="n">
+      <c r="N95" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O95" s="12" t="inlineStr">
@@ -25049,7 +25010,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N96" s="21" t="n">
+      <c r="N96" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O96" s="12" t="inlineStr">
@@ -25129,7 +25090,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N97" s="21" t="n">
+      <c r="N97" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O97" s="12" t="inlineStr">
@@ -25209,7 +25170,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N98" s="21" t="n">
+      <c r="N98" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O98" s="12" t="inlineStr">
@@ -25289,7 +25250,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N99" s="21" t="n">
+      <c r="N99" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O99" s="12" t="inlineStr">
@@ -25369,7 +25330,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N100" s="21" t="n">
+      <c r="N100" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O100" s="12" t="inlineStr">
@@ -25449,7 +25410,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N101" s="21" t="n">
+      <c r="N101" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O101" s="12" t="inlineStr">
@@ -25529,7 +25490,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N102" s="21" t="n">
+      <c r="N102" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O102" s="12" t="inlineStr">
@@ -25609,7 +25570,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N103" s="21" t="n">
+      <c r="N103" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O103" s="12" t="inlineStr">
@@ -25690,7 +25651,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N104" s="21" t="n">
+      <c r="N104" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O104" s="12" t="inlineStr">
@@ -25771,7 +25732,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N105" s="21" t="n">
+      <c r="N105" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O105" s="12" t="inlineStr">
@@ -25852,7 +25813,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N106" s="21" t="n">
+      <c r="N106" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O106" s="12" t="inlineStr">
@@ -25933,7 +25894,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N107" s="21" t="n">
+      <c r="N107" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O107" s="12" t="inlineStr">
@@ -26014,7 +25975,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N108" s="21" t="n">
+      <c r="N108" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O108" s="12" t="inlineStr">
@@ -26095,7 +26056,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N109" s="21" t="n">
+      <c r="N109" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O109" s="12" t="inlineStr">
@@ -26176,7 +26137,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N110" s="21" t="n">
+      <c r="N110" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O110" s="12" t="inlineStr">
@@ -26257,7 +26218,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N111" s="21" t="n">
+      <c r="N111" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O111" s="12" t="inlineStr">
@@ -26338,7 +26299,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N112" s="21" t="n">
+      <c r="N112" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O112" s="12" t="inlineStr">
@@ -26419,7 +26380,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N113" s="21" t="n">
+      <c r="N113" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O113" s="12" t="inlineStr">
@@ -26500,7 +26461,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N114" s="21" t="n">
+      <c r="N114" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O114" s="12" t="inlineStr">
@@ -26581,7 +26542,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N115" s="21" t="n">
+      <c r="N115" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O115" s="12" t="inlineStr">
@@ -26662,7 +26623,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N116" s="21" t="n">
+      <c r="N116" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O116" s="12" t="inlineStr">
@@ -26743,7 +26704,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N117" s="21" t="n">
+      <c r="N117" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O117" s="12" t="inlineStr">
@@ -26824,7 +26785,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N118" s="21" t="n">
+      <c r="N118" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O118" s="12" t="inlineStr">
@@ -26908,7 +26869,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N119" s="21" t="n">
+      <c r="N119" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O119" s="12" t="inlineStr">
@@ -26996,7 +26957,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N120" s="21" t="n">
+      <c r="N120" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O120" s="12" t="inlineStr">
@@ -27084,7 +27045,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N121" s="21" t="n">
+      <c r="N121" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O121" s="12" t="inlineStr">
@@ -27169,7 +27130,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N122" s="21" t="n">
+      <c r="N122" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O122" s="12" t="inlineStr">
@@ -27250,7 +27211,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N123" s="21" t="n">
+      <c r="N123" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O123" s="12" t="inlineStr">
@@ -27334,7 +27295,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N124" s="21" t="n">
+      <c r="N124" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O124" s="12" t="inlineStr">
@@ -27422,7 +27383,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N125" s="21" t="n">
+      <c r="N125" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O125" s="12" t="inlineStr">
@@ -27507,7 +27468,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N126" s="21" t="n">
+      <c r="N126" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O126" s="12" t="inlineStr">
@@ -27588,7 +27549,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N127" s="21" t="n">
+      <c r="N127" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O127" s="12" t="inlineStr">
@@ -27669,7 +27630,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N128" s="21" t="n">
+      <c r="N128" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O128" s="12" t="inlineStr">
@@ -27753,7 +27714,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N129" s="21" t="n">
+      <c r="N129" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O129" s="12" t="inlineStr">
@@ -27838,7 +27799,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N130" s="21" t="n">
+      <c r="N130" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O130" s="12" t="inlineStr">
@@ -27919,7 +27880,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N131" s="21" t="n">
+      <c r="N131" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O131" s="12" t="inlineStr">
@@ -28000,7 +27961,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N132" s="21" t="n">
+      <c r="N132" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O132" s="12" t="inlineStr">
@@ -28082,7 +28043,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N133" s="21" t="n">
+      <c r="N133" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O133" s="12" t="inlineStr">
@@ -28164,7 +28125,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N134" s="21" t="n">
+      <c r="N134" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O134" s="12" t="inlineStr">
@@ -28246,7 +28207,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N135" s="21" t="n">
+      <c r="N135" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O135" s="12" t="inlineStr">
@@ -28330,7 +28291,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N136" s="21" t="n">
+      <c r="N136" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O136" s="12" t="inlineStr">
@@ -28418,7 +28379,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N137" s="21" t="n">
+      <c r="N137" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O137" s="12" t="inlineStr">
@@ -28503,7 +28464,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N138" s="21" t="n">
+      <c r="N138" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O138" s="12" t="inlineStr">
@@ -28585,7 +28546,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N139" s="21" t="n">
+      <c r="N139" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O139" s="12" t="inlineStr">
@@ -28667,7 +28628,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N140" s="21" t="n">
+      <c r="N140" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O140" s="12" t="inlineStr">
@@ -28748,7 +28709,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N141" s="21" t="n">
+      <c r="N141" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O141" s="12" t="inlineStr">
@@ -28832,7 +28793,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N142" s="21" t="n">
+      <c r="N142" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O142" s="12" t="inlineStr">
@@ -28918,7 +28879,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N143" s="21" t="n">
+      <c r="N143" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O143" s="12" t="inlineStr">
@@ -28999,7 +28960,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N144" s="21" t="n">
+      <c r="N144" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O144" s="12" t="inlineStr">
@@ -29081,7 +29042,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N145" s="21" t="n">
+      <c r="N145" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O145" s="12" t="inlineStr">
@@ -29161,7 +29122,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N146" s="21" t="n">
+      <c r="N146" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O146" s="12" t="inlineStr">
@@ -29242,7 +29203,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N147" s="21" t="n">
+      <c r="N147" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O147" s="12" t="inlineStr">
@@ -29323,7 +29284,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N148" s="21" t="n">
+      <c r="N148" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O148" s="12" t="inlineStr">
@@ -29404,7 +29365,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N149" s="21" t="n">
+      <c r="N149" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O149" s="12" t="inlineStr">
@@ -29485,7 +29446,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N150" s="21" t="n">
+      <c r="N150" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O150" s="12" t="inlineStr">
@@ -29565,7 +29526,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N151" s="21" t="n">
+      <c r="N151" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O151" s="12" t="inlineStr">
@@ -29645,7 +29606,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N152" s="21" t="n">
+      <c r="N152" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O152" s="12" t="inlineStr">
@@ -29725,7 +29686,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N153" s="21" t="n">
+      <c r="N153" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O153" s="12" t="inlineStr">
@@ -29806,7 +29767,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N154" s="21" t="n">
+      <c r="N154" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O154" s="12" t="inlineStr">
@@ -29887,7 +29848,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N155" s="21" t="n">
+      <c r="N155" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O155" s="12" t="inlineStr">
@@ -29968,7 +29929,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N156" s="21" t="n">
+      <c r="N156" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O156" s="12" t="inlineStr">
@@ -30049,7 +30010,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N157" s="21" t="n">
+      <c r="N157" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O157" s="12" t="inlineStr">
@@ -30129,7 +30090,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N158" s="21" t="n">
+      <c r="N158" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O158" s="12" t="inlineStr">
@@ -30209,7 +30170,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N159" s="21" t="n">
+      <c r="N159" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O159" s="12" t="inlineStr">
@@ -30289,7 +30250,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N160" s="21" t="n">
+      <c r="N160" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O160" s="12" t="inlineStr">
@@ -30369,7 +30330,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N161" s="21" t="n">
+      <c r="N161" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O161" s="12" t="inlineStr">
@@ -30449,7 +30410,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N162" s="21" t="n">
+      <c r="N162" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O162" s="12" t="inlineStr">
@@ -30530,7 +30491,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N163" s="21" t="n">
+      <c r="N163" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O163" s="12" t="inlineStr">
@@ -30611,7 +30572,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N164" s="21" t="n">
+      <c r="N164" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O164" s="12" t="inlineStr">
@@ -30692,7 +30653,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N165" s="21" t="n">
+      <c r="N165" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O165" s="12" t="inlineStr">
@@ -30773,7 +30734,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N166" s="21" t="n">
+      <c r="N166" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O166" s="12" t="inlineStr">
@@ -30854,7 +30815,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N167" s="21" t="n">
+      <c r="N167" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O167" s="12" t="inlineStr">
@@ -30935,7 +30896,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N168" s="21" t="n">
+      <c r="N168" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O168" s="12" t="inlineStr">
@@ -31015,7 +30976,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N169" s="21" t="n">
+      <c r="N169" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O169" s="12" t="inlineStr">
@@ -31095,7 +31056,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N170" s="21" t="n">
+      <c r="N170" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O170" s="12" t="inlineStr">
@@ -31175,7 +31136,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N171" s="21" t="n">
+      <c r="N171" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O171" s="12" t="inlineStr">
@@ -31255,7 +31216,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N172" s="21" t="n">
+      <c r="N172" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O172" s="12" t="inlineStr">
@@ -31335,7 +31296,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N173" s="21" t="n">
+      <c r="N173" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O173" s="12" t="inlineStr">
@@ -31419,7 +31380,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N174" s="21" t="n">
+      <c r="N174" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O174" s="12" t="inlineStr">
@@ -31507,7 +31468,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N175" s="21" t="n">
+      <c r="N175" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O175" s="12" t="inlineStr">
@@ -31595,7 +31556,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N176" s="21" t="n">
+      <c r="N176" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O176" s="12" t="inlineStr">
@@ -31679,7 +31640,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N177" s="21" t="n">
+      <c r="N177" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O177" s="12" t="inlineStr">
@@ -31763,7 +31724,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N178" s="21" t="n">
+      <c r="N178" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O178" s="12" t="inlineStr">
@@ -31851,7 +31812,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N179" s="21" t="n">
+      <c r="N179" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O179" s="12" t="inlineStr">
@@ -31939,7 +31900,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N180" s="21" t="n">
+      <c r="N180" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O180" s="12" t="inlineStr">
@@ -32023,7 +31984,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N181" s="21" t="n">
+      <c r="N181" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O181" s="12" t="inlineStr">
@@ -32103,7 +32064,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N182" s="21" t="n">
+      <c r="N182" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O182" s="12" t="inlineStr">
@@ -32183,7 +32144,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N183" s="21" t="n">
+      <c r="N183" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O183" s="12" t="inlineStr">
@@ -32263,7 +32224,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N184" s="21" t="n">
+      <c r="N184" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O184" s="12" t="inlineStr">
@@ -32347,7 +32308,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N185" s="21" t="n">
+      <c r="N185" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O185" s="12" t="inlineStr">
@@ -32435,7 +32396,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N186" s="21" t="n">
+      <c r="N186" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O186" s="12" t="inlineStr">
@@ -32523,7 +32484,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N187" s="21" t="n">
+      <c r="N187" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O187" s="12" t="inlineStr">
@@ -32611,7 +32572,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N188" s="21" t="n">
+      <c r="N188" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O188" s="12" t="inlineStr">
@@ -32695,7 +32656,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N189" s="21" t="n">
+      <c r="N189" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O189" s="12" t="inlineStr">
@@ -32775,7 +32736,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N190" s="21" t="n">
+      <c r="N190" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O190" s="12" t="inlineStr">
@@ -32859,7 +32820,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N191" s="21" t="n">
+      <c r="N191" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O191" s="12" t="inlineStr">
@@ -32943,7 +32904,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N192" s="21" t="n">
+      <c r="N192" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O192" s="12" t="inlineStr">
@@ -33023,7 +32984,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N193" s="21" t="n">
+      <c r="N193" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O193" s="12" t="inlineStr">
@@ -33107,7 +33068,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N194" s="21" t="n">
+      <c r="N194" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O194" s="12" t="inlineStr">
@@ -33191,7 +33152,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N195" s="21" t="n">
+      <c r="N195" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O195" s="12" t="inlineStr">
@@ -33271,7 +33232,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N196" s="21" t="n">
+      <c r="N196" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O196" s="12" t="inlineStr">
@@ -33355,7 +33316,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N197" s="21" t="n">
+      <c r="N197" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O197" s="12" t="inlineStr">
@@ -33443,7 +33404,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N198" s="21" t="n">
+      <c r="N198" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O198" s="12" t="inlineStr">
@@ -33531,7 +33492,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N199" s="21" t="n">
+      <c r="N199" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O199" s="12" t="inlineStr">
@@ -33616,7 +33577,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N200" s="21" t="n">
+      <c r="N200" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O200" s="12" t="inlineStr">
@@ -33697,7 +33658,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N201" s="21" t="n">
+      <c r="N201" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O201" s="12" t="inlineStr">
@@ -33781,7 +33742,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N202" s="21" t="n">
+      <c r="N202" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O202" s="12" t="inlineStr">
@@ -33869,7 +33830,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N203" s="21" t="n">
+      <c r="N203" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O203" s="12" t="inlineStr">
@@ -33957,7 +33918,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N204" s="21" t="n">
+      <c r="N204" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O204" s="12" t="inlineStr">
@@ -34045,7 +34006,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N205" s="21" t="n">
+      <c r="N205" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O205" s="12" t="inlineStr">
@@ -34133,7 +34094,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N206" s="21" t="n">
+      <c r="N206" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O206" s="12" t="inlineStr">
@@ -34221,7 +34182,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N207" s="21" t="n">
+      <c r="N207" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O207" s="12" t="inlineStr">
@@ -34305,7 +34266,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N208" s="21" t="n">
+      <c r="N208" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O208" s="12" t="inlineStr">
@@ -34385,7 +34346,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N209" s="21" t="n">
+      <c r="N209" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O209" s="12" t="inlineStr">
@@ -34469,7 +34430,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N210" s="21" t="n">
+      <c r="N210" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O210" s="12" t="inlineStr">
@@ -34557,7 +34518,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N211" s="21" t="n">
+      <c r="N211" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O211" s="12" t="inlineStr">
@@ -34645,7 +34606,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N212" s="21" t="n">
+      <c r="N212" s="23" t="n">
         <v>46304</v>
       </c>
       <c r="O212" s="12" t="inlineStr">
@@ -34670,30 +34631,30 @@
   </sheetData>
   <autoFilter ref="A1:T212"/>
   <conditionalFormatting sqref="M2:M212">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="32">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="33">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
       <formula>"NG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="34">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
       <formula>"保留"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="35">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
       <formula>"対象外"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S212">
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="32">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="33">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
       <formula>"NG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="34">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
       <formula>"保留"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="35">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="0">
       <formula>"対象外"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35047,9 +35008,19 @@
         </is>
       </c>
       <c r="L2" s="12" t="n"/>
-      <c r="M2" s="12" t="n"/>
-      <c r="N2" s="12" t="n"/>
-      <c r="O2" s="12" t="n"/>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N2" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O2" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P2" s="12" t="n"/>
       <c r="Q2" s="15" t="inlineStr">
         <is>
@@ -35117,9 +35088,19 @@
         </is>
       </c>
       <c r="L3" s="12" t="n"/>
-      <c r="M3" s="12" t="n"/>
-      <c r="N3" s="12" t="n"/>
-      <c r="O3" s="12" t="n"/>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N3" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P3" s="12" t="n"/>
       <c r="Q3" s="15" t="inlineStr">
         <is>
@@ -35187,9 +35168,19 @@
         </is>
       </c>
       <c r="L4" s="12" t="n"/>
-      <c r="M4" s="12" t="n"/>
-      <c r="N4" s="12" t="n"/>
-      <c r="O4" s="12" t="n"/>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N4" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P4" s="12" t="n"/>
       <c r="Q4" s="15" t="inlineStr">
         <is>
@@ -35257,9 +35248,19 @@
         </is>
       </c>
       <c r="L5" s="12" t="n"/>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="12" t="n"/>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N5" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P5" s="12" t="n"/>
       <c r="Q5" s="15" t="inlineStr">
         <is>
@@ -35327,9 +35328,19 @@
         </is>
       </c>
       <c r="L6" s="12" t="n"/>
-      <c r="M6" s="12" t="n"/>
-      <c r="N6" s="12" t="n"/>
-      <c r="O6" s="12" t="n"/>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N6" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P6" s="12" t="n"/>
       <c r="Q6" s="15" t="inlineStr">
         <is>
@@ -35397,9 +35408,19 @@
         </is>
       </c>
       <c r="L7" s="12" t="n"/>
-      <c r="M7" s="12" t="n"/>
-      <c r="N7" s="12" t="n"/>
-      <c r="O7" s="12" t="n"/>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N7" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P7" s="12" t="n"/>
       <c r="Q7" s="15" t="inlineStr">
         <is>
@@ -35467,9 +35488,19 @@
         </is>
       </c>
       <c r="L8" s="12" t="n"/>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="12" t="n"/>
-      <c r="O8" s="12" t="n"/>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N8" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P8" s="12" t="n"/>
       <c r="Q8" s="15" t="inlineStr">
         <is>
@@ -35537,9 +35568,19 @@
         </is>
       </c>
       <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="12" t="n"/>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N9" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P9" s="12" t="n"/>
       <c r="Q9" s="15" t="inlineStr">
         <is>
@@ -35607,9 +35648,19 @@
         </is>
       </c>
       <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="12" t="n"/>
-      <c r="O10" s="12" t="n"/>
+      <c r="M10" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N10" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P10" s="12" t="n"/>
       <c r="Q10" s="15" t="inlineStr">
         <is>
@@ -35677,9 +35728,19 @@
         </is>
       </c>
       <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="12" t="n"/>
-      <c r="O11" s="12" t="n"/>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N11" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P11" s="12" t="n"/>
       <c r="Q11" s="15" t="inlineStr">
         <is>
@@ -35747,9 +35808,19 @@
         </is>
       </c>
       <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="12" t="n"/>
-      <c r="O12" s="12" t="n"/>
+      <c r="M12" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N12" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P12" s="12" t="n"/>
       <c r="Q12" s="15" t="inlineStr">
         <is>
@@ -35818,9 +35889,19 @@
         </is>
       </c>
       <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
-      <c r="N13" s="12" t="n"/>
-      <c r="O13" s="12" t="n"/>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N13" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P13" s="12" t="n"/>
       <c r="Q13" s="15" t="inlineStr">
         <is>
@@ -35888,9 +35969,19 @@
         </is>
       </c>
       <c r="L14" s="12" t="n"/>
-      <c r="M14" s="12" t="n"/>
-      <c r="N14" s="12" t="n"/>
-      <c r="O14" s="12" t="n"/>
+      <c r="M14" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N14" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P14" s="12" t="n"/>
       <c r="Q14" s="15" t="inlineStr">
         <is>
@@ -35958,9 +36049,19 @@
         </is>
       </c>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
-      <c r="N15" s="12" t="n"/>
-      <c r="O15" s="12" t="n"/>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N15" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P15" s="12" t="n"/>
       <c r="Q15" s="15" t="inlineStr">
         <is>
@@ -36028,9 +36129,19 @@
         </is>
       </c>
       <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="12" t="n"/>
-      <c r="O16" s="12" t="n"/>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N16" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P16" s="12" t="n"/>
       <c r="Q16" s="15" t="inlineStr">
         <is>
@@ -36098,9 +36209,19 @@
         </is>
       </c>
       <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
-      <c r="N17" s="12" t="n"/>
-      <c r="O17" s="12" t="n"/>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N17" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P17" s="12" t="n"/>
       <c r="Q17" s="15" t="inlineStr">
         <is>
@@ -36169,9 +36290,19 @@
         </is>
       </c>
       <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="12" t="n"/>
-      <c r="O18" s="12" t="n"/>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N18" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P18" s="12" t="n"/>
       <c r="Q18" s="15" t="inlineStr">
         <is>
@@ -36240,9 +36371,19 @@
         </is>
       </c>
       <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
-      <c r="N19" s="12" t="n"/>
-      <c r="O19" s="12" t="n"/>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N19" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P19" s="12" t="n"/>
       <c r="Q19" s="15" t="inlineStr">
         <is>
@@ -49739,7 +49880,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="N74" s="21" t="n">
+      <c r="N74" s="23" t="n">
         <v>46302</v>
       </c>
       <c r="O74" s="12" t="inlineStr">
@@ -51484,7 +51625,7 @@
         </is>
       </c>
       <c r="I2" s="16" t="n"/>
-      <c r="J2" s="23" t="n">
+      <c r="J2" s="24" t="n">
         <v>46304</v>
       </c>
       <c r="K2" s="16" t="inlineStr">
@@ -51493,7 +51634,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="39" customHeight="1">
       <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
@@ -51522,7 +51663,7 @@
           <t>201。ticketTypeIdがnullの申込として登録される</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>#18</t>
         </is>
@@ -51533,7 +51674,7 @@
         </is>
       </c>
       <c r="I3" s="16" t="n"/>
-      <c r="J3" s="23" t="n">
+      <c r="J3" s="24" t="n">
         <v>46304</v>
       </c>
       <c r="K3" s="16" t="inlineStr">
@@ -51761,13 +51902,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DA9D84E-CC7C-4C1D-912F-87E8362FA891}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5CECB6A-F27A-4032-87E4-CC6D5CF3505A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{905F03B3-EAB7-4040-B1D9-390A08979C5B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2F084F3-302E-4CBC-927B-CB4887B418DE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07234612-BAB6-4BFD-808F-B16B179D7014}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{300BB5C6-51F8-48CE-8ECB-8F6750A848FD}"/>
 </file>
--- a/docs/40_テスト/44_テスト結果表.xlsx
+++ b/docs/40_テスト/44_テスト結果表.xlsx
@@ -36452,9 +36452,19 @@
         </is>
       </c>
       <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
-      <c r="N20" s="12" t="n"/>
-      <c r="O20" s="12" t="n"/>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N20" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P20" s="12" t="n"/>
       <c r="Q20" s="15" t="inlineStr">
         <is>
@@ -36522,9 +36532,19 @@
         </is>
       </c>
       <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="12" t="n"/>
-      <c r="O21" s="12" t="n"/>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N21" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P21" s="12" t="n"/>
       <c r="Q21" s="15" t="inlineStr">
         <is>
@@ -36592,9 +36612,19 @@
         </is>
       </c>
       <c r="L22" s="12" t="n"/>
-      <c r="M22" s="12" t="n"/>
-      <c r="N22" s="12" t="n"/>
-      <c r="O22" s="12" t="n"/>
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N22" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P22" s="12" t="n"/>
       <c r="Q22" s="15" t="inlineStr">
         <is>
@@ -36663,9 +36693,19 @@
         </is>
       </c>
       <c r="L23" s="12" t="n"/>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="12" t="n"/>
-      <c r="O23" s="12" t="n"/>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N23" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O23" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P23" s="12" t="n"/>
       <c r="Q23" s="15" t="inlineStr">
         <is>
@@ -36734,9 +36774,19 @@
         </is>
       </c>
       <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="12" t="n"/>
-      <c r="O24" s="12" t="n"/>
+      <c r="M24" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N24" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P24" s="12" t="n"/>
       <c r="Q24" s="15" t="inlineStr">
         <is>
@@ -36805,9 +36855,19 @@
         </is>
       </c>
       <c r="L25" s="12" t="n"/>
-      <c r="M25" s="12" t="n"/>
-      <c r="N25" s="12" t="n"/>
-      <c r="O25" s="12" t="n"/>
+      <c r="M25" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N25" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O25" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P25" s="12" t="n"/>
       <c r="Q25" s="15" t="inlineStr">
         <is>
@@ -36876,9 +36936,19 @@
         </is>
       </c>
       <c r="L26" s="12" t="n"/>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="12" t="n"/>
-      <c r="O26" s="12" t="n"/>
+      <c r="M26" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N26" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P26" s="12" t="n"/>
       <c r="Q26" s="15" t="inlineStr">
         <is>
@@ -36946,9 +37016,19 @@
         </is>
       </c>
       <c r="L27" s="12" t="n"/>
-      <c r="M27" s="12" t="n"/>
-      <c r="N27" s="12" t="n"/>
-      <c r="O27" s="12" t="n"/>
+      <c r="M27" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N27" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P27" s="12" t="n"/>
       <c r="Q27" s="15" t="inlineStr">
         <is>
@@ -37016,9 +37096,19 @@
         </is>
       </c>
       <c r="L28" s="12" t="n"/>
-      <c r="M28" s="12" t="n"/>
-      <c r="N28" s="12" t="n"/>
-      <c r="O28" s="12" t="n"/>
+      <c r="M28" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N28" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P28" s="12" t="n"/>
       <c r="Q28" s="15" t="inlineStr">
         <is>
@@ -37086,9 +37176,19 @@
         </is>
       </c>
       <c r="L29" s="12" t="n"/>
-      <c r="M29" s="12" t="n"/>
-      <c r="N29" s="12" t="n"/>
-      <c r="O29" s="12" t="n"/>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N29" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O29" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P29" s="12" t="n"/>
       <c r="Q29" s="15" t="inlineStr">
         <is>
@@ -37156,9 +37256,19 @@
         </is>
       </c>
       <c r="L30" s="12" t="n"/>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="12" t="n"/>
-      <c r="O30" s="12" t="n"/>
+      <c r="M30" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N30" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P30" s="12" t="n"/>
       <c r="Q30" s="15" t="inlineStr">
         <is>
@@ -37226,9 +37336,19 @@
         </is>
       </c>
       <c r="L31" s="12" t="n"/>
-      <c r="M31" s="12" t="n"/>
-      <c r="N31" s="12" t="n"/>
-      <c r="O31" s="12" t="n"/>
+      <c r="M31" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N31" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O31" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P31" s="12" t="n"/>
       <c r="Q31" s="15" t="inlineStr">
         <is>
@@ -37296,9 +37416,19 @@
         </is>
       </c>
       <c r="L32" s="12" t="n"/>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="12" t="n"/>
-      <c r="O32" s="12" t="n"/>
+      <c r="M32" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N32" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P32" s="12" t="n"/>
       <c r="Q32" s="15" t="inlineStr">
         <is>
@@ -37366,9 +37496,19 @@
         </is>
       </c>
       <c r="L33" s="12" t="n"/>
-      <c r="M33" s="12" t="n"/>
-      <c r="N33" s="12" t="n"/>
-      <c r="O33" s="12" t="n"/>
+      <c r="M33" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N33" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O33" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P33" s="12" t="n"/>
       <c r="Q33" s="15" t="inlineStr">
         <is>
@@ -37436,9 +37576,19 @@
         </is>
       </c>
       <c r="L34" s="12" t="n"/>
-      <c r="M34" s="12" t="n"/>
-      <c r="N34" s="12" t="n"/>
-      <c r="O34" s="12" t="n"/>
+      <c r="M34" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N34" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O34" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P34" s="12" t="n"/>
       <c r="Q34" s="15" t="inlineStr">
         <is>
@@ -37506,9 +37656,19 @@
         </is>
       </c>
       <c r="L35" s="12" t="n"/>
-      <c r="M35" s="12" t="n"/>
-      <c r="N35" s="12" t="n"/>
-      <c r="O35" s="12" t="n"/>
+      <c r="M35" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N35" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O35" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P35" s="12" t="n"/>
       <c r="Q35" s="15" t="inlineStr">
         <is>
@@ -37576,9 +37736,19 @@
         </is>
       </c>
       <c r="L36" s="12" t="n"/>
-      <c r="M36" s="12" t="n"/>
-      <c r="N36" s="12" t="n"/>
-      <c r="O36" s="12" t="n"/>
+      <c r="M36" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N36" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P36" s="12" t="n"/>
       <c r="Q36" s="15" t="inlineStr">
         <is>
@@ -37647,9 +37817,19 @@
         </is>
       </c>
       <c r="L37" s="12" t="n"/>
-      <c r="M37" s="12" t="n"/>
-      <c r="N37" s="12" t="n"/>
-      <c r="O37" s="12" t="n"/>
+      <c r="M37" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N37" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O37" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P37" s="12" t="n"/>
       <c r="Q37" s="15" t="inlineStr">
         <is>
@@ -37718,9 +37898,19 @@
         </is>
       </c>
       <c r="L38" s="12" t="n"/>
-      <c r="M38" s="12" t="n"/>
-      <c r="N38" s="12" t="n"/>
-      <c r="O38" s="12" t="n"/>
+      <c r="M38" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N38" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O38" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P38" s="12" t="n"/>
       <c r="Q38" s="15" t="inlineStr">
         <is>
@@ -37788,9 +37978,19 @@
         </is>
       </c>
       <c r="L39" s="12" t="n"/>
-      <c r="M39" s="12" t="n"/>
-      <c r="N39" s="12" t="n"/>
-      <c r="O39" s="12" t="n"/>
+      <c r="M39" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N39" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O39" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P39" s="12" t="n"/>
       <c r="Q39" s="15" t="inlineStr">
         <is>
@@ -37859,9 +38059,19 @@
         </is>
       </c>
       <c r="L40" s="12" t="n"/>
-      <c r="M40" s="12" t="n"/>
-      <c r="N40" s="12" t="n"/>
-      <c r="O40" s="12" t="n"/>
+      <c r="M40" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N40" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O40" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P40" s="12" t="n"/>
       <c r="Q40" s="15" t="inlineStr">
         <is>
@@ -37929,9 +38139,19 @@
         </is>
       </c>
       <c r="L41" s="12" t="n"/>
-      <c r="M41" s="12" t="n"/>
-      <c r="N41" s="12" t="n"/>
-      <c r="O41" s="12" t="n"/>
+      <c r="M41" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N41" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O41" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P41" s="12" t="n"/>
       <c r="Q41" s="15" t="inlineStr">
         <is>
@@ -38000,9 +38220,19 @@
         </is>
       </c>
       <c r="L42" s="12" t="n"/>
-      <c r="M42" s="12" t="n"/>
-      <c r="N42" s="12" t="n"/>
-      <c r="O42" s="12" t="n"/>
+      <c r="M42" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N42" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O42" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P42" s="12" t="n"/>
       <c r="Q42" s="15" t="inlineStr">
         <is>
@@ -38071,9 +38301,19 @@
         </is>
       </c>
       <c r="L43" s="12" t="n"/>
-      <c r="M43" s="12" t="n"/>
-      <c r="N43" s="12" t="n"/>
-      <c r="O43" s="12" t="n"/>
+      <c r="M43" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N43" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O43" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P43" s="12" t="n"/>
       <c r="Q43" s="15" t="inlineStr">
         <is>
@@ -38141,9 +38381,19 @@
         </is>
       </c>
       <c r="L44" s="12" t="n"/>
-      <c r="M44" s="12" t="n"/>
-      <c r="N44" s="12" t="n"/>
-      <c r="O44" s="12" t="n"/>
+      <c r="M44" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N44" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O44" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P44" s="12" t="n"/>
       <c r="Q44" s="15" t="inlineStr">
         <is>
@@ -38211,9 +38461,19 @@
         </is>
       </c>
       <c r="L45" s="12" t="n"/>
-      <c r="M45" s="12" t="n"/>
-      <c r="N45" s="12" t="n"/>
-      <c r="O45" s="12" t="n"/>
+      <c r="M45" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N45" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O45" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P45" s="12" t="n"/>
       <c r="Q45" s="15" t="inlineStr">
         <is>
@@ -38281,9 +38541,19 @@
         </is>
       </c>
       <c r="L46" s="12" t="n"/>
-      <c r="M46" s="12" t="n"/>
-      <c r="N46" s="12" t="n"/>
-      <c r="O46" s="12" t="n"/>
+      <c r="M46" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N46" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O46" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P46" s="12" t="n"/>
       <c r="Q46" s="15" t="inlineStr">
         <is>
@@ -38351,9 +38621,19 @@
         </is>
       </c>
       <c r="L47" s="12" t="n"/>
-      <c r="M47" s="12" t="n"/>
-      <c r="N47" s="12" t="n"/>
-      <c r="O47" s="12" t="n"/>
+      <c r="M47" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N47" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O47" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P47" s="12" t="n"/>
       <c r="Q47" s="15" t="inlineStr">
         <is>
@@ -38421,9 +38701,19 @@
         </is>
       </c>
       <c r="L48" s="12" t="n"/>
-      <c r="M48" s="12" t="n"/>
-      <c r="N48" s="12" t="n"/>
-      <c r="O48" s="12" t="n"/>
+      <c r="M48" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N48" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O48" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P48" s="12" t="n"/>
       <c r="Q48" s="15" t="inlineStr">
         <is>
@@ -38491,9 +38781,19 @@
         </is>
       </c>
       <c r="L49" s="12" t="n"/>
-      <c r="M49" s="12" t="n"/>
-      <c r="N49" s="12" t="n"/>
-      <c r="O49" s="12" t="n"/>
+      <c r="M49" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N49" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O49" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P49" s="12" t="n"/>
       <c r="Q49" s="15" t="inlineStr">
         <is>
@@ -38552,7 +38852,7 @@
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>SC-021 項目⑭</t>
+          <t>SC-021 項目⑬</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
@@ -38561,9 +38861,19 @@
         </is>
       </c>
       <c r="L50" s="12" t="n"/>
-      <c r="M50" s="12" t="n"/>
-      <c r="N50" s="12" t="n"/>
-      <c r="O50" s="12" t="n"/>
+      <c r="M50" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N50" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O50" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P50" s="12" t="n"/>
       <c r="Q50" s="15" t="inlineStr">
         <is>
@@ -38631,9 +38941,19 @@
         </is>
       </c>
       <c r="L51" s="12" t="n"/>
-      <c r="M51" s="12" t="n"/>
-      <c r="N51" s="12" t="n"/>
-      <c r="O51" s="12" t="n"/>
+      <c r="M51" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N51" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O51" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P51" s="12" t="n"/>
       <c r="Q51" s="15" t="inlineStr">
         <is>
@@ -38701,9 +39021,19 @@
         </is>
       </c>
       <c r="L52" s="12" t="n"/>
-      <c r="M52" s="12" t="n"/>
-      <c r="N52" s="12" t="n"/>
-      <c r="O52" s="12" t="n"/>
+      <c r="M52" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N52" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O52" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P52" s="12" t="n"/>
       <c r="Q52" s="15" t="inlineStr">
         <is>
@@ -38742,7 +39072,7 @@
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>イベント名を押してSC-022を開き、「← 戻る」を押す</t>
+          <t>イベント名を押してSC-022を開き、「← イベント検索に戻る」を押す</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
@@ -38771,9 +39101,19 @@
         </is>
       </c>
       <c r="L53" s="12" t="n"/>
-      <c r="M53" s="12" t="n"/>
-      <c r="N53" s="12" t="n"/>
-      <c r="O53" s="12" t="n"/>
+      <c r="M53" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N53" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O53" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P53" s="12" t="n"/>
       <c r="Q53" s="15" t="inlineStr">
         <is>
@@ -38802,7 +39142,7 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>検索結果からお気に入りに登録できる</t>
+          <t>検索結果から開いた詳細でお気に入りに登録すると、検索画面のお気に入り数に反映される</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
@@ -38812,12 +39152,12 @@
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>TD-02のカードの「☆」を押す</t>
+          <t>TD-02のイベント名を押してSC-022を開き、「☆ お気に入りに追加」を押してからSC-021に戻る</t>
         </is>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>「★」に変わり、お気に入り数が1増える</t>
+          <t>SC-021のTD-02のお気に入り数が1増える</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
@@ -38833,7 +39173,7 @@
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>SC-021 イベント処理6</t>
+          <t>SC-021 イベント処理5、SC-022 イベント処理2</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
@@ -38842,9 +39182,19 @@
         </is>
       </c>
       <c r="L54" s="12" t="n"/>
-      <c r="M54" s="12" t="n"/>
-      <c r="N54" s="12" t="n"/>
-      <c r="O54" s="12" t="n"/>
+      <c r="M54" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N54" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O54" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P54" s="12" t="n"/>
       <c r="Q54" s="15" t="inlineStr">
         <is>
@@ -38912,9 +39262,19 @@
         </is>
       </c>
       <c r="L55" s="12" t="n"/>
-      <c r="M55" s="12" t="n"/>
-      <c r="N55" s="12" t="n"/>
-      <c r="O55" s="12" t="n"/>
+      <c r="M55" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N55" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O55" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P55" s="12" t="n"/>
       <c r="Q55" s="15" t="inlineStr">
         <is>
@@ -38983,9 +39343,19 @@
         </is>
       </c>
       <c r="L56" s="12" t="n"/>
-      <c r="M56" s="12" t="n"/>
-      <c r="N56" s="12" t="n"/>
-      <c r="O56" s="12" t="n"/>
+      <c r="M56" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N56" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O56" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P56" s="12" t="n"/>
       <c r="Q56" s="15" t="inlineStr">
         <is>
@@ -39024,7 +39394,7 @@
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>SC-020からイベント名を押してSC-022を開き、「← 戻る」を押す</t>
+          <t>SC-020からイベント名を押してSC-022を開き、「← イベント一覧に戻る」を押す</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -39053,9 +39423,19 @@
         </is>
       </c>
       <c r="L57" s="12" t="n"/>
-      <c r="M57" s="12" t="n"/>
-      <c r="N57" s="12" t="n"/>
-      <c r="O57" s="12" t="n"/>
+      <c r="M57" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N57" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O57" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P57" s="12" t="n"/>
       <c r="Q57" s="15" t="inlineStr">
         <is>
@@ -39094,7 +39474,7 @@
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>「☆ お気に入り」を押す</t>
+          <t>「☆ お気に入りに追加」を押す</t>
         </is>
       </c>
       <c r="G58" s="12" t="inlineStr">
@@ -39124,9 +39504,19 @@
         </is>
       </c>
       <c r="L58" s="12" t="n"/>
-      <c r="M58" s="12" t="n"/>
-      <c r="N58" s="12" t="n"/>
-      <c r="O58" s="12" t="n"/>
+      <c r="M58" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N58" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O58" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P58" s="12" t="n"/>
       <c r="Q58" s="15" t="inlineStr">
         <is>
@@ -39195,9 +39585,19 @@
         </is>
       </c>
       <c r="L59" s="12" t="n"/>
-      <c r="M59" s="12" t="n"/>
-      <c r="N59" s="12" t="n"/>
-      <c r="O59" s="12" t="n"/>
+      <c r="M59" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N59" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O59" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P59" s="12" t="n"/>
       <c r="Q59" s="15" t="inlineStr">
         <is>
@@ -39266,9 +39666,19 @@
         </is>
       </c>
       <c r="L60" s="12" t="n"/>
-      <c r="M60" s="12" t="n"/>
-      <c r="N60" s="12" t="n"/>
-      <c r="O60" s="12" t="n"/>
+      <c r="M60" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N60" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O60" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P60" s="12" t="n"/>
       <c r="Q60" s="15" t="inlineStr">
         <is>
@@ -39408,9 +39818,19 @@
         </is>
       </c>
       <c r="L62" s="12" t="n"/>
-      <c r="M62" s="12" t="n"/>
-      <c r="N62" s="12" t="n"/>
-      <c r="O62" s="12" t="n"/>
+      <c r="M62" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N62" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O62" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P62" s="12" t="n"/>
       <c r="Q62" s="15" t="inlineStr">
         <is>
@@ -39549,9 +39969,19 @@
         </is>
       </c>
       <c r="L64" s="12" t="n"/>
-      <c r="M64" s="12" t="n"/>
-      <c r="N64" s="12" t="n"/>
-      <c r="O64" s="12" t="n"/>
+      <c r="M64" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N64" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O64" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P64" s="12" t="n"/>
       <c r="Q64" s="15" t="inlineStr">
         <is>
@@ -39620,9 +40050,19 @@
         </is>
       </c>
       <c r="L65" s="12" t="n"/>
-      <c r="M65" s="12" t="n"/>
-      <c r="N65" s="12" t="n"/>
-      <c r="O65" s="12" t="n"/>
+      <c r="M65" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N65" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O65" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P65" s="12" t="n"/>
       <c r="Q65" s="15" t="inlineStr">
         <is>
@@ -39691,9 +40131,19 @@
         </is>
       </c>
       <c r="L66" s="12" t="n"/>
-      <c r="M66" s="12" t="n"/>
-      <c r="N66" s="12" t="n"/>
-      <c r="O66" s="12" t="n"/>
+      <c r="M66" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N66" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O66" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P66" s="12" t="n"/>
       <c r="Q66" s="15" t="inlineStr">
         <is>
@@ -44971,7 +45421,7 @@
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>【一般C】「区分テスト」を押してSC-022を開き、「☆ お気に入り」を押す</t>
+          <t>【一般C】「区分テスト」を押してSC-022を開き、「☆ お気に入りに追加」を押す</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -47724,7 +48174,7 @@
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>【一般A】TD-02のSC-022で「☆ お気に入り」を押す</t>
+          <t>【一般A】TD-02のSC-022で「☆ お気に入りに追加」を押す</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
@@ -51690,225 +52140,4 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010012AB853B196F794D8522E079E5062DE1" ma:contentTypeVersion="10" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f5519c8ad0001dc1944c7d5117d6ef1e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8d6e06c-e60e-47a7-a324-5df51f361a1d" xmlns:ns3="0eb4123e-ff08-448a-a51c-d574d85865b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6b6fc7ab0c5db989cb71f9aed3612649" ns2:_="" ns3:_="">
-    <xsd:import namespace="e8d6e06c-e60e-47a7-a324-5df51f361a1d"/>
-    <xsd:import namespace="0eb4123e-ff08-448a-a51c-d574d85865b6"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e8d6e06c-e60e-47a7-a324-5df51f361a1d" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8ae29c59-cffc-49bc-b1b2-82d81727b3d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0eb4123e-ff08-448a-a51c-d574d85865b6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{617f6a86-eb1c-4018-be3f-ff946cbc1596}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="0eb4123e-ff08-448a-a51c-d574d85865b6">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8d6e06c-e60e-47a7-a324-5df51f361a1d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0eb4123e-ff08-448a-a51c-d574d85865b6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5CECB6A-F27A-4032-87E4-CC6D5CF3505A}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2F084F3-302E-4CBC-927B-CB4887B418DE}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{300BB5C6-51F8-48CE-8ECB-8F6750A848FD}"/>
 </file>
--- a/docs/40_テスト/44_テスト結果表.xlsx
+++ b/docs/40_テスト/44_テスト結果表.xlsx
@@ -25,10 +25,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -39636,7 +39635,7 @@
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>コメントの「返信」を押し、表示された入力欄に入力して「投稿」を押す</t>
+          <t>コメントの「返信」を押し、表示された入力欄に入力して「返信を投稿」を押す</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -39747,9 +39746,19 @@
         </is>
       </c>
       <c r="L61" s="12" t="n"/>
-      <c r="M61" s="12" t="n"/>
-      <c r="N61" s="12" t="n"/>
-      <c r="O61" s="12" t="n"/>
+      <c r="M61" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N61" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O61" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P61" s="12" t="n"/>
       <c r="Q61" s="15" t="inlineStr">
         <is>
@@ -39898,9 +39907,19 @@
         </is>
       </c>
       <c r="L63" s="12" t="n"/>
-      <c r="M63" s="12" t="n"/>
-      <c r="N63" s="12" t="n"/>
-      <c r="O63" s="12" t="n"/>
+      <c r="M63" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N63" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O63" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P63" s="12" t="n"/>
       <c r="Q63" s="15" t="inlineStr">
         <is>
@@ -40211,9 +40230,19 @@
         </is>
       </c>
       <c r="L67" s="12" t="n"/>
-      <c r="M67" s="12" t="n"/>
-      <c r="N67" s="12" t="n"/>
-      <c r="O67" s="12" t="n"/>
+      <c r="M67" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N67" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O67" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P67" s="12" t="n"/>
       <c r="Q67" s="15" t="inlineStr">
         <is>
@@ -40281,9 +40310,19 @@
         </is>
       </c>
       <c r="L68" s="12" t="n"/>
-      <c r="M68" s="12" t="n"/>
-      <c r="N68" s="12" t="n"/>
-      <c r="O68" s="12" t="n"/>
+      <c r="M68" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N68" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O68" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P68" s="12" t="n"/>
       <c r="Q68" s="15" t="inlineStr">
         <is>
@@ -40351,9 +40390,19 @@
         </is>
       </c>
       <c r="L69" s="12" t="n"/>
-      <c r="M69" s="12" t="n"/>
-      <c r="N69" s="12" t="n"/>
-      <c r="O69" s="12" t="n"/>
+      <c r="M69" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N69" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O69" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P69" s="12" t="n"/>
       <c r="Q69" s="15" t="inlineStr">
         <is>
@@ -40422,10 +40471,24 @@
         </is>
       </c>
       <c r="L70" s="12" t="n"/>
-      <c r="M70" s="12" t="n"/>
-      <c r="N70" s="12" t="n"/>
-      <c r="O70" s="12" t="n"/>
-      <c r="P70" s="12" t="n"/>
+      <c r="M70" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N70" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O70" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P70" s="12" t="inlineStr">
+        <is>
+          <t>一般ユーザーはTD-02に申込済みのため、TD-05の利用者（一般ユーザー2）がTD-01に区分「学生」で申し込んで確認した（申込ID=4、受付済）。</t>
+        </is>
+      </c>
       <c r="Q70" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_画面結合.xlsx／SC-023</t>
@@ -40493,10 +40556,24 @@
         </is>
       </c>
       <c r="L71" s="12" t="n"/>
-      <c r="M71" s="12" t="n"/>
-      <c r="N71" s="12" t="n"/>
-      <c r="O71" s="12" t="n"/>
-      <c r="P71" s="12" t="n"/>
+      <c r="M71" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N71" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O71" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P71" s="12" t="inlineStr">
+        <is>
+          <t>一般ユーザーがTD-02に受付済で申込済みのため、TD-05の利用者（一般ユーザー2）がTD-02に申し込んで確認した（申込ID=5、キャンセル待ち）。</t>
+        </is>
+      </c>
       <c r="Q71" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_画面結合.xlsx／SC-023</t>
@@ -40563,9 +40640,19 @@
         </is>
       </c>
       <c r="L72" s="12" t="n"/>
-      <c r="M72" s="12" t="n"/>
-      <c r="N72" s="12" t="n"/>
-      <c r="O72" s="12" t="n"/>
+      <c r="M72" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N72" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O72" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P72" s="12" t="n"/>
       <c r="Q72" s="15" t="inlineStr">
         <is>
@@ -40633,9 +40720,19 @@
         </is>
       </c>
       <c r="L73" s="12" t="n"/>
-      <c r="M73" s="12" t="n"/>
-      <c r="N73" s="12" t="n"/>
-      <c r="O73" s="12" t="n"/>
+      <c r="M73" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N73" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O73" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P73" s="12" t="n"/>
       <c r="Q73" s="15" t="inlineStr">
         <is>
@@ -40703,9 +40800,19 @@
         </is>
       </c>
       <c r="L74" s="12" t="n"/>
-      <c r="M74" s="12" t="n"/>
-      <c r="N74" s="12" t="n"/>
-      <c r="O74" s="12" t="n"/>
+      <c r="M74" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N74" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O74" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P74" s="12" t="n"/>
       <c r="Q74" s="15" t="inlineStr">
         <is>
@@ -40843,9 +40950,19 @@
         </is>
       </c>
       <c r="L76" s="12" t="n"/>
-      <c r="M76" s="12" t="n"/>
-      <c r="N76" s="12" t="n"/>
-      <c r="O76" s="12" t="n"/>
+      <c r="M76" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N76" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O76" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P76" s="12" t="n"/>
       <c r="Q76" s="15" t="inlineStr">
         <is>

--- a/docs/40_テスト/44_テスト結果表.xlsx
+++ b/docs/40_テスト/44_テスト結果表.xlsx
@@ -947,6 +947,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="14" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1005,6 +1006,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -1244,6 +1246,7 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -40880,9 +40883,19 @@
         </is>
       </c>
       <c r="L75" s="12" t="n"/>
-      <c r="M75" s="12" t="n"/>
-      <c r="N75" s="12" t="n"/>
-      <c r="O75" s="12" t="n"/>
+      <c r="M75" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N75" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O75" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P75" s="12" t="n"/>
       <c r="Q75" s="15" t="inlineStr">
         <is>
@@ -41031,9 +41044,19 @@
         </is>
       </c>
       <c r="L77" s="12" t="n"/>
-      <c r="M77" s="12" t="n"/>
-      <c r="N77" s="12" t="n"/>
-      <c r="O77" s="12" t="n"/>
+      <c r="M77" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N77" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O77" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P77" s="12" t="n"/>
       <c r="Q77" s="15" t="inlineStr">
         <is>
@@ -41102,9 +41125,19 @@
         </is>
       </c>
       <c r="L78" s="12" t="n"/>
-      <c r="M78" s="12" t="n"/>
-      <c r="N78" s="12" t="n"/>
-      <c r="O78" s="12" t="n"/>
+      <c r="M78" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N78" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O78" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P78" s="12" t="n"/>
       <c r="Q78" s="15" t="inlineStr">
         <is>
@@ -41172,9 +41205,19 @@
         </is>
       </c>
       <c r="L79" s="12" t="n"/>
-      <c r="M79" s="12" t="n"/>
-      <c r="N79" s="12" t="n"/>
-      <c r="O79" s="12" t="n"/>
+      <c r="M79" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N79" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O79" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P79" s="12" t="n"/>
       <c r="Q79" s="15" t="inlineStr">
         <is>
@@ -41243,9 +41286,19 @@
         </is>
       </c>
       <c r="L80" s="12" t="n"/>
-      <c r="M80" s="12" t="n"/>
-      <c r="N80" s="12" t="n"/>
-      <c r="O80" s="12" t="n"/>
+      <c r="M80" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N80" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O80" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P80" s="12" t="n"/>
       <c r="Q80" s="15" t="inlineStr">
         <is>
@@ -41385,9 +41438,19 @@
         </is>
       </c>
       <c r="L82" s="12" t="n"/>
-      <c r="M82" s="12" t="n"/>
-      <c r="N82" s="12" t="n"/>
-      <c r="O82" s="12" t="n"/>
+      <c r="M82" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N82" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O82" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P82" s="12" t="n"/>
       <c r="Q82" s="15" t="inlineStr">
         <is>
@@ -41455,9 +41518,19 @@
         </is>
       </c>
       <c r="L83" s="12" t="n"/>
-      <c r="M83" s="12" t="n"/>
-      <c r="N83" s="12" t="n"/>
-      <c r="O83" s="12" t="n"/>
+      <c r="M83" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N83" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O83" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P83" s="12" t="n"/>
       <c r="Q83" s="15" t="inlineStr">
         <is>
@@ -41525,9 +41598,19 @@
         </is>
       </c>
       <c r="L84" s="12" t="n"/>
-      <c r="M84" s="12" t="n"/>
-      <c r="N84" s="12" t="n"/>
-      <c r="O84" s="12" t="n"/>
+      <c r="M84" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N84" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O84" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P84" s="12" t="n"/>
       <c r="Q84" s="15" t="inlineStr">
         <is>
@@ -41595,9 +41678,19 @@
         </is>
       </c>
       <c r="L85" s="12" t="n"/>
-      <c r="M85" s="12" t="n"/>
-      <c r="N85" s="12" t="n"/>
-      <c r="O85" s="12" t="n"/>
+      <c r="M85" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N85" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O85" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P85" s="12" t="n"/>
       <c r="Q85" s="15" t="inlineStr">
         <is>
@@ -41665,9 +41758,19 @@
         </is>
       </c>
       <c r="L86" s="12" t="n"/>
-      <c r="M86" s="12" t="n"/>
-      <c r="N86" s="12" t="n"/>
-      <c r="O86" s="12" t="n"/>
+      <c r="M86" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N86" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O86" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P86" s="12" t="n"/>
       <c r="Q86" s="15" t="inlineStr">
         <is>
@@ -41735,9 +41838,19 @@
         </is>
       </c>
       <c r="L87" s="12" t="n"/>
-      <c r="M87" s="12" t="n"/>
-      <c r="N87" s="12" t="n"/>
-      <c r="O87" s="12" t="n"/>
+      <c r="M87" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N87" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O87" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P87" s="12" t="n"/>
       <c r="Q87" s="15" t="inlineStr">
         <is>
@@ -41805,9 +41918,19 @@
         </is>
       </c>
       <c r="L88" s="12" t="n"/>
-      <c r="M88" s="12" t="n"/>
-      <c r="N88" s="12" t="n"/>
-      <c r="O88" s="12" t="n"/>
+      <c r="M88" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N88" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O88" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P88" s="12" t="n"/>
       <c r="Q88" s="15" t="inlineStr">
         <is>
@@ -41876,9 +41999,19 @@
         </is>
       </c>
       <c r="L89" s="12" t="n"/>
-      <c r="M89" s="12" t="n"/>
-      <c r="N89" s="12" t="n"/>
-      <c r="O89" s="12" t="n"/>
+      <c r="M89" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N89" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O89" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P89" s="12" t="n"/>
       <c r="Q89" s="15" t="inlineStr">
         <is>
@@ -41947,9 +42080,19 @@
         </is>
       </c>
       <c r="L90" s="12" t="n"/>
-      <c r="M90" s="12" t="n"/>
-      <c r="N90" s="12" t="n"/>
-      <c r="O90" s="12" t="n"/>
+      <c r="M90" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N90" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O90" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P90" s="12" t="n"/>
       <c r="Q90" s="15" t="inlineStr">
         <is>
@@ -42017,9 +42160,19 @@
         </is>
       </c>
       <c r="L91" s="12" t="n"/>
-      <c r="M91" s="12" t="n"/>
-      <c r="N91" s="12" t="n"/>
-      <c r="O91" s="12" t="n"/>
+      <c r="M91" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N91" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O91" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P91" s="12" t="n"/>
       <c r="Q91" s="15" t="inlineStr">
         <is>
@@ -42087,9 +42240,19 @@
         </is>
       </c>
       <c r="L92" s="12" t="n"/>
-      <c r="M92" s="12" t="n"/>
-      <c r="N92" s="12" t="n"/>
-      <c r="O92" s="12" t="n"/>
+      <c r="M92" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N92" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O92" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P92" s="12" t="n"/>
       <c r="Q92" s="15" t="inlineStr">
         <is>
@@ -42158,9 +42321,19 @@
         </is>
       </c>
       <c r="L93" s="12" t="n"/>
-      <c r="M93" s="12" t="n"/>
-      <c r="N93" s="12" t="n"/>
-      <c r="O93" s="12" t="n"/>
+      <c r="M93" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N93" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O93" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P93" s="12" t="n"/>
       <c r="Q93" s="15" t="inlineStr">
         <is>
@@ -42558,7 +42731,7 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>開催日時・申込締切が空で、「（イベント名）を複製しています。…」の案内が表示される</t>
+          <t>開催日時・申込締切が空で、「「（イベント名）」の内容を複写しました。…」の案内が表示される</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
@@ -42582,10 +42755,24 @@
         </is>
       </c>
       <c r="L99" s="12" t="n"/>
-      <c r="M99" s="12" t="n"/>
-      <c r="N99" s="12" t="n"/>
-      <c r="O99" s="12" t="n"/>
-      <c r="P99" s="12" t="n"/>
+      <c r="M99" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N99" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O99" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P99" s="12" t="inlineStr">
+        <is>
+          <t>IT-SC120-N03と同じ画面で確認した。</t>
+        </is>
+      </c>
       <c r="Q99" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_画面結合.xlsx／SC-121</t>
@@ -52257,4 +52444,225 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010012AB853B196F794D8522E079E5062DE1" ma:contentTypeVersion="10" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f5519c8ad0001dc1944c7d5117d6ef1e">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8d6e06c-e60e-47a7-a324-5df51f361a1d" xmlns:ns3="0eb4123e-ff08-448a-a51c-d574d85865b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6b6fc7ab0c5db989cb71f9aed3612649" ns2:_="" ns3:_="">
+    <xsd:import namespace="e8d6e06c-e60e-47a7-a324-5df51f361a1d"/>
+    <xsd:import namespace="0eb4123e-ff08-448a-a51c-d574d85865b6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e8d6e06c-e60e-47a7-a324-5df51f361a1d" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8ae29c59-cffc-49bc-b1b2-82d81727b3d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0eb4123e-ff08-448a-a51c-d574d85865b6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{617f6a86-eb1c-4018-be3f-ff946cbc1596}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="0eb4123e-ff08-448a-a51c-d574d85865b6">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8d6e06c-e60e-47a7-a324-5df51f361a1d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0eb4123e-ff08-448a-a51c-d574d85865b6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33A55CE1-1BE0-462F-A270-7D4CA7D09116}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A4816FE-E827-4F25-8B1F-512C6930ACAC}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FABF144-784F-4059-9E5C-44E6245EB4A8}"/>
 </file>
--- a/docs/40_テスト/44_テスト結果表.xlsx
+++ b/docs/40_テスト/44_テスト結果表.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="不具合一覧" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'UT'!$A$1:$T$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'UT'!$A$1:$T$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IT_API結合'!$A$1:$T$212</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'IT_画面結合'!$A$1:$T$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ST'!$A$1:$T$95</definedName>
@@ -25,9 +25,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -947,7 +948,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="14" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1006,7 +1006,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -1066,22 +1065,22 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D11" s="6">
-        <f>COUNTIF(UT!M2:M177,"OK")</f>
+        <f>COUNTIF(UT!M2:M180,"OK")</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>COUNTIF(UT!M2:M177,"NG")</f>
+        <f>COUNTIF(UT!M2:M180,"NG")</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>COUNTIF(UT!M2:M177,"保留")</f>
+        <f>COUNTIF(UT!M2:M180,"保留")</f>
         <v/>
       </c>
       <c r="G11" s="6">
-        <f>COUNTIF(UT!M2:M177,"対象外")</f>
+        <f>COUNTIF(UT!M2:M180,"対象外")</f>
         <v/>
       </c>
       <c r="H11" s="6">
@@ -1246,7 +1245,6 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -1328,7 +1326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T177"/>
+  <dimension ref="A1:T180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11842,7 +11840,7 @@
     <row r="120" ht="27" customHeight="1">
       <c r="A120" s="12" t="inlineStr">
         <is>
-          <t>UT-FORM-E01</t>
+          <t>UT-FORM-N09</t>
         </is>
       </c>
       <c r="B120" s="12" t="inlineStr">
@@ -11852,12 +11850,12 @@
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>異常系</t>
+          <t>正常系</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>バリデーション: 必須項目が未入力の場合form.invalid</t>
+          <t>編集モード: 区分を変更せずに保存すると、ticketTypesを送らない</t>
         </is>
       </c>
       <c r="E120" s="12" t="inlineStr">
@@ -11872,7 +11870,7 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>バリデーション: 必須項目が未入力の場合form.invalid</t>
+          <t>編集モード: 区分を変更せずに保存すると、ticketTypesを送らない</t>
         </is>
       </c>
       <c r="H120" s="12" t="inlineStr">
@@ -11887,7 +11885,7 @@
       </c>
       <c r="J120" s="12" t="inlineStr">
         <is>
-          <t>30_画面詳細設計書</t>
+          <t>30_画面詳細設計書 SC-121 補足、31_API詳細設計書 AP-121</t>
         </is>
       </c>
       <c r="K120" s="12" t="inlineStr">
@@ -11906,7 +11904,7 @@
         </is>
       </c>
       <c r="N120" s="23" t="n">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="O120" s="12" t="inlineStr">
         <is>
@@ -11915,12 +11913,12 @@
       </c>
       <c r="P120" s="12" t="inlineStr">
         <is>
-          <t>自動テスト成功</t>
+          <t>自動テスト成功。Issue #19 の修正に伴い追加したテスト</t>
         </is>
       </c>
       <c r="Q120" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261014.txt</t>
         </is>
       </c>
       <c r="R120" s="12" t="n"/>
@@ -11930,7 +11928,7 @@
     <row r="121" ht="27" customHeight="1">
       <c r="A121" s="12" t="inlineStr">
         <is>
-          <t>UT-FORM-E02</t>
+          <t>UT-FORM-N10</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
@@ -11940,12 +11938,12 @@
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>異常系</t>
+          <t>正常系</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>保存時に入力値エラー（400）が返るとfieldErrorsに反映される</t>
+          <t>編集モード: 区分の無いイベントを、区分を追加せずに保存すると、ticketTypesを送らない</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr">
@@ -11960,7 +11958,7 @@
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>保存時に入力値エラー（400）が返るとfieldErrorsに反映される</t>
+          <t>編集モード: 区分の無いイベントを、区分を追加せずに保存すると、ticketTypesを送らない</t>
         </is>
       </c>
       <c r="H121" s="12" t="inlineStr">
@@ -11975,7 +11973,7 @@
       </c>
       <c r="J121" s="12" t="inlineStr">
         <is>
-          <t>30_画面詳細設計書</t>
+          <t>30_画面詳細設計書 SC-121 補足、31_API詳細設計書 AP-121</t>
         </is>
       </c>
       <c r="K121" s="12" t="inlineStr">
@@ -11994,7 +11992,7 @@
         </is>
       </c>
       <c r="N121" s="23" t="n">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="O121" s="12" t="inlineStr">
         <is>
@@ -12003,12 +12001,12 @@
       </c>
       <c r="P121" s="12" t="inlineStr">
         <is>
-          <t>自動テスト成功</t>
+          <t>自動テスト成功。Issue #19 の修正に伴い追加したテスト</t>
         </is>
       </c>
       <c r="Q121" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261014.txt</t>
         </is>
       </c>
       <c r="R121" s="12" t="n"/>
@@ -12018,12 +12016,12 @@
     <row r="122" ht="27" customHeight="1">
       <c r="A122" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N01</t>
+          <t>UT-FORM-N11</t>
         </is>
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>イベント一覧（SC-020）</t>
+          <t>イベント登録・編集（SC-121）</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
@@ -12033,7 +12031,7 @@
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>初期表示でイベント一覧を取得する</t>
+          <t>編集モード: 区分を変更して保存すると、変更後のticketTypesを送る</t>
         </is>
       </c>
       <c r="E122" s="12" t="inlineStr">
@@ -12048,7 +12046,7 @@
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>初期表示でイベント一覧を取得する</t>
+          <t>編集モード: 区分を変更して保存すると、変更後のticketTypesを送る</t>
         </is>
       </c>
       <c r="H122" s="12" t="inlineStr">
@@ -12063,7 +12061,7 @@
       </c>
       <c r="J122" s="12" t="inlineStr">
         <is>
-          <t>30_画面詳細設計書</t>
+          <t>30_画面詳細設計書 SC-121 補足、31_API詳細設計書 AP-121</t>
         </is>
       </c>
       <c r="K122" s="12" t="inlineStr">
@@ -12073,7 +12071,7 @@
       </c>
       <c r="L122" s="12" t="inlineStr">
         <is>
-          <t>events/event-list/event-list.spec.ts</t>
+          <t>admin/admin-event-form/admin-event-form.spec.ts</t>
         </is>
       </c>
       <c r="M122" s="12" t="inlineStr">
@@ -12082,7 +12080,7 @@
         </is>
       </c>
       <c r="N122" s="23" t="n">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="O122" s="12" t="inlineStr">
         <is>
@@ -12091,12 +12089,12 @@
       </c>
       <c r="P122" s="12" t="inlineStr">
         <is>
-          <t>自動テスト成功</t>
+          <t>自動テスト成功。Issue #19 の修正に伴い追加したテスト</t>
         </is>
       </c>
       <c r="Q122" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261014.txt</t>
         </is>
       </c>
       <c r="R122" s="12" t="n"/>
@@ -12106,22 +12104,22 @@
     <row r="123" ht="27" customHeight="1">
       <c r="A123" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N02</t>
+          <t>UT-FORM-E01</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>イベント一覧（SC-020）</t>
+          <t>イベント登録・編集（SC-121）</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>正常系</t>
+          <t>異常系</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 既定は開催日時昇順</t>
+          <t>バリデーション: 必須項目が未入力の場合form.invalid</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr">
@@ -12136,7 +12134,7 @@
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 既定は開催日時昇順</t>
+          <t>バリデーション: 必須項目が未入力の場合form.invalid</t>
         </is>
       </c>
       <c r="H123" s="12" t="inlineStr">
@@ -12161,7 +12159,7 @@
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>events/event-list/event-list.spec.ts</t>
+          <t>admin/admin-event-form/admin-event-form.spec.ts</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
@@ -12194,22 +12192,22 @@
     <row r="124" ht="27" customHeight="1">
       <c r="A124" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N03</t>
+          <t>UT-FORM-E02</t>
         </is>
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>イベント一覧（SC-020）</t>
+          <t>イベント登録・編集（SC-121）</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
-          <t>正常系</t>
+          <t>異常系</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 申込数の多い順</t>
+          <t>保存時に入力値エラー（400）が返るとfieldErrorsに反映される</t>
         </is>
       </c>
       <c r="E124" s="12" t="inlineStr">
@@ -12224,7 +12222,7 @@
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 申込数の多い順</t>
+          <t>保存時に入力値エラー（400）が返るとfieldErrorsに反映される</t>
         </is>
       </c>
       <c r="H124" s="12" t="inlineStr">
@@ -12249,7 +12247,7 @@
       </c>
       <c r="L124" s="12" t="inlineStr">
         <is>
-          <t>events/event-list/event-list.spec.ts</t>
+          <t>admin/admin-event-form/admin-event-form.spec.ts</t>
         </is>
       </c>
       <c r="M124" s="12" t="inlineStr">
@@ -12282,7 +12280,7 @@
     <row r="125" ht="27" customHeight="1">
       <c r="A125" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N04</t>
+          <t>UT-LIST-N01</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
@@ -12297,7 +12295,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>並び替え: お気に入り数の多い順</t>
+          <t>初期表示でイベント一覧を取得する</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
@@ -12312,7 +12310,7 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>並び替え: お気に入り数の多い順</t>
+          <t>初期表示でイベント一覧を取得する</t>
         </is>
       </c>
       <c r="H125" s="12" t="inlineStr">
@@ -12370,7 +12368,7 @@
     <row r="126" ht="27" customHeight="1">
       <c r="A126" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N05</t>
+          <t>UT-LIST-N02</t>
         </is>
       </c>
       <c r="B126" s="12" t="inlineStr">
@@ -12385,7 +12383,7 @@
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 申込締切が近い順</t>
+          <t>並び替え: 既定は開催日時昇順</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr">
@@ -12400,7 +12398,7 @@
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 申込締切が近い順</t>
+          <t>並び替え: 既定は開催日時昇順</t>
         </is>
       </c>
       <c r="H126" s="12" t="inlineStr">
@@ -12458,7 +12456,7 @@
     <row r="127" ht="27" customHeight="1">
       <c r="A127" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N06</t>
+          <t>UT-LIST-N03</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
@@ -12473,7 +12471,7 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 開催済みのイベントは末尾に並ぶ（既定の開催日時順）</t>
+          <t>並び替え: 申込数の多い順</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
@@ -12488,7 +12486,7 @@
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 開催済みのイベントは末尾に並ぶ（既定の開催日時順）</t>
+          <t>並び替え: 申込数の多い順</t>
         </is>
       </c>
       <c r="H127" s="12" t="inlineStr">
@@ -12546,7 +12544,7 @@
     <row r="128" ht="27" customHeight="1">
       <c r="A128" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N07</t>
+          <t>UT-LIST-N04</t>
         </is>
       </c>
       <c r="B128" s="12" t="inlineStr">
@@ -12561,7 +12559,7 @@
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 申込数の多い順でも開催済みのイベントは末尾に並ぶ</t>
+          <t>並び替え: お気に入り数の多い順</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
@@ -12576,7 +12574,7 @@
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 申込数の多い順でも開催済みのイベントは末尾に並ぶ</t>
+          <t>並び替え: お気に入り数の多い順</t>
         </is>
       </c>
       <c r="H128" s="12" t="inlineStr">
@@ -12634,7 +12632,7 @@
     <row r="129" ht="27" customHeight="1">
       <c r="A129" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N08</t>
+          <t>UT-LIST-N05</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
@@ -12649,7 +12647,7 @@
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 受付終了でも開催前のイベントは末尾に移動しない</t>
+          <t>並び替え: 申込締切が近い順</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
@@ -12664,7 +12662,7 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 受付終了でも開催前のイベントは末尾に移動しない</t>
+          <t>並び替え: 申込締切が近い順</t>
         </is>
       </c>
       <c r="H129" s="12" t="inlineStr">
@@ -12722,7 +12720,7 @@
     <row r="130" ht="27" customHeight="1">
       <c r="A130" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N09</t>
+          <t>UT-LIST-N06</t>
         </is>
       </c>
       <c r="B130" s="12" t="inlineStr">
@@ -12737,7 +12735,7 @@
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>詳細展開: toggleExpandでイベント詳細を取得する</t>
+          <t>並び替え: 開催済みのイベントは末尾に並ぶ（既定の開催日時順）</t>
         </is>
       </c>
       <c r="E130" s="12" t="inlineStr">
@@ -12752,7 +12750,7 @@
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>詳細展開: toggleExpandでイベント詳細を取得する</t>
+          <t>並び替え: 開催済みのイベントは末尾に並ぶ（既定の開催日時順）</t>
         </is>
       </c>
       <c r="H130" s="12" t="inlineStr">
@@ -12810,7 +12808,7 @@
     <row r="131" ht="27" customHeight="1">
       <c r="A131" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N10</t>
+          <t>UT-LIST-N07</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
@@ -12825,7 +12823,7 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>詳細展開: 同じ行をもう一度押すと閉じる</t>
+          <t>並び替え: 申込数の多い順でも開催済みのイベントは末尾に並ぶ</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
@@ -12840,7 +12838,7 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>詳細展開: 同じ行をもう一度押すと閉じる</t>
+          <t>並び替え: 申込数の多い順でも開催済みのイベントは末尾に並ぶ</t>
         </is>
       </c>
       <c r="H131" s="12" t="inlineStr">
@@ -12898,7 +12896,7 @@
     <row r="132" ht="27" customHeight="1">
       <c r="A132" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N11</t>
+          <t>UT-LIST-N08</t>
         </is>
       </c>
       <c r="B132" s="12" t="inlineStr">
@@ -12913,7 +12911,7 @@
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>申込成功で申込完了画面へ遷移する</t>
+          <t>並び替え: 受付終了でも開催前のイベントは末尾に移動しない</t>
         </is>
       </c>
       <c r="E132" s="12" t="inlineStr">
@@ -12928,7 +12926,7 @@
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>申込成功で申込完了画面へ遷移する</t>
+          <t>並び替え: 受付終了でも開催前のイベントは末尾に移動しない</t>
         </is>
       </c>
       <c r="H132" s="12" t="inlineStr">
@@ -12986,7 +12984,7 @@
     <row r="133" ht="27" customHeight="1">
       <c r="A133" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N12</t>
+          <t>UT-LIST-N09</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
@@ -13001,7 +12999,7 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>お気に入りトグルでfavoriteStore.toggleを呼ぶ</t>
+          <t>詳細展開: toggleExpandでイベント詳細を取得する</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
@@ -13016,7 +13014,7 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>お気に入りトグルでfavoriteStore.toggleを呼ぶ</t>
+          <t>詳細展開: toggleExpandでイベント詳細を取得する</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
@@ -13074,7 +13072,7 @@
     <row r="134" ht="27" customHeight="1">
       <c r="A134" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N13</t>
+          <t>UT-LIST-N10</t>
         </is>
       </c>
       <c r="B134" s="12" t="inlineStr">
@@ -13089,7 +13087,7 @@
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>お気に入り登録でお気に入り数が即座に1増える</t>
+          <t>詳細展開: 同じ行をもう一度押すと閉じる</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
@@ -13104,7 +13102,7 @@
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>お気に入り登録でお気に入り数が即座に1増える</t>
+          <t>詳細展開: 同じ行をもう一度押すと閉じる</t>
         </is>
       </c>
       <c r="H134" s="12" t="inlineStr">
@@ -13162,7 +13160,7 @@
     <row r="135" ht="27" customHeight="1">
       <c r="A135" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N14</t>
+          <t>UT-LIST-N11</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
@@ -13177,7 +13175,7 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>お気に入り解除でお気に入り数が即座に1減る</t>
+          <t>申込成功で申込完了画面へ遷移する</t>
         </is>
       </c>
       <c r="E135" s="12" t="inlineStr">
@@ -13192,7 +13190,7 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>お気に入り解除でお気に入り数が即座に1減る</t>
+          <t>申込成功で申込完了画面へ遷移する</t>
         </is>
       </c>
       <c r="H135" s="12" t="inlineStr">
@@ -13250,7 +13248,7 @@
     <row r="136" ht="27" customHeight="1">
       <c r="A136" s="12" t="inlineStr">
         <is>
-          <t>UT-LIST-N15</t>
+          <t>UT-LIST-N12</t>
         </is>
       </c>
       <c r="B136" s="12" t="inlineStr">
@@ -13265,7 +13263,7 @@
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>管理者の場合isAdminがtrueになる</t>
+          <t>お気に入りトグルでfavoriteStore.toggleを呼ぶ</t>
         </is>
       </c>
       <c r="E136" s="12" t="inlineStr">
@@ -13280,7 +13278,7 @@
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>管理者の場合isAdminがtrueになる</t>
+          <t>お気に入りトグルでfavoriteStore.toggleを呼ぶ</t>
         </is>
       </c>
       <c r="H136" s="12" t="inlineStr">
@@ -13338,12 +13336,12 @@
     <row r="137" ht="27" customHeight="1">
       <c r="A137" s="12" t="inlineStr">
         <is>
-          <t>UT-SRCH-N01</t>
+          <t>UT-LIST-N13</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>イベント検索（SC-021）</t>
+          <t>イベント一覧（SC-020）</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
@@ -13353,7 +13351,7 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>初期状態では開催日時昇順で全件を返す</t>
+          <t>お気に入り登録でお気に入り数が即座に1増える</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr">
@@ -13368,7 +13366,7 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>初期状態では開催日時昇順で全件を返す</t>
+          <t>お気に入り登録でお気に入り数が即座に1増える</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
@@ -13393,7 +13391,7 @@
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>events/event-search/event-search.spec.ts</t>
+          <t>events/event-list/event-list.spec.ts</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
@@ -13426,12 +13424,12 @@
     <row r="138" ht="27" customHeight="1">
       <c r="A138" s="12" t="inlineStr">
         <is>
-          <t>UT-SRCH-N02</t>
+          <t>UT-LIST-N14</t>
         </is>
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t>イベント検索（SC-021）</t>
+          <t>イベント一覧（SC-020）</t>
         </is>
       </c>
       <c r="C138" s="12" t="inlineStr">
@@ -13441,7 +13439,7 @@
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>キーワードでイベント名を絞り込む</t>
+          <t>お気に入り解除でお気に入り数が即座に1減る</t>
         </is>
       </c>
       <c r="E138" s="12" t="inlineStr">
@@ -13456,7 +13454,7 @@
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>キーワードでイベント名を絞り込む</t>
+          <t>お気に入り解除でお気に入り数が即座に1減る</t>
         </is>
       </c>
       <c r="H138" s="12" t="inlineStr">
@@ -13481,7 +13479,7 @@
       </c>
       <c r="L138" s="12" t="inlineStr">
         <is>
-          <t>events/event-search/event-search.spec.ts</t>
+          <t>events/event-list/event-list.spec.ts</t>
         </is>
       </c>
       <c r="M138" s="12" t="inlineStr">
@@ -13514,12 +13512,12 @@
     <row r="139" ht="27" customHeight="1">
       <c r="A139" s="12" t="inlineStr">
         <is>
-          <t>UT-SRCH-N03</t>
+          <t>UT-LIST-N15</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>イベント検索（SC-021）</t>
+          <t>イベント一覧（SC-020）</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
@@ -13529,7 +13527,7 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>キーワードで場所を絞り込む（大文字小文字を区別しない）</t>
+          <t>管理者の場合isAdminがtrueになる</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
@@ -13544,7 +13542,7 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>キーワードで場所を絞り込む（大文字小文字を区別しない）</t>
+          <t>管理者の場合isAdminがtrueになる</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
@@ -13569,7 +13567,7 @@
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>events/event-search/event-search.spec.ts</t>
+          <t>events/event-list/event-list.spec.ts</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
@@ -13602,7 +13600,7 @@
     <row r="140" ht="27" customHeight="1">
       <c r="A140" s="12" t="inlineStr">
         <is>
-          <t>UT-SRCH-N04</t>
+          <t>UT-SRCH-N01</t>
         </is>
       </c>
       <c r="B140" s="12" t="inlineStr">
@@ -13617,7 +13615,7 @@
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>開催日（から）で絞り込む</t>
+          <t>初期状態では開催日時昇順で全件を返す</t>
         </is>
       </c>
       <c r="E140" s="12" t="inlineStr">
@@ -13632,7 +13630,7 @@
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>開催日（から）で絞り込む</t>
+          <t>初期状態では開催日時昇順で全件を返す</t>
         </is>
       </c>
       <c r="H140" s="12" t="inlineStr">
@@ -13690,7 +13688,7 @@
     <row r="141" ht="27" customHeight="1">
       <c r="A141" s="12" t="inlineStr">
         <is>
-          <t>UT-SRCH-N05</t>
+          <t>UT-SRCH-N02</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
@@ -13705,7 +13703,7 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>開催日（まで）で絞り込む</t>
+          <t>キーワードでイベント名を絞り込む</t>
         </is>
       </c>
       <c r="E141" s="12" t="inlineStr">
@@ -13720,7 +13718,7 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>開催日（まで）で絞り込む</t>
+          <t>キーワードでイベント名を絞り込む</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
@@ -13778,7 +13776,7 @@
     <row r="142" ht="27" customHeight="1">
       <c r="A142" s="12" t="inlineStr">
         <is>
-          <t>UT-SRCH-N06</t>
+          <t>UT-SRCH-N03</t>
         </is>
       </c>
       <c r="B142" s="12" t="inlineStr">
@@ -13793,7 +13791,7 @@
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>開催日（から）と（まで）の両方を指定すると、その範囲で絞り込む</t>
+          <t>キーワードで場所を絞り込む（大文字小文字を区別しない）</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr">
@@ -13808,7 +13806,7 @@
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>開催日（から）と（まで）の両方を指定すると、その範囲で絞り込む</t>
+          <t>キーワードで場所を絞り込む（大文字小文字を区別しない）</t>
         </is>
       </c>
       <c r="H142" s="12" t="inlineStr">
@@ -13866,7 +13864,7 @@
     <row r="143" ht="27" customHeight="1">
       <c r="A143" s="12" t="inlineStr">
         <is>
-          <t>UT-SRCH-N07</t>
+          <t>UT-SRCH-N04</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
@@ -13881,7 +13879,7 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>条件をクリアすると絞り込みが解除される</t>
+          <t>開催日（から）で絞り込む</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
@@ -13896,7 +13894,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>条件をクリアすると絞り込みが解除される</t>
+          <t>開催日（から）で絞り込む</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
@@ -13954,7 +13952,7 @@
     <row r="144" ht="27" customHeight="1">
       <c r="A144" s="12" t="inlineStr">
         <is>
-          <t>UT-SRCH-N08</t>
+          <t>UT-SRCH-N05</t>
         </is>
       </c>
       <c r="B144" s="12" t="inlineStr">
@@ -13969,7 +13967,7 @@
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 開催済みのイベントは検索結果の末尾に並ぶ</t>
+          <t>開催日（まで）で絞り込む</t>
         </is>
       </c>
       <c r="E144" s="12" t="inlineStr">
@@ -13984,7 +13982,7 @@
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 開催済みのイベントは検索結果の末尾に並ぶ</t>
+          <t>開催日（まで）で絞り込む</t>
         </is>
       </c>
       <c r="H144" s="12" t="inlineStr">
@@ -14042,7 +14040,7 @@
     <row r="145" ht="27" customHeight="1">
       <c r="A145" s="12" t="inlineStr">
         <is>
-          <t>UT-SRCH-N09</t>
+          <t>UT-SRCH-N06</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
@@ -14057,7 +14055,7 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 絞り込んだ結果の中でも開催済みのイベントは末尾に並ぶ</t>
+          <t>開催日（から）と（まで）の両方を指定すると、その範囲で絞り込む</t>
         </is>
       </c>
       <c r="E145" s="12" t="inlineStr">
@@ -14072,7 +14070,7 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 絞り込んだ結果の中でも開催済みのイベントは末尾に並ぶ</t>
+          <t>開催日（から）と（まで）の両方を指定すると、その範囲で絞り込む</t>
         </is>
       </c>
       <c r="H145" s="12" t="inlineStr">
@@ -14130,7 +14128,7 @@
     <row r="146" ht="27" customHeight="1">
       <c r="A146" s="12" t="inlineStr">
         <is>
-          <t>UT-SRCH-N10</t>
+          <t>UT-SRCH-N07</t>
         </is>
       </c>
       <c r="B146" s="12" t="inlineStr">
@@ -14145,7 +14143,7 @@
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 申込数の多い順</t>
+          <t>条件をクリアすると絞り込みが解除される</t>
         </is>
       </c>
       <c r="E146" s="12" t="inlineStr">
@@ -14160,7 +14158,7 @@
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 申込数の多い順</t>
+          <t>条件をクリアすると絞り込みが解除される</t>
         </is>
       </c>
       <c r="H146" s="12" t="inlineStr">
@@ -14218,7 +14216,7 @@
     <row r="147" ht="27" customHeight="1">
       <c r="A147" s="12" t="inlineStr">
         <is>
-          <t>UT-SRCH-N11</t>
+          <t>UT-SRCH-N08</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
@@ -14233,7 +14231,7 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>並び替え: お気に入り数の多い順</t>
+          <t>並び替え: 開催済みのイベントは検索結果の末尾に並ぶ</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr">
@@ -14248,7 +14246,7 @@
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>並び替え: お気に入り数の多い順</t>
+          <t>並び替え: 開催済みのイベントは検索結果の末尾に並ぶ</t>
         </is>
       </c>
       <c r="H147" s="12" t="inlineStr">
@@ -14306,7 +14304,7 @@
     <row r="148" ht="27" customHeight="1">
       <c r="A148" s="12" t="inlineStr">
         <is>
-          <t>UT-SRCH-N12</t>
+          <t>UT-SRCH-N09</t>
         </is>
       </c>
       <c r="B148" s="12" t="inlineStr">
@@ -14321,7 +14319,7 @@
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 申込締切が近い順</t>
+          <t>並び替え: 絞り込んだ結果の中でも開催済みのイベントは末尾に並ぶ</t>
         </is>
       </c>
       <c r="E148" s="12" t="inlineStr">
@@ -14336,7 +14334,7 @@
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>並び替え: 申込締切が近い順</t>
+          <t>並び替え: 絞り込んだ結果の中でも開催済みのイベントは末尾に並ぶ</t>
         </is>
       </c>
       <c r="H148" s="12" t="inlineStr">
@@ -14394,12 +14392,12 @@
     <row r="149" ht="27" customHeight="1">
       <c r="A149" s="12" t="inlineStr">
         <is>
-          <t>UT-MY-N01</t>
+          <t>UT-SRCH-N10</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>マイページ（SC-030）</t>
+          <t>イベント検索（SC-021）</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
@@ -14409,7 +14407,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>初期表示で申込一覧を取得する</t>
+          <t>並び替え: 申込数の多い順</t>
         </is>
       </c>
       <c r="E149" s="12" t="inlineStr">
@@ -14424,7 +14422,7 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>初期表示で申込一覧を取得する</t>
+          <t>並び替え: 申込数の多い順</t>
         </is>
       </c>
       <c r="H149" s="12" t="inlineStr">
@@ -14449,7 +14447,7 @@
       </c>
       <c r="L149" s="12" t="inlineStr">
         <is>
-          <t>my-applications/my-applications.spec.ts</t>
+          <t>events/event-search/event-search.spec.ts</t>
         </is>
       </c>
       <c r="M149" s="12" t="inlineStr">
@@ -14482,12 +14480,12 @@
     <row r="150" ht="27" customHeight="1">
       <c r="A150" s="12" t="inlineStr">
         <is>
-          <t>UT-MY-N02</t>
+          <t>UT-SRCH-N11</t>
         </is>
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t>マイページ（SC-030）</t>
+          <t>イベント検索（SC-021）</t>
         </is>
       </c>
       <c r="C150" s="12" t="inlineStr">
@@ -14497,7 +14495,7 @@
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>初期表示でお気に入り一覧を取得する</t>
+          <t>並び替え: お気に入り数の多い順</t>
         </is>
       </c>
       <c r="E150" s="12" t="inlineStr">
@@ -14512,7 +14510,7 @@
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
-          <t>初期表示でお気に入り一覧を取得する</t>
+          <t>並び替え: お気に入り数の多い順</t>
         </is>
       </c>
       <c r="H150" s="12" t="inlineStr">
@@ -14537,7 +14535,7 @@
       </c>
       <c r="L150" s="12" t="inlineStr">
         <is>
-          <t>my-applications/my-applications.spec.ts</t>
+          <t>events/event-search/event-search.spec.ts</t>
         </is>
       </c>
       <c r="M150" s="12" t="inlineStr">
@@ -14570,12 +14568,12 @@
     <row r="151" ht="27" customHeight="1">
       <c r="A151" s="12" t="inlineStr">
         <is>
-          <t>UT-MY-N03</t>
+          <t>UT-SRCH-N12</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>マイページ（SC-030）</t>
+          <t>イベント検索（SC-021）</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
@@ -14585,7 +14583,7 @@
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>タブ切替でactiveTabが切り替わる</t>
+          <t>並び替え: 申込締切が近い順</t>
         </is>
       </c>
       <c r="E151" s="12" t="inlineStr">
@@ -14600,7 +14598,7 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>タブ切替でactiveTabが切り替わる</t>
+          <t>並び替え: 申込締切が近い順</t>
         </is>
       </c>
       <c r="H151" s="12" t="inlineStr">
@@ -14625,7 +14623,7 @@
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>my-applications/my-applications.spec.ts</t>
+          <t>events/event-search/event-search.spec.ts</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
@@ -14658,7 +14656,7 @@
     <row r="152" ht="27" customHeight="1">
       <c r="A152" s="12" t="inlineStr">
         <is>
-          <t>UT-MY-N04</t>
+          <t>UT-MY-N01</t>
         </is>
       </c>
       <c r="B152" s="12" t="inlineStr">
@@ -14673,7 +14671,7 @@
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>キャンセル確認でOKした場合、APIを呼び一覧を再取得する</t>
+          <t>初期表示で申込一覧を取得する</t>
         </is>
       </c>
       <c r="E152" s="12" t="inlineStr">
@@ -14688,7 +14686,7 @@
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>キャンセル確認でOKした場合、APIを呼び一覧を再取得する</t>
+          <t>初期表示で申込一覧を取得する</t>
         </is>
       </c>
       <c r="H152" s="12" t="inlineStr">
@@ -14746,7 +14744,7 @@
     <row r="153" ht="27" customHeight="1">
       <c r="A153" s="12" t="inlineStr">
         <is>
-          <t>UT-MY-N05</t>
+          <t>UT-MY-N02</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
@@ -14761,7 +14759,7 @@
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>キャンセル確認でキャンセルした場合、APIを呼ばない</t>
+          <t>初期表示でお気に入り一覧を取得する</t>
         </is>
       </c>
       <c r="E153" s="12" t="inlineStr">
@@ -14776,7 +14774,7 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>キャンセル確認でキャンセルした場合、APIを呼ばない</t>
+          <t>初期表示でお気に入り一覧を取得する</t>
         </is>
       </c>
       <c r="H153" s="12" t="inlineStr">
@@ -14834,7 +14832,7 @@
     <row r="154" ht="27" customHeight="1">
       <c r="A154" s="12" t="inlineStr">
         <is>
-          <t>UT-MY-N06</t>
+          <t>UT-MY-N03</t>
         </is>
       </c>
       <c r="B154" s="12" t="inlineStr">
@@ -14849,7 +14847,7 @@
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>お気に入り解除でAPIを呼び、ストアを無効化してから一覧を再取得する</t>
+          <t>タブ切替でactiveTabが切り替わる</t>
         </is>
       </c>
       <c r="E154" s="12" t="inlineStr">
@@ -14864,7 +14862,7 @@
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>お気に入り解除でAPIを呼び、ストアを無効化してから一覧を再取得する</t>
+          <t>タブ切替でactiveTabが切り替わる</t>
         </is>
       </c>
       <c r="H154" s="12" t="inlineStr">
@@ -14922,7 +14920,7 @@
     <row r="155" ht="27" customHeight="1">
       <c r="A155" s="12" t="inlineStr">
         <is>
-          <t>UT-MY-E01</t>
+          <t>UT-MY-N04</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
@@ -14932,12 +14930,12 @@
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>異常系</t>
+          <t>正常系</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>申込一覧の取得に失敗した場合はエラーメッセージを表示する</t>
+          <t>キャンセル確認でOKした場合、APIを呼び一覧を再取得する</t>
         </is>
       </c>
       <c r="E155" s="12" t="inlineStr">
@@ -14952,7 +14950,7 @@
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>申込一覧の取得に失敗した場合はエラーメッセージを表示する</t>
+          <t>キャンセル確認でOKした場合、APIを呼び一覧を再取得する</t>
         </is>
       </c>
       <c r="H155" s="12" t="inlineStr">
@@ -15010,12 +15008,12 @@
     <row r="156" ht="27" customHeight="1">
       <c r="A156" s="12" t="inlineStr">
         <is>
-          <t>UT-ORD-N01</t>
+          <t>UT-MY-N05</t>
         </is>
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t>開催済みのイベントを末尾に並べる共通処理</t>
+          <t>マイページ（SC-030）</t>
         </is>
       </c>
       <c r="C156" s="12" t="inlineStr">
@@ -15025,7 +15023,7 @@
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>isHeld: 開催日時が現在時刻より前なら開催済み</t>
+          <t>キャンセル確認でキャンセルした場合、APIを呼ばない</t>
         </is>
       </c>
       <c r="E156" s="12" t="inlineStr">
@@ -15040,7 +15038,7 @@
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>isHeld: 開催日時が現在時刻より前なら開催済み</t>
+          <t>キャンセル確認でキャンセルした場合、APIを呼ばない</t>
         </is>
       </c>
       <c r="H156" s="12" t="inlineStr">
@@ -15065,7 +15063,7 @@
       </c>
       <c r="L156" s="12" t="inlineStr">
         <is>
-          <t>core/event-order.spec.ts</t>
+          <t>my-applications/my-applications.spec.ts</t>
         </is>
       </c>
       <c r="M156" s="12" t="inlineStr">
@@ -15098,12 +15096,12 @@
     <row r="157" ht="27" customHeight="1">
       <c r="A157" s="12" t="inlineStr">
         <is>
-          <t>UT-ORD-N02</t>
+          <t>UT-MY-N06</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>開催済みのイベントを末尾に並べる共通処理</t>
+          <t>マイページ（SC-030）</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
@@ -15113,7 +15111,7 @@
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>isHeld: 開催日時が現在時刻ちょうどなら開催済み（境界）</t>
+          <t>お気に入り解除でAPIを呼び、ストアを無効化してから一覧を再取得する</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
@@ -15128,7 +15126,7 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>isHeld: 開催日時が現在時刻ちょうどなら開催済み（境界）</t>
+          <t>お気に入り解除でAPIを呼び、ストアを無効化してから一覧を再取得する</t>
         </is>
       </c>
       <c r="H157" s="12" t="inlineStr">
@@ -15153,7 +15151,7 @@
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
-          <t>core/event-order.spec.ts</t>
+          <t>my-applications/my-applications.spec.ts</t>
         </is>
       </c>
       <c r="M157" s="12" t="inlineStr">
@@ -15186,22 +15184,22 @@
     <row r="158" ht="27" customHeight="1">
       <c r="A158" s="12" t="inlineStr">
         <is>
-          <t>UT-ORD-N03</t>
+          <t>UT-MY-E01</t>
         </is>
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t>開催済みのイベントを末尾に並べる共通処理</t>
+          <t>マイページ（SC-030）</t>
         </is>
       </c>
       <c r="C158" s="12" t="inlineStr">
         <is>
-          <t>正常系</t>
+          <t>異常系</t>
         </is>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>isHeld: 開催日時が現在時刻より後なら開催前</t>
+          <t>申込一覧の取得に失敗した場合はエラーメッセージを表示する</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
@@ -15216,7 +15214,7 @@
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
-          <t>isHeld: 開催日時が現在時刻より後なら開催前</t>
+          <t>申込一覧の取得に失敗した場合はエラーメッセージを表示する</t>
         </is>
       </c>
       <c r="H158" s="12" t="inlineStr">
@@ -15241,7 +15239,7 @@
       </c>
       <c r="L158" s="12" t="inlineStr">
         <is>
-          <t>core/event-order.spec.ts</t>
+          <t>my-applications/my-applications.spec.ts</t>
         </is>
       </c>
       <c r="M158" s="12" t="inlineStr">
@@ -15274,7 +15272,7 @@
     <row r="159" ht="27" customHeight="1">
       <c r="A159" s="12" t="inlineStr">
         <is>
-          <t>UT-ORD-N04</t>
+          <t>UT-ORD-N01</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
@@ -15289,7 +15287,7 @@
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>moveHeldEventsLast: 開催済みを末尾に移し、それぞれの中の順序は保つ</t>
+          <t>isHeld: 開催日時が現在時刻より前なら開催済み</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr">
@@ -15304,7 +15302,7 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>moveHeldEventsLast: 開催済みを末尾に移し、それぞれの中の順序は保つ</t>
+          <t>isHeld: 開催日時が現在時刻より前なら開催済み</t>
         </is>
       </c>
       <c r="H159" s="12" t="inlineStr">
@@ -15362,7 +15360,7 @@
     <row r="160" ht="27" customHeight="1">
       <c r="A160" s="12" t="inlineStr">
         <is>
-          <t>UT-ORD-N05</t>
+          <t>UT-ORD-N02</t>
         </is>
       </c>
       <c r="B160" s="12" t="inlineStr">
@@ -15377,7 +15375,7 @@
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>moveHeldEventsLast: 開催済みが無ければ順序は変わらない</t>
+          <t>isHeld: 開催日時が現在時刻ちょうどなら開催済み（境界）</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
@@ -15392,7 +15390,7 @@
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>moveHeldEventsLast: 開催済みが無ければ順序は変わらない</t>
+          <t>isHeld: 開催日時が現在時刻ちょうどなら開催済み（境界）</t>
         </is>
       </c>
       <c r="H160" s="12" t="inlineStr">
@@ -15450,7 +15448,7 @@
     <row r="161" ht="27" customHeight="1">
       <c r="A161" s="12" t="inlineStr">
         <is>
-          <t>UT-ORD-N06</t>
+          <t>UT-ORD-N03</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
@@ -15465,7 +15463,7 @@
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>moveHeldEventsLast: 渡された配列そのものは変更せず、新しい配列を返す</t>
+          <t>isHeld: 開催日時が現在時刻より後なら開催前</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr">
@@ -15480,7 +15478,7 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>moveHeldEventsLast: 渡された配列そのものは変更せず、新しい配列を返す</t>
+          <t>isHeld: 開催日時が現在時刻より後なら開催前</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr">
@@ -15538,7 +15536,7 @@
     <row r="162" ht="27" customHeight="1">
       <c r="A162" s="12" t="inlineStr">
         <is>
-          <t>UT-ORD-N07</t>
+          <t>UT-ORD-N04</t>
         </is>
       </c>
       <c r="B162" s="12" t="inlineStr">
@@ -15553,7 +15551,7 @@
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>moveHeldEventsLast: すべて開催済みの場合は順序を変えずに返す</t>
+          <t>moveHeldEventsLast: 開催済みを末尾に移し、それぞれの中の順序は保つ</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
@@ -15568,7 +15566,7 @@
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>moveHeldEventsLast: すべて開催済みの場合は順序を変えずに返す</t>
+          <t>moveHeldEventsLast: 開催済みを末尾に移し、それぞれの中の順序は保つ</t>
         </is>
       </c>
       <c r="H162" s="12" t="inlineStr">
@@ -15626,7 +15624,7 @@
     <row r="163" ht="27" customHeight="1">
       <c r="A163" s="12" t="inlineStr">
         <is>
-          <t>UT-ORD-N08</t>
+          <t>UT-ORD-N05</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
@@ -15641,7 +15639,7 @@
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>moveHeldEventsLast: 空の配列を渡すと空の配列を返す</t>
+          <t>moveHeldEventsLast: 開催済みが無ければ順序は変わらない</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr">
@@ -15656,7 +15654,7 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>moveHeldEventsLast: 空の配列を渡すと空の配列を返す</t>
+          <t>moveHeldEventsLast: 開催済みが無ければ順序は変わらない</t>
         </is>
       </c>
       <c r="H163" s="12" t="inlineStr">
@@ -15714,12 +15712,12 @@
     <row r="164" ht="27" customHeight="1">
       <c r="A164" s="12" t="inlineStr">
         <is>
-          <t>UT-TREE-N01</t>
+          <t>UT-ORD-N06</t>
         </is>
       </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t>コメントを返信の木構造に組み立てる処理</t>
+          <t>開催済みのイベントを末尾に並べる共通処理</t>
         </is>
       </c>
       <c r="C164" s="12" t="inlineStr">
@@ -15729,7 +15727,7 @@
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>親を持たないコメントはすべてルートになる</t>
+          <t>moveHeldEventsLast: 渡された配列そのものは変更せず、新しい配列を返す</t>
         </is>
       </c>
       <c r="E164" s="12" t="inlineStr">
@@ -15744,7 +15742,7 @@
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
-          <t>親を持たないコメントはすべてルートになる</t>
+          <t>moveHeldEventsLast: 渡された配列そのものは変更せず、新しい配列を返す</t>
         </is>
       </c>
       <c r="H164" s="12" t="inlineStr">
@@ -15769,7 +15767,7 @@
       </c>
       <c r="L164" s="12" t="inlineStr">
         <is>
-          <t>core/comment-api.spec.ts</t>
+          <t>core/event-order.spec.ts</t>
         </is>
       </c>
       <c r="M164" s="12" t="inlineStr">
@@ -15802,12 +15800,12 @@
     <row r="165" ht="27" customHeight="1">
       <c r="A165" s="12" t="inlineStr">
         <is>
-          <t>UT-TREE-N02</t>
+          <t>UT-ORD-N07</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>コメントを返信の木構造に組み立てる処理</t>
+          <t>開催済みのイベントを末尾に並べる共通処理</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
@@ -15817,7 +15815,7 @@
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>parentCommentIdで指定した親の子として組み立てる</t>
+          <t>moveHeldEventsLast: すべて開催済みの場合は順序を変えずに返す</t>
         </is>
       </c>
       <c r="E165" s="12" t="inlineStr">
@@ -15832,7 +15830,7 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>parentCommentIdで指定した親の子として組み立てる</t>
+          <t>moveHeldEventsLast: すべて開催済みの場合は順序を変えずに返す</t>
         </is>
       </c>
       <c r="H165" s="12" t="inlineStr">
@@ -15857,7 +15855,7 @@
       </c>
       <c r="L165" s="12" t="inlineStr">
         <is>
-          <t>core/comment-api.spec.ts</t>
+          <t>core/event-order.spec.ts</t>
         </is>
       </c>
       <c r="M165" s="12" t="inlineStr">
@@ -15890,12 +15888,12 @@
     <row r="166" ht="27" customHeight="1">
       <c r="A166" s="12" t="inlineStr">
         <is>
-          <t>UT-TREE-N03</t>
+          <t>UT-ORD-N08</t>
         </is>
       </c>
       <c r="B166" s="12" t="inlineStr">
         <is>
-          <t>コメントを返信の木構造に組み立てる処理</t>
+          <t>開催済みのイベントを末尾に並べる共通処理</t>
         </is>
       </c>
       <c r="C166" s="12" t="inlineStr">
@@ -15905,7 +15903,7 @@
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>返信の階層数に制限が無く、何階層でも入れ子にできる</t>
+          <t>moveHeldEventsLast: 空の配列を渡すと空の配列を返す</t>
         </is>
       </c>
       <c r="E166" s="12" t="inlineStr">
@@ -15920,7 +15918,7 @@
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
-          <t>返信の階層数に制限が無く、何階層でも入れ子にできる</t>
+          <t>moveHeldEventsLast: 空の配列を渡すと空の配列を返す</t>
         </is>
       </c>
       <c r="H166" s="12" t="inlineStr">
@@ -15945,7 +15943,7 @@
       </c>
       <c r="L166" s="12" t="inlineStr">
         <is>
-          <t>core/comment-api.spec.ts</t>
+          <t>core/event-order.spec.ts</t>
         </is>
       </c>
       <c r="M166" s="12" t="inlineStr">
@@ -15978,7 +15976,7 @@
     <row r="167" ht="27" customHeight="1">
       <c r="A167" s="12" t="inlineStr">
         <is>
-          <t>UT-TREE-N04</t>
+          <t>UT-TREE-N01</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
@@ -15993,7 +15991,7 @@
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>1つの親に複数の返信がある場合、すべて子として並ぶ</t>
+          <t>親を持たないコメントはすべてルートになる</t>
         </is>
       </c>
       <c r="E167" s="12" t="inlineStr">
@@ -16008,7 +16006,7 @@
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>1つの親に複数の返信がある場合、すべて子として並ぶ</t>
+          <t>親を持たないコメントはすべてルートになる</t>
         </is>
       </c>
       <c r="H167" s="12" t="inlineStr">
@@ -16066,7 +16064,7 @@
     <row r="168" ht="27" customHeight="1">
       <c r="A168" s="12" t="inlineStr">
         <is>
-          <t>UT-TREE-N05</t>
+          <t>UT-TREE-N02</t>
         </is>
       </c>
       <c r="B168" s="12" t="inlineStr">
@@ -16081,7 +16079,7 @@
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>削除済み（deleted: true）のコメントも、返信の親としてそのままツリーに残る</t>
+          <t>parentCommentIdで指定した親の子として組み立てる</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr">
@@ -16096,7 +16094,7 @@
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
-          <t>削除済み（deleted: true）のコメントも、返信の親としてそのままツリーに残る</t>
+          <t>parentCommentIdで指定した親の子として組み立てる</t>
         </is>
       </c>
       <c r="H168" s="12" t="inlineStr">
@@ -16154,12 +16152,12 @@
     <row r="169" ht="27" customHeight="1">
       <c r="A169" s="12" t="inlineStr">
         <is>
-          <t>UT-AUTHG-N01</t>
+          <t>UT-TREE-N03</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>未ログインでの画面遷移の制御（authGuard）</t>
+          <t>コメントを返信の木構造に組み立てる処理</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
@@ -16169,7 +16167,7 @@
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>ログイン中は通過させる（true）</t>
+          <t>返信の階層数に制限が無く、何階層でも入れ子にできる</t>
         </is>
       </c>
       <c r="E169" s="12" t="inlineStr">
@@ -16184,7 +16182,7 @@
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>ログイン中は通過させる（true）</t>
+          <t>返信の階層数に制限が無く、何階層でも入れ子にできる</t>
         </is>
       </c>
       <c r="H169" s="12" t="inlineStr">
@@ -16209,7 +16207,7 @@
       </c>
       <c r="L169" s="12" t="inlineStr">
         <is>
-          <t>core/auth-guard.spec.ts</t>
+          <t>core/comment-api.spec.ts</t>
         </is>
       </c>
       <c r="M169" s="12" t="inlineStr">
@@ -16242,22 +16240,22 @@
     <row r="170" ht="27" customHeight="1">
       <c r="A170" s="12" t="inlineStr">
         <is>
-          <t>UT-AUTHG-E01</t>
+          <t>UT-TREE-N04</t>
         </is>
       </c>
       <c r="B170" s="12" t="inlineStr">
         <is>
-          <t>未ログインでの画面遷移の制御（authGuard）</t>
+          <t>コメントを返信の木構造に組み立てる処理</t>
         </is>
       </c>
       <c r="C170" s="12" t="inlineStr">
         <is>
-          <t>異常系</t>
+          <t>正常系</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>未ログインの場合はログイン画面へのUrlTreeを返す</t>
+          <t>1つの親に複数の返信がある場合、すべて子として並ぶ</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr">
@@ -16272,7 +16270,7 @@
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>未ログインの場合はログイン画面へのUrlTreeを返す</t>
+          <t>1つの親に複数の返信がある場合、すべて子として並ぶ</t>
         </is>
       </c>
       <c r="H170" s="12" t="inlineStr">
@@ -16297,7 +16295,7 @@
       </c>
       <c r="L170" s="12" t="inlineStr">
         <is>
-          <t>core/auth-guard.spec.ts</t>
+          <t>core/comment-api.spec.ts</t>
         </is>
       </c>
       <c r="M170" s="12" t="inlineStr">
@@ -16330,12 +16328,12 @@
     <row r="171" ht="27" customHeight="1">
       <c r="A171" s="12" t="inlineStr">
         <is>
-          <t>UT-ADMG-N01</t>
+          <t>UT-TREE-N05</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>管理者向け画面への遷移の制御（adminGuard）</t>
+          <t>コメントを返信の木構造に組み立てる処理</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
@@ -16345,7 +16343,7 @@
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>管理者（利用者区分コード＝管理者）は通過させる（true）</t>
+          <t>削除済み（deleted: true）のコメントも、返信の親としてそのままツリーに残る</t>
         </is>
       </c>
       <c r="E171" s="12" t="inlineStr">
@@ -16360,7 +16358,7 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>管理者（利用者区分コード＝管理者）は通過させる（true）</t>
+          <t>削除済み（deleted: true）のコメントも、返信の親としてそのままツリーに残る</t>
         </is>
       </c>
       <c r="H171" s="12" t="inlineStr">
@@ -16385,7 +16383,7 @@
       </c>
       <c r="L171" s="12" t="inlineStr">
         <is>
-          <t>core/admin-guard.spec.ts</t>
+          <t>core/comment-api.spec.ts</t>
         </is>
       </c>
       <c r="M171" s="12" t="inlineStr">
@@ -16418,22 +16416,22 @@
     <row r="172" ht="40.5" customHeight="1">
       <c r="A172" s="12" t="inlineStr">
         <is>
-          <t>UT-ADMG-E01</t>
+          <t>UT-AUTHG-N01</t>
         </is>
       </c>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t>管理者向け画面への遷移の制御（adminGuard）</t>
+          <t>未ログインでの画面遷移の制御（authGuard）</t>
         </is>
       </c>
       <c r="C172" s="12" t="inlineStr">
         <is>
-          <t>異常系</t>
+          <t>正常系</t>
         </is>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>一般利用者（利用者区分コード＝一般利用者）はイベント一覧へのUrlTreeを返す（利用者区分コード基準の判定）</t>
+          <t>ログイン中は通過させる（true）</t>
         </is>
       </c>
       <c r="E172" s="12" t="inlineStr">
@@ -16448,7 +16446,7 @@
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
-          <t>一般利用者（利用者区分コード＝一般利用者）はイベント一覧へのUrlTreeを返す（利用者区分コード基準の判定）</t>
+          <t>ログイン中は通過させる（true）</t>
         </is>
       </c>
       <c r="H172" s="12" t="inlineStr">
@@ -16473,7 +16471,7 @@
       </c>
       <c r="L172" s="12" t="inlineStr">
         <is>
-          <t>core/admin-guard.spec.ts</t>
+          <t>core/auth-guard.spec.ts</t>
         </is>
       </c>
       <c r="M172" s="12" t="inlineStr">
@@ -16506,12 +16504,12 @@
     <row r="173" ht="54" customHeight="1">
       <c r="A173" s="12" t="inlineStr">
         <is>
-          <t>UT-HTTP-E01</t>
+          <t>UT-AUTHG-E01</t>
         </is>
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>API呼び出しのエラーの共通処理（httpErrorInterceptor）</t>
+          <t>未ログインでの画面遷移の制御（authGuard）</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
@@ -16521,7 +16519,7 @@
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>401を受け取るとログイン状態を解除してログイン画面へ遷移し、エラーは呼び出し元にも伝える</t>
+          <t>未ログインの場合はログイン画面へのUrlTreeを返す</t>
         </is>
       </c>
       <c r="E173" s="12" t="inlineStr">
@@ -16536,7 +16534,7 @@
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>401を受け取るとログイン状態を解除してログイン画面へ遷移し、エラーは呼び出し元にも伝える</t>
+          <t>未ログインの場合はログイン画面へのUrlTreeを返す</t>
         </is>
       </c>
       <c r="H173" s="12" t="inlineStr">
@@ -16561,7 +16559,7 @@
       </c>
       <c r="L173" s="12" t="inlineStr">
         <is>
-          <t>core/http-error-interceptor.spec.ts</t>
+          <t>core/auth-guard.spec.ts</t>
         </is>
       </c>
       <c r="M173" s="12" t="inlineStr">
@@ -16594,22 +16592,22 @@
     <row r="174" ht="54" customHeight="1">
       <c r="A174" s="12" t="inlineStr">
         <is>
-          <t>UT-HTTP-E02</t>
+          <t>UT-ADMG-N01</t>
         </is>
       </c>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t>API呼び出しのエラーの共通処理（httpErrorInterceptor）</t>
+          <t>管理者向け画面への遷移の制御（adminGuard）</t>
         </is>
       </c>
       <c r="C174" s="12" t="inlineStr">
         <is>
-          <t>異常系</t>
+          <t>正常系</t>
         </is>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>ログインAPIの401（メールアドレス・パスワードの誤り）ではログイン状態を変えず遷移もしない</t>
+          <t>管理者（利用者区分コード＝管理者）は通過させる（true）</t>
         </is>
       </c>
       <c r="E174" s="12" t="inlineStr">
@@ -16624,7 +16622,7 @@
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
-          <t>ログインAPIの401（メールアドレス・パスワードの誤り）ではログイン状態を変えず遷移もしない</t>
+          <t>管理者（利用者区分コード＝管理者）は通過させる（true）</t>
         </is>
       </c>
       <c r="H174" s="12" t="inlineStr">
@@ -16649,7 +16647,7 @@
       </c>
       <c r="L174" s="12" t="inlineStr">
         <is>
-          <t>core/http-error-interceptor.spec.ts</t>
+          <t>core/admin-guard.spec.ts</t>
         </is>
       </c>
       <c r="M174" s="12" t="inlineStr">
@@ -16682,12 +16680,12 @@
     <row r="175" ht="54" customHeight="1">
       <c r="A175" s="12" t="inlineStr">
         <is>
-          <t>UT-HTTP-E03</t>
+          <t>UT-ADMG-E01</t>
         </is>
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t>API呼び出しのエラーの共通処理（httpErrorInterceptor）</t>
+          <t>管理者向け画面への遷移の制御（adminGuard）</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
@@ -16697,7 +16695,7 @@
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>403（権限エラー）ではログイン状態を変えず遷移もしない</t>
+          <t>一般利用者（利用者区分コード＝一般利用者）はイベント一覧へのUrlTreeを返す（利用者区分コード基準の判定）</t>
         </is>
       </c>
       <c r="E175" s="12" t="inlineStr">
@@ -16712,7 +16710,7 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>403（権限エラー）ではログイン状態を変えず遷移もしない</t>
+          <t>一般利用者（利用者区分コード＝一般利用者）はイベント一覧へのUrlTreeを返す（利用者区分コード基準の判定）</t>
         </is>
       </c>
       <c r="H175" s="12" t="inlineStr">
@@ -16737,7 +16735,7 @@
       </c>
       <c r="L175" s="12" t="inlineStr">
         <is>
-          <t>core/http-error-interceptor.spec.ts</t>
+          <t>core/admin-guard.spec.ts</t>
         </is>
       </c>
       <c r="M175" s="12" t="inlineStr">
@@ -16770,7 +16768,7 @@
     <row r="176" ht="54" customHeight="1">
       <c r="A176" s="12" t="inlineStr">
         <is>
-          <t>UT-HTTP-E04</t>
+          <t>UT-HTTP-E01</t>
         </is>
       </c>
       <c r="B176" s="12" t="inlineStr">
@@ -16785,7 +16783,7 @@
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>サーバーに接続できない場合（status 0）は共通のメッセージに置き換える</t>
+          <t>401を受け取るとログイン状態を解除してログイン画面へ遷移し、エラーは呼び出し元にも伝える</t>
         </is>
       </c>
       <c r="E176" s="12" t="inlineStr">
@@ -16800,7 +16798,7 @@
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
-          <t>サーバーに接続できない場合（status 0）は共通のメッセージに置き換える</t>
+          <t>401を受け取るとログイン状態を解除してログイン画面へ遷移し、エラーは呼び出し元にも伝える</t>
         </is>
       </c>
       <c r="H176" s="12" t="inlineStr">
@@ -16858,12 +16856,12 @@
     <row r="177" ht="40.5" customHeight="1">
       <c r="A177" s="12" t="inlineStr">
         <is>
-          <t>UT-APP-E15</t>
+          <t>UT-HTTP-E02</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>ApplicationService（申込・キャンセル・当日受付）</t>
+          <t>API呼び出しのエラーの共通処理（httpErrorInterceptor）</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
@@ -16873,22 +16871,22 @@
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>区分の無いイベントに区分を指定すると指定された区分が見つかりませんで拒否される</t>
+          <t>ログインAPIの401（メールアドレス・パスワードの誤り）ではログイン状態を変えず遷移もしない</t>
         </is>
       </c>
       <c r="E177" s="12" t="inlineStr">
         <is>
-          <t>区分なしイベントでticketTypeIdを指定</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
-          <t>apply</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>NotFoundException「指定された区分が見つかりません」（E-B-005）</t>
+          <t>ログインAPIの401（メールアドレス・パスワードの誤り）ではログイン状態を変えず遷移もしない</t>
         </is>
       </c>
       <c r="H177" s="12" t="inlineStr">
@@ -16903,7 +16901,7 @@
       </c>
       <c r="J177" s="12" t="inlineStr">
         <is>
-          <t>32_処理詳細設計書 4章 AP-030 No.7</t>
+          <t>30_画面詳細設計書</t>
         </is>
       </c>
       <c r="K177" s="12" t="inlineStr">
@@ -16913,7 +16911,7 @@
       </c>
       <c r="L177" s="12" t="inlineStr">
         <is>
-          <t>apply_異常系_区分の無いイベントに区分を指定すると指定された区分が見つかりませんで拒否される</t>
+          <t>core/http-error-interceptor.spec.ts</t>
         </is>
       </c>
       <c r="M177" s="12" t="inlineStr">
@@ -16922,7 +16920,7 @@
         </is>
       </c>
       <c r="N177" s="23" t="n">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="O177" s="12" t="inlineStr">
         <is>
@@ -16931,21 +16929,285 @@
       </c>
       <c r="P177" s="12" t="inlineStr">
         <is>
-          <t>自動テスト成功（Issue #18 の修正で追加）</t>
+          <t>自動テスト成功</t>
         </is>
       </c>
       <c r="Q177" s="12" t="inlineStr">
         <is>
-          <t>evidence/UT/UT_バックエンド_結果一覧_20261009.txt</t>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
         </is>
       </c>
       <c r="R177" s="12" t="n"/>
       <c r="S177" s="12" t="n"/>
       <c r="T177" s="12" t="n"/>
     </row>
+    <row r="178">
+      <c r="A178" s="12" t="inlineStr">
+        <is>
+          <t>UT-HTTP-E03</t>
+        </is>
+      </c>
+      <c r="B178" s="12" t="inlineStr">
+        <is>
+          <t>API呼び出しのエラーの共通処理（httpErrorInterceptor）</t>
+        </is>
+      </c>
+      <c r="C178" s="12" t="inlineStr">
+        <is>
+          <t>異常系</t>
+        </is>
+      </c>
+      <c r="D178" s="12" t="inlineStr">
+        <is>
+          <t>403（権限エラー）ではログイン状態を変えず遷移もしない</t>
+        </is>
+      </c>
+      <c r="E178" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G178" s="12" t="inlineStr">
+        <is>
+          <t>403（権限エラー）ではログイン状態を変えず遷移もしない</t>
+        </is>
+      </c>
+      <c r="H178" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J178" s="12" t="inlineStr">
+        <is>
+          <t>30_画面詳細設計書</t>
+        </is>
+      </c>
+      <c r="K178" s="12" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="L178" s="12" t="inlineStr">
+        <is>
+          <t>core/http-error-interceptor.spec.ts</t>
+        </is>
+      </c>
+      <c r="M178" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N178" s="23" t="n">
+        <v>46302</v>
+      </c>
+      <c r="O178" s="12" t="inlineStr">
+        <is>
+          <t>佐々木（Claude Code）</t>
+        </is>
+      </c>
+      <c r="P178" s="12" t="inlineStr">
+        <is>
+          <t>自動テスト成功</t>
+        </is>
+      </c>
+      <c r="Q178" s="12" t="inlineStr">
+        <is>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
+        </is>
+      </c>
+      <c r="R178" s="12" t="n"/>
+      <c r="S178" s="12" t="n"/>
+      <c r="T178" s="12" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="12" t="inlineStr">
+        <is>
+          <t>UT-HTTP-E04</t>
+        </is>
+      </c>
+      <c r="B179" s="12" t="inlineStr">
+        <is>
+          <t>API呼び出しのエラーの共通処理（httpErrorInterceptor）</t>
+        </is>
+      </c>
+      <c r="C179" s="12" t="inlineStr">
+        <is>
+          <t>異常系</t>
+        </is>
+      </c>
+      <c r="D179" s="12" t="inlineStr">
+        <is>
+          <t>サーバーに接続できない場合（status 0）は共通のメッセージに置き換える</t>
+        </is>
+      </c>
+      <c r="E179" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G179" s="12" t="inlineStr">
+        <is>
+          <t>サーバーに接続できない場合（status 0）は共通のメッセージに置き換える</t>
+        </is>
+      </c>
+      <c r="H179" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" s="12" t="inlineStr">
+        <is>
+          <t>30_画面詳細設計書</t>
+        </is>
+      </c>
+      <c r="K179" s="12" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="L179" s="12" t="inlineStr">
+        <is>
+          <t>core/http-error-interceptor.spec.ts</t>
+        </is>
+      </c>
+      <c r="M179" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N179" s="23" t="n">
+        <v>46302</v>
+      </c>
+      <c r="O179" s="12" t="inlineStr">
+        <is>
+          <t>佐々木（Claude Code）</t>
+        </is>
+      </c>
+      <c r="P179" s="12" t="inlineStr">
+        <is>
+          <t>自動テスト成功</t>
+        </is>
+      </c>
+      <c r="Q179" s="12" t="inlineStr">
+        <is>
+          <t>evidence/UT/UT_フロントエンド_結果一覧_20261007.txt</t>
+        </is>
+      </c>
+      <c r="R179" s="12" t="n"/>
+      <c r="S179" s="12" t="n"/>
+      <c r="T179" s="12" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="12" t="inlineStr">
+        <is>
+          <t>UT-APP-E15</t>
+        </is>
+      </c>
+      <c r="B180" s="12" t="inlineStr">
+        <is>
+          <t>ApplicationService（申込・キャンセル・当日受付）</t>
+        </is>
+      </c>
+      <c r="C180" s="12" t="inlineStr">
+        <is>
+          <t>異常系</t>
+        </is>
+      </c>
+      <c r="D180" s="12" t="inlineStr">
+        <is>
+          <t>区分の無いイベントに区分を指定すると指定された区分が見つかりませんで拒否される</t>
+        </is>
+      </c>
+      <c r="E180" s="12" t="inlineStr">
+        <is>
+          <t>区分なしイベントでticketTypeIdを指定</t>
+        </is>
+      </c>
+      <c r="F180" s="12" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="G180" s="12" t="inlineStr">
+        <is>
+          <t>NotFoundException「指定された区分が見つかりません」（E-B-005）</t>
+        </is>
+      </c>
+      <c r="H180" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J180" s="12" t="inlineStr">
+        <is>
+          <t>32_処理詳細設計書 4章 AP-030 No.7</t>
+        </is>
+      </c>
+      <c r="K180" s="12" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="L180" s="12" t="inlineStr">
+        <is>
+          <t>apply_異常系_区分の無いイベントに区分を指定すると指定された区分が見つかりませんで拒否される</t>
+        </is>
+      </c>
+      <c r="M180" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N180" s="23" t="n">
+        <v>46304</v>
+      </c>
+      <c r="O180" s="12" t="inlineStr">
+        <is>
+          <t>佐々木（Claude Code）</t>
+        </is>
+      </c>
+      <c r="P180" s="12" t="inlineStr">
+        <is>
+          <t>自動テスト成功（Issue #18 の修正で追加）</t>
+        </is>
+      </c>
+      <c r="Q180" s="12" t="inlineStr">
+        <is>
+          <t>evidence/UT/UT_バックエンド_結果一覧_20261009.txt</t>
+        </is>
+      </c>
+      <c r="R180" s="12" t="n"/>
+      <c r="S180" s="12" t="n"/>
+      <c r="T180" s="12" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T177"/>
-  <conditionalFormatting sqref="M2:M177">
+  <autoFilter ref="A1:T180"/>
+  <conditionalFormatting sqref="M2:M180">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"OK"</formula>
     </cfRule>
@@ -16959,7 +17221,7 @@
       <formula>"対象外"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S177">
+  <conditionalFormatting sqref="S2:S180">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"OK"</formula>
     </cfRule>
@@ -16974,10 +17236,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M180" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,保留,対象外"</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="S2:S180" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>
@@ -41367,9 +41629,19 @@
         </is>
       </c>
       <c r="L81" s="12" t="n"/>
-      <c r="M81" s="12" t="n"/>
-      <c r="N81" s="12" t="n"/>
-      <c r="O81" s="12" t="n"/>
+      <c r="M81" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N81" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O81" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P81" s="12" t="n"/>
       <c r="Q81" s="15" t="inlineStr">
         <is>
@@ -42402,9 +42674,19 @@
         </is>
       </c>
       <c r="L94" s="12" t="n"/>
-      <c r="M94" s="12" t="n"/>
-      <c r="N94" s="12" t="n"/>
-      <c r="O94" s="12" t="n"/>
+      <c r="M94" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N94" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O94" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P94" s="12" t="n"/>
       <c r="Q94" s="15" t="inlineStr">
         <is>
@@ -42472,9 +42754,19 @@
         </is>
       </c>
       <c r="L95" s="12" t="n"/>
-      <c r="M95" s="12" t="n"/>
-      <c r="N95" s="12" t="n"/>
-      <c r="O95" s="12" t="n"/>
+      <c r="M95" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N95" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O95" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P95" s="12" t="n"/>
       <c r="Q95" s="15" t="inlineStr">
         <is>
@@ -42544,9 +42836,19 @@
         </is>
       </c>
       <c r="L96" s="12" t="n"/>
-      <c r="M96" s="12" t="n"/>
-      <c r="N96" s="12" t="n"/>
-      <c r="O96" s="12" t="n"/>
+      <c r="M96" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N96" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O96" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P96" s="12" t="n"/>
       <c r="Q96" s="15" t="inlineStr">
         <is>
@@ -42614,9 +42916,19 @@
         </is>
       </c>
       <c r="L97" s="12" t="n"/>
-      <c r="M97" s="12" t="n"/>
-      <c r="N97" s="12" t="n"/>
-      <c r="O97" s="12" t="n"/>
+      <c r="M97" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N97" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O97" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P97" s="12" t="n"/>
       <c r="Q97" s="15" t="inlineStr">
         <is>
@@ -42685,18 +42997,43 @@
         </is>
       </c>
       <c r="L98" s="12" t="n"/>
-      <c r="M98" s="12" t="n"/>
-      <c r="N98" s="12" t="n"/>
-      <c r="O98" s="12" t="n"/>
-      <c r="P98" s="12" t="n"/>
+      <c r="M98" s="12" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="N98" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O98" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P98" s="12" t="inlineStr">
+        <is>
+          <t>「区分に申込があるため変更できません」と表示され、保存できなかった。events の ID=53 の place は「会議室A」のまま変わっていない。参加区分は変更していない（区分の無いイベント）。
+【再テスト 2026/10/14】Issue #19 の修正後、場所を「会議室C」に変えて保存するとSC-120へ遷移し、変更後の場所が表示された。events の ID=53 の place が「会議室C」に更新され、ticket_types は変わっていない。</t>
+        </is>
+      </c>
       <c r="Q98" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_画面結合.xlsx／SC-121</t>
         </is>
       </c>
-      <c r="R98" s="12" t="n"/>
-      <c r="S98" s="12" t="n"/>
-      <c r="T98" s="12" t="n"/>
+      <c r="R98" s="12" t="inlineStr">
+        <is>
+          <t>#19</t>
+        </is>
+      </c>
+      <c r="S98" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T98" s="23" t="n">
+        <v>46309</v>
+      </c>
     </row>
     <row r="99" ht="27" customHeight="1">
       <c r="A99" s="12" t="inlineStr">
@@ -42840,9 +43177,19 @@
         </is>
       </c>
       <c r="L100" s="12" t="n"/>
-      <c r="M100" s="12" t="n"/>
-      <c r="N100" s="12" t="n"/>
-      <c r="O100" s="12" t="n"/>
+      <c r="M100" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N100" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O100" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P100" s="12" t="n"/>
       <c r="Q100" s="15" t="inlineStr">
         <is>
@@ -42911,9 +43258,19 @@
         </is>
       </c>
       <c r="L101" s="12" t="n"/>
-      <c r="M101" s="12" t="n"/>
-      <c r="N101" s="12" t="n"/>
-      <c r="O101" s="12" t="n"/>
+      <c r="M101" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N101" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O101" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P101" s="12" t="n"/>
       <c r="Q101" s="15" t="inlineStr">
         <is>
@@ -42982,9 +43339,19 @@
         </is>
       </c>
       <c r="L102" s="12" t="n"/>
-      <c r="M102" s="12" t="n"/>
-      <c r="N102" s="12" t="n"/>
-      <c r="O102" s="12" t="n"/>
+      <c r="M102" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N102" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O102" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P102" s="12" t="n"/>
       <c r="Q102" s="15" t="inlineStr">
         <is>
@@ -43053,9 +43420,19 @@
         </is>
       </c>
       <c r="L103" s="12" t="n"/>
-      <c r="M103" s="12" t="n"/>
-      <c r="N103" s="12" t="n"/>
-      <c r="O103" s="12" t="n"/>
+      <c r="M103" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N103" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O103" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P103" s="12" t="n"/>
       <c r="Q103" s="15" t="inlineStr">
         <is>
@@ -43123,9 +43500,19 @@
         </is>
       </c>
       <c r="L104" s="12" t="n"/>
-      <c r="M104" s="12" t="n"/>
-      <c r="N104" s="12" t="n"/>
-      <c r="O104" s="12" t="n"/>
+      <c r="M104" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N104" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O104" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P104" s="12" t="n"/>
       <c r="Q104" s="15" t="inlineStr">
         <is>
@@ -43194,9 +43581,19 @@
         </is>
       </c>
       <c r="L105" s="12" t="n"/>
-      <c r="M105" s="12" t="n"/>
-      <c r="N105" s="12" t="n"/>
-      <c r="O105" s="12" t="n"/>
+      <c r="M105" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N105" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O105" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P105" s="12" t="n"/>
       <c r="Q105" s="15" t="inlineStr">
         <is>
@@ -43265,9 +43662,19 @@
         </is>
       </c>
       <c r="L106" s="12" t="n"/>
-      <c r="M106" s="12" t="n"/>
-      <c r="N106" s="12" t="n"/>
-      <c r="O106" s="12" t="n"/>
+      <c r="M106" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N106" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O106" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P106" s="12" t="n"/>
       <c r="Q106" s="15" t="inlineStr">
         <is>
@@ -43335,9 +43742,19 @@
         </is>
       </c>
       <c r="L107" s="12" t="n"/>
-      <c r="M107" s="12" t="n"/>
-      <c r="N107" s="12" t="n"/>
-      <c r="O107" s="12" t="n"/>
+      <c r="M107" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N107" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O107" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P107" s="12" t="n"/>
       <c r="Q107" s="15" t="inlineStr">
         <is>
@@ -43405,9 +43822,19 @@
         </is>
       </c>
       <c r="L108" s="12" t="n"/>
-      <c r="M108" s="12" t="n"/>
-      <c r="N108" s="12" t="n"/>
-      <c r="O108" s="12" t="n"/>
+      <c r="M108" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N108" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O108" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P108" s="12" t="n"/>
       <c r="Q108" s="15" t="inlineStr">
         <is>
@@ -43476,9 +43903,19 @@
         </is>
       </c>
       <c r="L109" s="12" t="n"/>
-      <c r="M109" s="12" t="n"/>
-      <c r="N109" s="12" t="n"/>
-      <c r="O109" s="12" t="n"/>
+      <c r="M109" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N109" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O109" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P109" s="12" t="n"/>
       <c r="Q109" s="15" t="inlineStr">
         <is>
@@ -43517,7 +43954,7 @@
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>その行の「チェックイン」を押し、確認でOKを押す</t>
+          <t>その行の「再チェックイン」を押し、確認でOKを押す</t>
         </is>
       </c>
       <c r="G110" s="12" t="inlineStr">
@@ -43547,9 +43984,19 @@
         </is>
       </c>
       <c r="L110" s="12" t="n"/>
-      <c r="M110" s="12" t="n"/>
-      <c r="N110" s="12" t="n"/>
-      <c r="O110" s="12" t="n"/>
+      <c r="M110" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N110" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O110" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P110" s="12" t="n"/>
       <c r="Q110" s="15" t="inlineStr">
         <is>
@@ -43588,7 +44035,7 @@
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>その行の「チェックイン」を押し、確認で取り消す</t>
+          <t>その行の「再チェックイン」を押し、確認で取り消す</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
@@ -43618,9 +44065,19 @@
         </is>
       </c>
       <c r="L111" s="12" t="n"/>
-      <c r="M111" s="12" t="n"/>
-      <c r="N111" s="12" t="n"/>
-      <c r="O111" s="12" t="n"/>
+      <c r="M111" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N111" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O111" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P111" s="12" t="n"/>
       <c r="Q111" s="15" t="inlineStr">
         <is>
@@ -43688,9 +44145,19 @@
         </is>
       </c>
       <c r="L112" s="12" t="n"/>
-      <c r="M112" s="12" t="n"/>
-      <c r="N112" s="12" t="n"/>
-      <c r="O112" s="12" t="n"/>
+      <c r="M112" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N112" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O112" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P112" s="12" t="n"/>
       <c r="Q112" s="15" t="inlineStr">
         <is>
@@ -43758,9 +44225,19 @@
         </is>
       </c>
       <c r="L113" s="12" t="n"/>
-      <c r="M113" s="12" t="n"/>
-      <c r="N113" s="12" t="n"/>
-      <c r="O113" s="12" t="n"/>
+      <c r="M113" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N113" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O113" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P113" s="12" t="n"/>
       <c r="Q113" s="15" t="inlineStr">
         <is>
@@ -43828,9 +44305,19 @@
         </is>
       </c>
       <c r="L114" s="12" t="n"/>
-      <c r="M114" s="12" t="n"/>
-      <c r="N114" s="12" t="n"/>
-      <c r="O114" s="12" t="n"/>
+      <c r="M114" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N114" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O114" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P114" s="12" t="n"/>
       <c r="Q114" s="15" t="inlineStr">
         <is>
@@ -43898,9 +44385,19 @@
         </is>
       </c>
       <c r="L115" s="12" t="n"/>
-      <c r="M115" s="12" t="n"/>
-      <c r="N115" s="12" t="n"/>
-      <c r="O115" s="12" t="n"/>
+      <c r="M115" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N115" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O115" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P115" s="12" t="n"/>
       <c r="Q115" s="15" t="inlineStr">
         <is>
@@ -43968,9 +44465,19 @@
         </is>
       </c>
       <c r="L116" s="12" t="n"/>
-      <c r="M116" s="12" t="n"/>
-      <c r="N116" s="12" t="n"/>
-      <c r="O116" s="12" t="n"/>
+      <c r="M116" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N116" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O116" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P116" s="12" t="n"/>
       <c r="Q116" s="15" t="inlineStr">
         <is>
@@ -44038,9 +44545,19 @@
         </is>
       </c>
       <c r="L117" s="12" t="n"/>
-      <c r="M117" s="12" t="n"/>
-      <c r="N117" s="12" t="n"/>
-      <c r="O117" s="12" t="n"/>
+      <c r="M117" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N117" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O117" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P117" s="12" t="n"/>
       <c r="Q117" s="15" t="inlineStr">
         <is>
@@ -44109,9 +44626,19 @@
         </is>
       </c>
       <c r="L118" s="12" t="n"/>
-      <c r="M118" s="12" t="n"/>
-      <c r="N118" s="12" t="n"/>
-      <c r="O118" s="12" t="n"/>
+      <c r="M118" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N118" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O118" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P118" s="12" t="n"/>
       <c r="Q118" s="15" t="inlineStr">
         <is>
@@ -44179,9 +44706,19 @@
         </is>
       </c>
       <c r="L119" s="12" t="n"/>
-      <c r="M119" s="12" t="n"/>
-      <c r="N119" s="12" t="n"/>
-      <c r="O119" s="12" t="n"/>
+      <c r="M119" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N119" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O119" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P119" s="12" t="n"/>
       <c r="Q119" s="15" t="inlineStr">
         <is>
@@ -44249,9 +44786,19 @@
         </is>
       </c>
       <c r="L120" s="12" t="n"/>
-      <c r="M120" s="12" t="n"/>
-      <c r="N120" s="12" t="n"/>
-      <c r="O120" s="12" t="n"/>
+      <c r="M120" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N120" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O120" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P120" s="12" t="n"/>
       <c r="Q120" s="15" t="inlineStr">
         <is>
@@ -44320,9 +44867,19 @@
         </is>
       </c>
       <c r="L121" s="12" t="n"/>
-      <c r="M121" s="12" t="n"/>
-      <c r="N121" s="12" t="n"/>
-      <c r="O121" s="12" t="n"/>
+      <c r="M121" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N121" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O121" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P121" s="12" t="n"/>
       <c r="Q121" s="15" t="inlineStr">
         <is>
@@ -44391,9 +44948,19 @@
         </is>
       </c>
       <c r="L122" s="12" t="n"/>
-      <c r="M122" s="12" t="n"/>
-      <c r="N122" s="12" t="n"/>
-      <c r="O122" s="12" t="n"/>
+      <c r="M122" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N122" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O122" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P122" s="12" t="n"/>
       <c r="Q122" s="15" t="inlineStr">
         <is>
@@ -44461,9 +45028,19 @@
         </is>
       </c>
       <c r="L123" s="12" t="n"/>
-      <c r="M123" s="12" t="n"/>
-      <c r="N123" s="12" t="n"/>
-      <c r="O123" s="12" t="n"/>
+      <c r="M123" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N123" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O123" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P123" s="12" t="n"/>
       <c r="Q123" s="15" t="inlineStr">
         <is>
@@ -44531,9 +45108,19 @@
         </is>
       </c>
       <c r="L124" s="12" t="n"/>
-      <c r="M124" s="12" t="n"/>
-      <c r="N124" s="12" t="n"/>
-      <c r="O124" s="12" t="n"/>
+      <c r="M124" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N124" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O124" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P124" s="12" t="n"/>
       <c r="Q124" s="15" t="inlineStr">
         <is>
@@ -44602,9 +45189,19 @@
         </is>
       </c>
       <c r="L125" s="12" t="n"/>
-      <c r="M125" s="12" t="n"/>
-      <c r="N125" s="12" t="n"/>
-      <c r="O125" s="12" t="n"/>
+      <c r="M125" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N125" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O125" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P125" s="12" t="n"/>
       <c r="Q125" s="15" t="inlineStr">
         <is>
@@ -44673,10 +45270,24 @@
         </is>
       </c>
       <c r="L126" s="12" t="n"/>
-      <c r="M126" s="12" t="n"/>
-      <c r="N126" s="12" t="n"/>
-      <c r="O126" s="12" t="n"/>
-      <c r="P126" s="12" t="n"/>
+      <c r="M126" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N126" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O126" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P126" s="12" t="inlineStr">
+        <is>
+          <t>TD-05の利用者（一般ユーザー2）はIT-SC030-N07（本人による退会）で使うため、退会確認用ユーザー（ID=3）で確認した。</t>
+        </is>
+      </c>
       <c r="Q126" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_画面結合.xlsx／SC-141</t>
@@ -44744,9 +45355,19 @@
         </is>
       </c>
       <c r="L127" s="12" t="n"/>
-      <c r="M127" s="12" t="n"/>
-      <c r="N127" s="12" t="n"/>
-      <c r="O127" s="12" t="n"/>
+      <c r="M127" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N127" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O127" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P127" s="12" t="n"/>
       <c r="Q127" s="15" t="inlineStr">
         <is>
@@ -44814,9 +45435,19 @@
         </is>
       </c>
       <c r="L128" s="12" t="n"/>
-      <c r="M128" s="12" t="n"/>
-      <c r="N128" s="12" t="n"/>
-      <c r="O128" s="12" t="n"/>
+      <c r="M128" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N128" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O128" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P128" s="12" t="n"/>
       <c r="Q128" s="15" t="inlineStr">
         <is>
@@ -44884,9 +45515,19 @@
         </is>
       </c>
       <c r="L129" s="12" t="n"/>
-      <c r="M129" s="12" t="n"/>
-      <c r="N129" s="12" t="n"/>
-      <c r="O129" s="12" t="n"/>
+      <c r="M129" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N129" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O129" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P129" s="12" t="n"/>
       <c r="Q129" s="15" t="inlineStr">
         <is>
@@ -44955,9 +45596,19 @@
         </is>
       </c>
       <c r="L130" s="12" t="n"/>
-      <c r="M130" s="12" t="n"/>
-      <c r="N130" s="12" t="n"/>
-      <c r="O130" s="12" t="n"/>
+      <c r="M130" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N130" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O130" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P130" s="12" t="n"/>
       <c r="Q130" s="15" t="inlineStr">
         <is>
@@ -45025,9 +45676,19 @@
         </is>
       </c>
       <c r="L131" s="12" t="n"/>
-      <c r="M131" s="12" t="n"/>
-      <c r="N131" s="12" t="n"/>
-      <c r="O131" s="12" t="n"/>
+      <c r="M131" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N131" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O131" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P131" s="12" t="n"/>
       <c r="Q131" s="15" t="inlineStr">
         <is>
@@ -45095,9 +45756,19 @@
         </is>
       </c>
       <c r="L132" s="12" t="n"/>
-      <c r="M132" s="12" t="n"/>
-      <c r="N132" s="12" t="n"/>
-      <c r="O132" s="12" t="n"/>
+      <c r="M132" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N132" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O132" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P132" s="12" t="n"/>
       <c r="Q132" s="15" t="inlineStr">
         <is>
@@ -45165,9 +45836,19 @@
         </is>
       </c>
       <c r="L133" s="12" t="n"/>
-      <c r="M133" s="12" t="n"/>
-      <c r="N133" s="12" t="n"/>
-      <c r="O133" s="12" t="n"/>
+      <c r="M133" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N133" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O133" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P133" s="12" t="n"/>
       <c r="Q133" s="15" t="inlineStr">
         <is>
@@ -52269,7 +52950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -52432,6 +53113,55 @@
         <v>46304</v>
       </c>
       <c r="K3" s="16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>IT-SC121-N05</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>有効な申込があるイベントは、参加区分を変えなくても編集画面から保存できない</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>管理者で、受付済の申込がある「定員1テスト」（ID=53、区分なし）の編集画面を開き、場所を「会議室C」に変えて「保存」を押す</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>SC-120へ遷移し、変更後の場所が表示される。events.placeが更新される</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>「区分に申込があるため変更できません」と表示され、保存できない。events.placeは変わらない</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>#19</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>修正済み（再テストOK）</t>
+        </is>
+      </c>
+      <c r="I4" s="16" t="n"/>
+      <c r="J4" s="24" t="n">
+        <v>46309</v>
+      </c>
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -52656,13 +53386,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33A55CE1-1BE0-462F-A270-7D4CA7D09116}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA954426-4784-462E-93AE-DDEC3CD543D7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A4816FE-E827-4F25-8B1F-512C6930ACAC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB6D0D43-E17B-433C-9C0F-87F31A59BB4C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FABF144-784F-4059-9E5C-44E6245EB4A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{402DAD18-CB1A-44B2-B30A-C3C2694CC8F5}"/>
 </file>
--- a/docs/40_テスト/44_テスト結果表.xlsx
+++ b/docs/40_テスト/44_テスト結果表.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="サマリ" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,10 +25,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -16941,7 +16940,7 @@
       <c r="S177" s="12" t="n"/>
       <c r="T177" s="12" t="n"/>
     </row>
-    <row r="178">
+    <row r="178" ht="67.5" customHeight="1">
       <c r="A178" s="12" t="inlineStr">
         <is>
           <t>UT-HTTP-E03</t>
@@ -17029,7 +17028,7 @@
       <c r="S178" s="12" t="n"/>
       <c r="T178" s="12" t="n"/>
     </row>
-    <row r="179">
+    <row r="179" ht="67.5" customHeight="1">
       <c r="A179" s="12" t="inlineStr">
         <is>
           <t>UT-HTTP-E04</t>
@@ -17117,7 +17116,7 @@
       <c r="S179" s="12" t="n"/>
       <c r="T179" s="12" t="n"/>
     </row>
-    <row r="180">
+    <row r="180" ht="67.5" customHeight="1">
       <c r="A180" s="12" t="inlineStr">
         <is>
           <t>UT-APP-E15</t>
@@ -46225,10 +46224,24 @@
         </is>
       </c>
       <c r="L2" s="12" t="n"/>
-      <c r="M2" s="12" t="n"/>
-      <c r="N2" s="12" t="n"/>
-      <c r="O2" s="12" t="n"/>
-      <c r="P2" s="12" t="n"/>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N2" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O2" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P2" s="12" t="inlineStr">
+        <is>
+          <t>入力画面の撮影は漏れたため、登録直後（14:52）のイベント一覧の画面とデータベースの前後で確認した（users に ID=5「ST利用者」、role_code=1 が 14:51:44 に追加）。</t>
+        </is>
+      </c>
       <c r="Q2" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／ST-01</t>
@@ -46295,9 +46308,19 @@
         </is>
       </c>
       <c r="L3" s="12" t="n"/>
-      <c r="M3" s="12" t="n"/>
-      <c r="N3" s="12" t="n"/>
-      <c r="O3" s="12" t="n"/>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N3" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P3" s="12" t="n"/>
       <c r="Q3" s="15" t="inlineStr">
         <is>
@@ -46365,9 +46388,19 @@
         </is>
       </c>
       <c r="L4" s="12" t="n"/>
-      <c r="M4" s="12" t="n"/>
-      <c r="N4" s="12" t="n"/>
-      <c r="O4" s="12" t="n"/>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N4" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P4" s="12" t="n"/>
       <c r="Q4" s="15" t="inlineStr">
         <is>
@@ -46436,9 +46469,19 @@
         </is>
       </c>
       <c r="L5" s="12" t="n"/>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="12" t="n"/>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N5" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P5" s="12" t="n"/>
       <c r="Q5" s="15" t="inlineStr">
         <is>
@@ -46507,9 +46550,19 @@
         </is>
       </c>
       <c r="L6" s="12" t="n"/>
-      <c r="M6" s="12" t="n"/>
-      <c r="N6" s="12" t="n"/>
-      <c r="O6" s="12" t="n"/>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N6" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P6" s="12" t="n"/>
       <c r="Q6" s="15" t="inlineStr">
         <is>
@@ -46577,9 +46630,19 @@
         </is>
       </c>
       <c r="L7" s="12" t="n"/>
-      <c r="M7" s="12" t="n"/>
-      <c r="N7" s="12" t="n"/>
-      <c r="O7" s="12" t="n"/>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N7" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P7" s="12" t="n"/>
       <c r="Q7" s="15" t="inlineStr">
         <is>
@@ -46648,9 +46711,19 @@
         </is>
       </c>
       <c r="L8" s="12" t="n"/>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="12" t="n"/>
-      <c r="O8" s="12" t="n"/>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N8" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P8" s="12" t="n"/>
       <c r="Q8" s="15" t="inlineStr">
         <is>
@@ -46718,9 +46791,19 @@
         </is>
       </c>
       <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="12" t="n"/>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N9" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P9" s="12" t="n"/>
       <c r="Q9" s="15" t="inlineStr">
         <is>
@@ -46788,9 +46871,19 @@
         </is>
       </c>
       <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="12" t="n"/>
-      <c r="O10" s="12" t="n"/>
+      <c r="M10" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N10" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P10" s="12" t="n"/>
       <c r="Q10" s="15" t="inlineStr">
         <is>
@@ -46859,9 +46952,19 @@
         </is>
       </c>
       <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="12" t="n"/>
-      <c r="O11" s="12" t="n"/>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N11" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P11" s="12" t="n"/>
       <c r="Q11" s="15" t="inlineStr">
         <is>
@@ -46930,9 +47033,19 @@
         </is>
       </c>
       <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="12" t="n"/>
-      <c r="O12" s="12" t="n"/>
+      <c r="M12" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N12" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P12" s="12" t="n"/>
       <c r="Q12" s="15" t="inlineStr">
         <is>
@@ -47001,9 +47114,19 @@
         </is>
       </c>
       <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
-      <c r="N13" s="12" t="n"/>
-      <c r="O13" s="12" t="n"/>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N13" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P13" s="12" t="n"/>
       <c r="Q13" s="15" t="inlineStr">
         <is>
@@ -47071,9 +47194,19 @@
         </is>
       </c>
       <c r="L14" s="12" t="n"/>
-      <c r="M14" s="12" t="n"/>
-      <c r="N14" s="12" t="n"/>
-      <c r="O14" s="12" t="n"/>
+      <c r="M14" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N14" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P14" s="12" t="n"/>
       <c r="Q14" s="15" t="inlineStr">
         <is>
@@ -47143,9 +47276,19 @@
         </is>
       </c>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
-      <c r="N15" s="12" t="n"/>
-      <c r="O15" s="12" t="n"/>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N15" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P15" s="12" t="n"/>
       <c r="Q15" s="15" t="inlineStr">
         <is>
@@ -47214,9 +47357,19 @@
         </is>
       </c>
       <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="12" t="n"/>
-      <c r="O16" s="12" t="n"/>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N16" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P16" s="12" t="n"/>
       <c r="Q16" s="15" t="inlineStr">
         <is>
@@ -47284,9 +47437,19 @@
         </is>
       </c>
       <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
-      <c r="N17" s="12" t="n"/>
-      <c r="O17" s="12" t="n"/>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N17" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P17" s="12" t="n"/>
       <c r="Q17" s="15" t="inlineStr">
         <is>
@@ -47355,9 +47518,19 @@
         </is>
       </c>
       <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="12" t="n"/>
-      <c r="O18" s="12" t="n"/>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N18" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P18" s="12" t="n"/>
       <c r="Q18" s="15" t="inlineStr">
         <is>
@@ -47425,9 +47598,19 @@
         </is>
       </c>
       <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
-      <c r="N19" s="12" t="n"/>
-      <c r="O19" s="12" t="n"/>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N19" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P19" s="12" t="n"/>
       <c r="Q19" s="15" t="inlineStr">
         <is>
@@ -47495,9 +47678,19 @@
         </is>
       </c>
       <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
-      <c r="N20" s="12" t="n"/>
-      <c r="O20" s="12" t="n"/>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N20" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P20" s="12" t="n"/>
       <c r="Q20" s="15" t="inlineStr">
         <is>
@@ -47566,9 +47759,19 @@
         </is>
       </c>
       <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="12" t="n"/>
-      <c r="O21" s="12" t="n"/>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N21" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P21" s="12" t="n"/>
       <c r="Q21" s="15" t="inlineStr">
         <is>
@@ -47612,7 +47815,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>「ST説明会」の行に、定員3・受付済数1・充足率0.33が表示される</t>
+          <t>「ST説明会」の行に、定員3・受付済数1・充足率33%が表示される</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -47636,10 +47839,24 @@
         </is>
       </c>
       <c r="L22" s="12" t="n"/>
-      <c r="M22" s="12" t="n"/>
-      <c r="N22" s="12" t="n"/>
-      <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N22" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P22" s="12" t="inlineStr">
+        <is>
+          <t>「ST説明会」の行に定員3・受付済数1・充足率33%が表示された。</t>
+        </is>
+      </c>
       <c r="Q22" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／ST-02</t>
@@ -47706,9 +47923,19 @@
         </is>
       </c>
       <c r="L23" s="12" t="n"/>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="12" t="n"/>
-      <c r="O23" s="12" t="n"/>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N23" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O23" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P23" s="12" t="n"/>
       <c r="Q23" s="15" t="inlineStr">
         <is>
@@ -47777,10 +48004,24 @@
         </is>
       </c>
       <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="12" t="n"/>
-      <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
+      <c r="M24" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N24" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P24" s="12" t="inlineStr">
+        <is>
+          <t>開催日時・申込締切以外の項目が複写された。参加区分は「午後」「午前」の順で表示され、複製元の登録順（午前・午後）と異なる（設計書に並び順の定めは無い）。</t>
+        </is>
+      </c>
       <c r="Q24" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／ST-02</t>
@@ -47849,9 +48090,19 @@
         </is>
       </c>
       <c r="L25" s="12" t="n"/>
-      <c r="M25" s="12" t="n"/>
-      <c r="N25" s="12" t="n"/>
-      <c r="O25" s="12" t="n"/>
+      <c r="M25" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N25" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O25" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P25" s="12" t="n"/>
       <c r="Q25" s="15" t="inlineStr">
         <is>
@@ -47919,10 +48170,24 @@
         </is>
       </c>
       <c r="L26" s="12" t="n"/>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="12" t="n"/>
-      <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
+      <c r="M26" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N26" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P26" s="12" t="inlineStr">
+        <is>
+          <t>シナリオ開始時にデータを作り直したため、コメントは0件（「コメントはありません。」）の表示を確認した。</t>
+        </is>
+      </c>
       <c r="Q26" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／ST-02</t>
@@ -47990,9 +48255,19 @@
         </is>
       </c>
       <c r="L27" s="12" t="n"/>
-      <c r="M27" s="12" t="n"/>
-      <c r="N27" s="12" t="n"/>
-      <c r="O27" s="12" t="n"/>
+      <c r="M27" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N27" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P27" s="12" t="n"/>
       <c r="Q27" s="15" t="inlineStr">
         <is>
@@ -48060,10 +48335,24 @@
         </is>
       </c>
       <c r="L28" s="12" t="n"/>
-      <c r="M28" s="12" t="n"/>
-      <c r="N28" s="12" t="n"/>
-      <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
+      <c r="M28" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N28" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P28" s="12" t="inlineStr">
+        <is>
+          <t>SC-022 ではなく、SC-020（イベント一覧）の詳細の展開で確認した。残り枠0名、「満席のため、申し込むとキャンセル待ちに登録されます。」と「キャンセル待ちで申し込む」ボタンが表示された。</t>
+        </is>
+      </c>
       <c r="Q28" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／ST-03</t>
@@ -48131,9 +48420,19 @@
         </is>
       </c>
       <c r="L29" s="12" t="n"/>
-      <c r="M29" s="12" t="n"/>
-      <c r="N29" s="12" t="n"/>
-      <c r="O29" s="12" t="n"/>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N29" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O29" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P29" s="12" t="n"/>
       <c r="Q29" s="15" t="inlineStr">
         <is>
@@ -48202,9 +48501,19 @@
         </is>
       </c>
       <c r="L30" s="12" t="n"/>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="12" t="n"/>
-      <c r="O30" s="12" t="n"/>
+      <c r="M30" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N30" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P30" s="12" t="n"/>
       <c r="Q30" s="15" t="inlineStr">
         <is>
@@ -48272,9 +48581,19 @@
         </is>
       </c>
       <c r="L31" s="12" t="n"/>
-      <c r="M31" s="12" t="n"/>
-      <c r="N31" s="12" t="n"/>
-      <c r="O31" s="12" t="n"/>
+      <c r="M31" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N31" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O31" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P31" s="12" t="n"/>
       <c r="Q31" s="15" t="inlineStr">
         <is>
@@ -48342,9 +48661,19 @@
         </is>
       </c>
       <c r="L32" s="12" t="n"/>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="12" t="n"/>
-      <c r="O32" s="12" t="n"/>
+      <c r="M32" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N32" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P32" s="12" t="n"/>
       <c r="Q32" s="15" t="inlineStr">
         <is>
@@ -48413,9 +48742,19 @@
         </is>
       </c>
       <c r="L33" s="12" t="n"/>
-      <c r="M33" s="12" t="n"/>
-      <c r="N33" s="12" t="n"/>
-      <c r="O33" s="12" t="n"/>
+      <c r="M33" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N33" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O33" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P33" s="12" t="n"/>
       <c r="Q33" s="15" t="inlineStr">
         <is>
@@ -48483,9 +48822,19 @@
         </is>
       </c>
       <c r="L34" s="12" t="n"/>
-      <c r="M34" s="12" t="n"/>
-      <c r="N34" s="12" t="n"/>
-      <c r="O34" s="12" t="n"/>
+      <c r="M34" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N34" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O34" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P34" s="12" t="n"/>
       <c r="Q34" s="15" t="inlineStr">
         <is>
@@ -48553,9 +48902,19 @@
         </is>
       </c>
       <c r="L35" s="12" t="n"/>
-      <c r="M35" s="12" t="n"/>
-      <c r="N35" s="12" t="n"/>
-      <c r="O35" s="12" t="n"/>
+      <c r="M35" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N35" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O35" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P35" s="12" t="n"/>
       <c r="Q35" s="15" t="inlineStr">
         <is>
@@ -48623,9 +48982,19 @@
         </is>
       </c>
       <c r="L36" s="12" t="n"/>
-      <c r="M36" s="12" t="n"/>
-      <c r="N36" s="12" t="n"/>
-      <c r="O36" s="12" t="n"/>
+      <c r="M36" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N36" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P36" s="12" t="n"/>
       <c r="Q36" s="15" t="inlineStr">
         <is>
@@ -48694,9 +49063,19 @@
         </is>
       </c>
       <c r="L37" s="12" t="n"/>
-      <c r="M37" s="12" t="n"/>
-      <c r="N37" s="12" t="n"/>
-      <c r="O37" s="12" t="n"/>
+      <c r="M37" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N37" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O37" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P37" s="12" t="n"/>
       <c r="Q37" s="15" t="inlineStr">
         <is>
@@ -48765,9 +49144,19 @@
         </is>
       </c>
       <c r="L38" s="12" t="n"/>
-      <c r="M38" s="12" t="n"/>
-      <c r="N38" s="12" t="n"/>
-      <c r="O38" s="12" t="n"/>
+      <c r="M38" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N38" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O38" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P38" s="12" t="n"/>
       <c r="Q38" s="15" t="inlineStr">
         <is>
@@ -48835,9 +49224,19 @@
         </is>
       </c>
       <c r="L39" s="12" t="n"/>
-      <c r="M39" s="12" t="n"/>
-      <c r="N39" s="12" t="n"/>
-      <c r="O39" s="12" t="n"/>
+      <c r="M39" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N39" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O39" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P39" s="12" t="n"/>
       <c r="Q39" s="15" t="inlineStr">
         <is>
@@ -48906,9 +49305,19 @@
         </is>
       </c>
       <c r="L40" s="12" t="n"/>
-      <c r="M40" s="12" t="n"/>
-      <c r="N40" s="12" t="n"/>
-      <c r="O40" s="12" t="n"/>
+      <c r="M40" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N40" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O40" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P40" s="12" t="n"/>
       <c r="Q40" s="15" t="inlineStr">
         <is>
@@ -48976,9 +49385,19 @@
         </is>
       </c>
       <c r="L41" s="12" t="n"/>
-      <c r="M41" s="12" t="n"/>
-      <c r="N41" s="12" t="n"/>
-      <c r="O41" s="12" t="n"/>
+      <c r="M41" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N41" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O41" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P41" s="12" t="n"/>
       <c r="Q41" s="15" t="inlineStr">
         <is>
@@ -49047,9 +49466,19 @@
         </is>
       </c>
       <c r="L42" s="12" t="n"/>
-      <c r="M42" s="12" t="n"/>
-      <c r="N42" s="12" t="n"/>
-      <c r="O42" s="12" t="n"/>
+      <c r="M42" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N42" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O42" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P42" s="12" t="n"/>
       <c r="Q42" s="15" t="inlineStr">
         <is>
@@ -49118,9 +49547,19 @@
         </is>
       </c>
       <c r="L43" s="12" t="n"/>
-      <c r="M43" s="12" t="n"/>
-      <c r="N43" s="12" t="n"/>
-      <c r="O43" s="12" t="n"/>
+      <c r="M43" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N43" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O43" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P43" s="12" t="n"/>
       <c r="Q43" s="15" t="inlineStr">
         <is>
@@ -49189,9 +49628,19 @@
         </is>
       </c>
       <c r="L44" s="12" t="n"/>
-      <c r="M44" s="12" t="n"/>
-      <c r="N44" s="12" t="n"/>
-      <c r="O44" s="12" t="n"/>
+      <c r="M44" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N44" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O44" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P44" s="12" t="n"/>
       <c r="Q44" s="15" t="inlineStr">
         <is>
@@ -49260,9 +49709,19 @@
         </is>
       </c>
       <c r="L45" s="12" t="n"/>
-      <c r="M45" s="12" t="n"/>
-      <c r="N45" s="12" t="n"/>
-      <c r="O45" s="12" t="n"/>
+      <c r="M45" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N45" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O45" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P45" s="12" t="n"/>
       <c r="Q45" s="15" t="inlineStr">
         <is>
@@ -49330,9 +49789,19 @@
         </is>
       </c>
       <c r="L46" s="12" t="n"/>
-      <c r="M46" s="12" t="n"/>
-      <c r="N46" s="12" t="n"/>
-      <c r="O46" s="12" t="n"/>
+      <c r="M46" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N46" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O46" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P46" s="12" t="n"/>
       <c r="Q46" s="15" t="inlineStr">
         <is>
@@ -49403,10 +49872,24 @@
         </is>
       </c>
       <c r="L47" s="12" t="n"/>
-      <c r="M47" s="12" t="n"/>
-      <c r="N47" s="12" t="n"/>
-      <c r="O47" s="12" t="n"/>
-      <c r="P47" s="12" t="n"/>
+      <c r="M47" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N47" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O47" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P47" s="12" t="inlineStr">
+        <is>
+          <t>ST-04-05〜07 の申込・お気に入り・コメントが残っていた。利用者詳細には、TD-04（開催済テスト）の申込も表示されている（テストデータとして登録した申込）。</t>
+        </is>
+      </c>
       <c r="Q47" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／ST-04</t>
@@ -49473,9 +49956,19 @@
         </is>
       </c>
       <c r="L48" s="12" t="n"/>
-      <c r="M48" s="12" t="n"/>
-      <c r="N48" s="12" t="n"/>
-      <c r="O48" s="12" t="n"/>
+      <c r="M48" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N48" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O48" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P48" s="12" t="n"/>
       <c r="Q48" s="15" t="inlineStr">
         <is>
@@ -49543,9 +50036,19 @@
         </is>
       </c>
       <c r="L49" s="12" t="n"/>
-      <c r="M49" s="12" t="n"/>
-      <c r="N49" s="12" t="n"/>
-      <c r="O49" s="12" t="n"/>
+      <c r="M49" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N49" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O49" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P49" s="12" t="n"/>
       <c r="Q49" s="15" t="inlineStr">
         <is>
@@ -49613,9 +50116,19 @@
         </is>
       </c>
       <c r="L50" s="12" t="n"/>
-      <c r="M50" s="12" t="n"/>
-      <c r="N50" s="12" t="n"/>
-      <c r="O50" s="12" t="n"/>
+      <c r="M50" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N50" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O50" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P50" s="12" t="n"/>
       <c r="Q50" s="15" t="inlineStr">
         <is>
@@ -49683,10 +50196,24 @@
         </is>
       </c>
       <c r="L51" s="12" t="n"/>
-      <c r="M51" s="12" t="n"/>
-      <c r="N51" s="12" t="n"/>
-      <c r="O51" s="12" t="n"/>
-      <c r="P51" s="12" t="n"/>
+      <c r="M51" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N51" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O51" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P51" s="12" t="inlineStr">
+        <is>
+          <t>パスワード変更画面（/my/password）を開いた直後の画像は撮影が漏れたため、ST-05-03 の画像（同じ画面で変更を完了した状態）で、パスワード変更画面が表示されたことを確認した。</t>
+        </is>
+      </c>
       <c r="Q51" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／ST-05</t>
@@ -49754,9 +50281,19 @@
         </is>
       </c>
       <c r="L52" s="12" t="n"/>
-      <c r="M52" s="12" t="n"/>
-      <c r="N52" s="12" t="n"/>
-      <c r="O52" s="12" t="n"/>
+      <c r="M52" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N52" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O52" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P52" s="12" t="n"/>
       <c r="Q52" s="15" t="inlineStr">
         <is>
@@ -49824,9 +50361,19 @@
         </is>
       </c>
       <c r="L53" s="12" t="n"/>
-      <c r="M53" s="12" t="n"/>
-      <c r="N53" s="12" t="n"/>
-      <c r="O53" s="12" t="n"/>
+      <c r="M53" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N53" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O53" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P53" s="12" t="n"/>
       <c r="Q53" s="15" t="inlineStr">
         <is>
@@ -49894,9 +50441,19 @@
         </is>
       </c>
       <c r="L54" s="12" t="n"/>
-      <c r="M54" s="12" t="n"/>
-      <c r="N54" s="12" t="n"/>
-      <c r="O54" s="12" t="n"/>
+      <c r="M54" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N54" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O54" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P54" s="12" t="n"/>
       <c r="Q54" s="15" t="inlineStr">
         <is>
@@ -49965,9 +50522,19 @@
         </is>
       </c>
       <c r="L55" s="12" t="n"/>
-      <c r="M55" s="12" t="n"/>
-      <c r="N55" s="12" t="n"/>
-      <c r="O55" s="12" t="n"/>
+      <c r="M55" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N55" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O55" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P55" s="12" t="n"/>
       <c r="Q55" s="15" t="inlineStr">
         <is>
@@ -50035,9 +50602,19 @@
         </is>
       </c>
       <c r="L56" s="12" t="n"/>
-      <c r="M56" s="12" t="n"/>
-      <c r="N56" s="12" t="n"/>
-      <c r="O56" s="12" t="n"/>
+      <c r="M56" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N56" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O56" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P56" s="12" t="n"/>
       <c r="Q56" s="15" t="inlineStr">
         <is>
@@ -50106,9 +50683,19 @@
         </is>
       </c>
       <c r="L57" s="12" t="n"/>
-      <c r="M57" s="12" t="n"/>
-      <c r="N57" s="12" t="n"/>
-      <c r="O57" s="12" t="n"/>
+      <c r="M57" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N57" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O57" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P57" s="12" t="n"/>
       <c r="Q57" s="15" t="inlineStr">
         <is>
@@ -50177,9 +50764,19 @@
         </is>
       </c>
       <c r="L58" s="12" t="n"/>
-      <c r="M58" s="12" t="n"/>
-      <c r="N58" s="12" t="n"/>
-      <c r="O58" s="12" t="n"/>
+      <c r="M58" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N58" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O58" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P58" s="12" t="n"/>
       <c r="Q58" s="15" t="inlineStr">
         <is>
@@ -50247,9 +50844,19 @@
         </is>
       </c>
       <c r="L59" s="12" t="n"/>
-      <c r="M59" s="12" t="n"/>
-      <c r="N59" s="12" t="n"/>
-      <c r="O59" s="12" t="n"/>
+      <c r="M59" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N59" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O59" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P59" s="12" t="n"/>
       <c r="Q59" s="15" t="inlineStr">
         <is>
@@ -50318,9 +50925,19 @@
         </is>
       </c>
       <c r="L60" s="12" t="n"/>
-      <c r="M60" s="12" t="n"/>
-      <c r="N60" s="12" t="n"/>
-      <c r="O60" s="12" t="n"/>
+      <c r="M60" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N60" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O60" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P60" s="12" t="n"/>
       <c r="Q60" s="15" t="inlineStr">
         <is>
@@ -50388,9 +51005,19 @@
         </is>
       </c>
       <c r="L61" s="12" t="n"/>
-      <c r="M61" s="12" t="n"/>
-      <c r="N61" s="12" t="n"/>
-      <c r="O61" s="12" t="n"/>
+      <c r="M61" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N61" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O61" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P61" s="12" t="n"/>
       <c r="Q61" s="15" t="inlineStr">
         <is>
@@ -50459,9 +51086,19 @@
         </is>
       </c>
       <c r="L62" s="12" t="n"/>
-      <c r="M62" s="12" t="n"/>
-      <c r="N62" s="12" t="n"/>
-      <c r="O62" s="12" t="n"/>
+      <c r="M62" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N62" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="O62" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P62" s="12" t="n"/>
       <c r="Q62" s="15" t="inlineStr">
         <is>
@@ -50530,9 +51167,19 @@
         </is>
       </c>
       <c r="L63" s="12" t="n"/>
-      <c r="M63" s="12" t="n"/>
-      <c r="N63" s="12" t="n"/>
-      <c r="O63" s="12" t="n"/>
+      <c r="M63" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N63" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O63" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P63" s="12" t="n"/>
       <c r="Q63" s="15" t="inlineStr">
         <is>
@@ -50601,10 +51248,24 @@
         </is>
       </c>
       <c r="L64" s="12" t="n"/>
-      <c r="M64" s="12" t="n"/>
-      <c r="N64" s="12" t="n"/>
-      <c r="O64" s="12" t="n"/>
-      <c r="P64" s="12" t="n"/>
+      <c r="M64" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N64" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O64" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P64" s="12" t="inlineStr">
+        <is>
+          <t>「申込があるため削除できません」が通知され、区分テストは一覧に残った。通知の画像は撮り直し（09:32）。events の deleted_at は NULL のまま。</t>
+        </is>
+      </c>
       <c r="Q64" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／ST-12</t>
@@ -50672,9 +51333,19 @@
         </is>
       </c>
       <c r="L65" s="12" t="n"/>
-      <c r="M65" s="12" t="n"/>
-      <c r="N65" s="12" t="n"/>
-      <c r="O65" s="12" t="n"/>
+      <c r="M65" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N65" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O65" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P65" s="12" t="n"/>
       <c r="Q65" s="15" t="inlineStr">
         <is>
@@ -50743,9 +51414,19 @@
         </is>
       </c>
       <c r="L66" s="12" t="n"/>
-      <c r="M66" s="12" t="n"/>
-      <c r="N66" s="12" t="n"/>
-      <c r="O66" s="12" t="n"/>
+      <c r="M66" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N66" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O66" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P66" s="12" t="n"/>
       <c r="Q66" s="15" t="inlineStr">
         <is>
@@ -50813,10 +51494,24 @@
         </is>
       </c>
       <c r="L67" s="12" t="n"/>
-      <c r="M67" s="12" t="n"/>
-      <c r="N67" s="12" t="n"/>
-      <c r="O67" s="12" t="n"/>
-      <c r="P67" s="12" t="n"/>
+      <c r="M67" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N67" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O67" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P67" s="12" t="inlineStr">
+        <is>
+          <t>ST-12-04 と同じ画面（自分の利用者詳細、/admin/users/2）で、ボタンが「管理者権限を外す」だけで「退会させる」が表示されていないことを確認した（ST-12-05 用の画像は撮影漏れのため、ST-12-04 の画像を使用）。</t>
+        </is>
+      </c>
       <c r="Q67" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／ST-12</t>
@@ -50884,9 +51579,19 @@
         </is>
       </c>
       <c r="L68" s="12" t="n"/>
-      <c r="M68" s="12" t="n"/>
-      <c r="N68" s="12" t="n"/>
-      <c r="O68" s="12" t="n"/>
+      <c r="M68" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N68" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O68" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P68" s="12" t="n"/>
       <c r="Q68" s="15" t="inlineStr">
         <is>
@@ -50954,9 +51659,19 @@
         </is>
       </c>
       <c r="L69" s="12" t="n"/>
-      <c r="M69" s="12" t="n"/>
-      <c r="N69" s="12" t="n"/>
-      <c r="O69" s="12" t="n"/>
+      <c r="M69" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N69" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O69" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P69" s="12" t="n"/>
       <c r="Q69" s="15" t="inlineStr">
         <is>
@@ -51025,9 +51740,19 @@
         </is>
       </c>
       <c r="L70" s="12" t="n"/>
-      <c r="M70" s="12" t="n"/>
-      <c r="N70" s="12" t="n"/>
-      <c r="O70" s="12" t="n"/>
+      <c r="M70" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N70" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O70" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P70" s="12" t="n"/>
       <c r="Q70" s="15" t="inlineStr">
         <is>
@@ -51095,10 +51820,24 @@
         </is>
       </c>
       <c r="L71" s="12" t="n"/>
-      <c r="M71" s="12" t="n"/>
-      <c r="N71" s="12" t="n"/>
-      <c r="O71" s="12" t="n"/>
-      <c r="P71" s="12" t="n"/>
+      <c r="M71" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N71" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O71" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P71" s="12" t="inlineStr">
+        <is>
+          <t>一般B のタブ（退会前から開いていたイベント一覧）で「マイページ」を押すと、API が401を返し、ログイン画面に遷移した。</t>
+        </is>
+      </c>
       <c r="Q71" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／ST-13</t>
@@ -51165,9 +51904,19 @@
         </is>
       </c>
       <c r="L72" s="12" t="n"/>
-      <c r="M72" s="12" t="n"/>
-      <c r="N72" s="12" t="n"/>
-      <c r="O72" s="12" t="n"/>
+      <c r="M72" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N72" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O72" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P72" s="12" t="n"/>
       <c r="Q72" s="15" t="inlineStr">
         <is>
@@ -51236,9 +51985,19 @@
         </is>
       </c>
       <c r="L73" s="12" t="n"/>
-      <c r="M73" s="12" t="n"/>
-      <c r="N73" s="12" t="n"/>
-      <c r="O73" s="12" t="n"/>
+      <c r="M73" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N73" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O73" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P73" s="12" t="n"/>
       <c r="Q73" s="15" t="inlineStr">
         <is>
@@ -51394,10 +52153,24 @@
         </is>
       </c>
       <c r="L75" s="12" t="n"/>
-      <c r="M75" s="12" t="n"/>
-      <c r="N75" s="12" t="n"/>
-      <c r="O75" s="12" t="n"/>
-      <c r="P75" s="12" t="n"/>
+      <c r="M75" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N75" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O75" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P75" s="12" t="inlineStr">
+        <is>
+          <t>一般A（10:01:11）が受付済、一般B（10:01:13）がキャンセル待ちになった。applications の event_id=53 は status_code 1 が1件・2 が1件。</t>
+        </is>
+      </c>
       <c r="Q75" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -51464,10 +52237,24 @@
         </is>
       </c>
       <c r="L76" s="12" t="n"/>
-      <c r="M76" s="12" t="n"/>
-      <c r="N76" s="12" t="n"/>
-      <c r="O76" s="12" t="n"/>
-      <c r="P76" s="12" t="n"/>
+      <c r="M76" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N76" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O76" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P76" s="12" t="inlineStr">
+        <is>
+          <t>61回の呼び出しをスクリプトで連続して行い（約15秒）、61回すべて200だった。結果の一覧を証跡に貼付。</t>
+        </is>
+      </c>
       <c r="Q76" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -51534,10 +52321,24 @@
         </is>
       </c>
       <c r="L77" s="12" t="n"/>
-      <c r="M77" s="12" t="n"/>
-      <c r="N77" s="12" t="n"/>
-      <c r="O77" s="12" t="n"/>
-      <c r="P77" s="12" t="n"/>
+      <c r="M77" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N77" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O77" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P77" s="12" t="inlineStr">
+        <is>
+          <t>Network タブを Doc で絞り込み、画面を3つ切り替えた後も Doc の行は0件だった。</t>
+        </is>
+      </c>
       <c r="Q77" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -51604,10 +52405,24 @@
         </is>
       </c>
       <c r="L78" s="12" t="n"/>
-      <c r="M78" s="12" t="n"/>
-      <c r="N78" s="12" t="n"/>
-      <c r="O78" s="12" t="n"/>
-      <c r="P78" s="12" t="n"/>
+      <c r="M78" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N78" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O78" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P78" s="12" t="inlineStr">
+        <is>
+          <t>キャンセル待ちだけの状態は画面から作れない（受付済がキャンセルすると繰り上がる）ため、SQLで受付済の申込（ID=2）をキャンセル済（9）に変えてから、定員1テストを削除した。events の行は残り deleted_at に日時が入り、申込2件も残った。</t>
+        </is>
+      </c>
       <c r="Q78" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -51674,10 +52489,24 @@
         </is>
       </c>
       <c r="L79" s="12" t="n"/>
-      <c r="M79" s="12" t="n"/>
-      <c r="N79" s="12" t="n"/>
-      <c r="O79" s="12" t="n"/>
-      <c r="P79" s="12" t="n"/>
+      <c r="M79" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N79" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O79" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P79" s="12" t="inlineStr">
+        <is>
+          <t>nf-user@example.com の password_hash は「$2a$10$...」のハッシュ値で、Test1234 ではなかった。</t>
+        </is>
+      </c>
       <c r="Q79" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -51744,10 +52573,24 @@
         </is>
       </c>
       <c r="L80" s="12" t="n"/>
-      <c r="M80" s="12" t="n"/>
-      <c r="N80" s="12" t="n"/>
-      <c r="O80" s="12" t="n"/>
-      <c r="P80" s="12" t="n"/>
+      <c r="M80" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N80" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O80" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P80" s="12" t="inlineStr">
+        <is>
+          <t>INFO「イベント登録完了 eventId=57 実行者userId=2」が出力されていた。</t>
+        </is>
+      </c>
       <c r="Q80" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -51814,10 +52657,24 @@
         </is>
       </c>
       <c r="L81" s="12" t="n"/>
-      <c r="M81" s="12" t="n"/>
-      <c r="N81" s="12" t="n"/>
-      <c r="O81" s="12" t="n"/>
-      <c r="P81" s="12" t="n"/>
+      <c r="M81" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N81" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O81" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P81" s="12" t="inlineStr">
+        <is>
+          <t>一般A が 10:55:12 に申し込んだ（データベースで確認）が、申込の成功を示すログは出力されていない。</t>
+        </is>
+      </c>
       <c r="Q81" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -51884,10 +52741,24 @@
         </is>
       </c>
       <c r="L82" s="12" t="n"/>
-      <c r="M82" s="12" t="n"/>
-      <c r="N82" s="12" t="n"/>
-      <c r="O82" s="12" t="n"/>
-      <c r="P82" s="12" t="n"/>
+      <c r="M82" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N82" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O82" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P82" s="12" t="inlineStr">
+        <is>
+          <t>60秒以上書き込みが無い状態から、61回の呼び出しをスクリプトで連続して行い、1〜60回目は200、61回目が429「リクエストが多すぎます。しばらく時間をおいて再度お試しください」だった。結果の一覧を証跡に貼付。</t>
+        </is>
+      </c>
       <c r="Q82" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -51954,9 +52825,19 @@
         </is>
       </c>
       <c r="L83" s="12" t="n"/>
-      <c r="M83" s="12" t="n"/>
-      <c r="N83" s="12" t="n"/>
-      <c r="O83" s="12" t="n"/>
+      <c r="M83" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N83" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O83" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P83" s="12" t="n"/>
       <c r="Q83" s="15" t="inlineStr">
         <is>
@@ -52024,9 +52905,19 @@
         </is>
       </c>
       <c r="L84" s="12" t="n"/>
-      <c r="M84" s="12" t="n"/>
-      <c r="N84" s="12" t="n"/>
-      <c r="O84" s="12" t="n"/>
+      <c r="M84" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N84" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O84" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P84" s="12" t="n"/>
       <c r="Q84" s="15" t="inlineStr">
         <is>
@@ -52094,10 +52985,24 @@
         </is>
       </c>
       <c r="L85" s="12" t="n"/>
-      <c r="M85" s="12" t="n"/>
-      <c r="N85" s="12" t="n"/>
-      <c r="O85" s="12" t="n"/>
-      <c r="P85" s="12" t="n"/>
+      <c r="M85" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N85" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O85" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P85" s="12" t="inlineStr">
+        <is>
+          <t>Excel で申込者名が「'=HYPERLINK(...」と文字列で表示され、数式として実行されなかった。CSVの中身は画面のダウンロードと同じAPI（GET /api/reports/applications?format=csv）で取得して補足として貼付。</t>
+        </is>
+      </c>
       <c r="Q85" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -52164,9 +53069,19 @@
         </is>
       </c>
       <c r="L86" s="12" t="n"/>
-      <c r="M86" s="12" t="n"/>
-      <c r="N86" s="12" t="n"/>
-      <c r="O86" s="12" t="n"/>
+      <c r="M86" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N86" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O86" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P86" s="12" t="n"/>
       <c r="Q86" s="15" t="inlineStr">
         <is>
@@ -52234,10 +53149,24 @@
         </is>
       </c>
       <c r="L87" s="12" t="n"/>
-      <c r="M87" s="12" t="n"/>
-      <c r="N87" s="12" t="n"/>
-      <c r="O87" s="12" t="n"/>
-      <c r="P87" s="12" t="n"/>
+      <c r="M87" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N87" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O87" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P87" s="12" t="inlineStr">
+        <is>
+          <t>ブラウザのアドレスバーから開いた場合は X-User-Id が無いため 401「認証が必要です」になった。X-User-Id: 1 を付けて同じURLを呼ぶと 400「パラメータの形式が不正です」が返り、イベントの情報は返らなかった（補足として貼付）。</t>
+        </is>
+      </c>
       <c r="Q87" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -52304,10 +53233,24 @@
         </is>
       </c>
       <c r="L88" s="12" t="n"/>
-      <c r="M88" s="12" t="n"/>
-      <c r="N88" s="12" t="n"/>
-      <c r="O88" s="12" t="n"/>
-      <c r="P88" s="12" t="n"/>
+      <c r="M88" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N88" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O88" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P88" s="12" t="inlineStr">
+        <is>
+          <t>保存したログ（10:54〜10:57）を Wrong1234 で検索し、0件。ログイン失敗は WARN「ログインできませんでした。…」のみ。</t>
+        </is>
+      </c>
       <c r="Q88" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -52374,10 +53317,24 @@
         </is>
       </c>
       <c r="L89" s="12" t="n"/>
-      <c r="M89" s="12" t="n"/>
-      <c r="N89" s="12" t="n"/>
-      <c r="O89" s="12" t="n"/>
-      <c r="P89" s="12" t="n"/>
+      <c r="M89" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N89" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O89" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P89" s="12" t="inlineStr">
+        <is>
+          <t>保存したログを Regist1234 で検索し、0件。</t>
+        </is>
+      </c>
       <c r="Q89" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -52444,10 +53401,24 @@
         </is>
       </c>
       <c r="L90" s="12" t="n"/>
-      <c r="M90" s="12" t="n"/>
-      <c r="N90" s="12" t="n"/>
-      <c r="O90" s="12" t="n"/>
-      <c r="P90" s="12" t="n"/>
+      <c r="M90" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N90" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O90" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P90" s="12" t="inlineStr">
+        <is>
+          <t>保存したログを Change1234 で検索し、0件。パスワード変更は INFO「パスワード変更完了 userId=8」のみ。</t>
+        </is>
+      </c>
       <c r="Q90" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -52514,9 +53485,19 @@
         </is>
       </c>
       <c r="L91" s="12" t="n"/>
-      <c r="M91" s="12" t="n"/>
-      <c r="N91" s="12" t="n"/>
-      <c r="O91" s="12" t="n"/>
+      <c r="M91" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N91" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O91" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P91" s="12" t="n"/>
       <c r="Q91" s="15" t="inlineStr">
         <is>
@@ -52584,9 +53565,19 @@
         </is>
       </c>
       <c r="L92" s="12" t="n"/>
-      <c r="M92" s="12" t="n"/>
-      <c r="N92" s="12" t="n"/>
-      <c r="O92" s="12" t="n"/>
+      <c r="M92" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N92" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O92" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
       <c r="P92" s="12" t="n"/>
       <c r="Q92" s="15" t="inlineStr">
         <is>
@@ -52654,10 +53645,24 @@
         </is>
       </c>
       <c r="L93" s="12" t="n"/>
-      <c r="M93" s="12" t="n"/>
-      <c r="N93" s="12" t="n"/>
-      <c r="O93" s="12" t="n"/>
-      <c r="P93" s="12" t="n"/>
+      <c r="M93" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N93" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O93" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P93" s="12" t="inlineStr">
+        <is>
+          <t>利用者一覧（7件）の全要素の項目は userId・name・email・roleCode・roleName・anonymizedAt で、パスワードの項目は無い（応答の全体を補足として貼付）。</t>
+        </is>
+      </c>
       <c r="Q93" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -52724,10 +53729,24 @@
         </is>
       </c>
       <c r="L94" s="12" t="n"/>
-      <c r="M94" s="12" t="n"/>
-      <c r="N94" s="12" t="n"/>
-      <c r="O94" s="12" t="n"/>
-      <c r="P94" s="12" t="n"/>
+      <c r="M94" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N94" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O94" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P94" s="12" t="inlineStr">
+        <is>
+          <t>MySQL80 のサービスを停止して呼ぶと、約30秒後に500「システムエラーが発生しました。時間をおいて再度お試しください」が返った。応答にスタックトレース・SQL・クラス名は無い（スタックトレースはサーバーのログにのみ出力）。確認後、MySQL80 を起動し直した。</t>
+        </is>
+      </c>
       <c r="Q94" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -52794,10 +53813,24 @@
         </is>
       </c>
       <c r="L95" s="12" t="n"/>
-      <c r="M95" s="12" t="n"/>
-      <c r="N95" s="12" t="n"/>
-      <c r="O95" s="12" t="n"/>
-      <c r="P95" s="12" t="n"/>
+      <c r="M95" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N95" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O95" s="12" t="inlineStr">
+        <is>
+          <t>佐々木</t>
+        </is>
+      </c>
+      <c r="P95" s="12" t="inlineStr">
+        <is>
+          <t>バックエンドを停止した状態で、ログイン画面（SC-010）からログインを試みると「サーバーに接続できません。バックエンドが起動しているか確認してください。」が表示され、画面は空白にならなかった（直前の操作でログアウトしていたため、SC-020ではなくSC-010で確認）。</t>
+        </is>
+      </c>
       <c r="Q95" s="15" t="inlineStr">
         <is>
           <t>45_テストエビデンス_総合.xlsx／非機能</t>
@@ -53118,7 +54151,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="39" customHeight="1">
       <c r="A4" s="16" t="n">
         <v>3</v>
       </c>
@@ -53174,225 +54207,4 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010012AB853B196F794D8522E079E5062DE1" ma:contentTypeVersion="10" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f5519c8ad0001dc1944c7d5117d6ef1e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8d6e06c-e60e-47a7-a324-5df51f361a1d" xmlns:ns3="0eb4123e-ff08-448a-a51c-d574d85865b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6b6fc7ab0c5db989cb71f9aed3612649" ns2:_="" ns3:_="">
-    <xsd:import namespace="e8d6e06c-e60e-47a7-a324-5df51f361a1d"/>
-    <xsd:import namespace="0eb4123e-ff08-448a-a51c-d574d85865b6"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e8d6e06c-e60e-47a7-a324-5df51f361a1d" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8ae29c59-cffc-49bc-b1b2-82d81727b3d8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0eb4123e-ff08-448a-a51c-d574d85865b6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{617f6a86-eb1c-4018-be3f-ff946cbc1596}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="0eb4123e-ff08-448a-a51c-d574d85865b6">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8d6e06c-e60e-47a7-a324-5df51f361a1d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0eb4123e-ff08-448a-a51c-d574d85865b6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA954426-4784-462E-93AE-DDEC3CD543D7}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB6D0D43-E17B-433C-9C0F-87F31A59BB4C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{402DAD18-CB1A-44B2-B30A-C3C2694CC8F5}"/>
 </file>